--- a/json-datasets/csv/State_District-Relation.xlsx
+++ b/json-datasets/csv/State_District-Relation.xlsx
@@ -5,16 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GITHUB\ifsc-code-india\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GITHUB\ifsc-code-india\json-datasets\csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6DBE8AF-7D54-4655-8B3F-74E43EEF955C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DE231C3-318C-4B42-B9D3-0BBCAA212FF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="State" sheetId="1" r:id="rId1"/>
     <sheet name="District" sheetId="2" r:id="rId2"/>
+    <sheet name="District-old New Name" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">District!$A$1:$C$788</definedName>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1615" uniqueCount="826">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="830">
   <si>
     <t>STATE</t>
   </si>
@@ -2522,6 +2523,18 @@
   </si>
   <si>
     <t>Pratapgarh_up</t>
+  </si>
+  <si>
+    <t>Old Name</t>
+  </si>
+  <si>
+    <t>New Name</t>
+  </si>
+  <si>
+    <t>Harayana</t>
+  </si>
+  <si>
+    <t>Gurgaon</t>
   </si>
 </sst>
 </file>
@@ -3105,7 +3118,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FDBB0FF-B482-4668-8D23-A62BD1FE53B2}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:C788"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3124,7 +3136,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="2" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>21</v>
       </c>
@@ -3133,7 +3145,7 @@
       </c>
       <c r="C2" s="1"/>
     </row>
-    <row r="3" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>21</v>
       </c>
@@ -3142,7 +3154,7 @@
       </c>
       <c r="C3" s="1"/>
     </row>
-    <row r="4" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>21</v>
       </c>
@@ -3151,7 +3163,7 @@
       </c>
       <c r="C4" s="1"/>
     </row>
-    <row r="5" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -3160,7 +3172,7 @@
       </c>
       <c r="C5" s="1"/>
     </row>
-    <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -3169,7 +3181,7 @@
       </c>
       <c r="C6" s="1"/>
     </row>
-    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -3178,7 +3190,7 @@
       </c>
       <c r="C7" s="1"/>
     </row>
-    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
@@ -3187,7 +3199,7 @@
       </c>
       <c r="C8" s="1"/>
     </row>
-    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
@@ -3196,7 +3208,7 @@
       </c>
       <c r="C9" s="1"/>
     </row>
-    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
@@ -3205,7 +3217,7 @@
       </c>
       <c r="C10" s="1"/>
     </row>
-    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
@@ -3214,7 +3226,7 @@
       </c>
       <c r="C11" s="1"/>
     </row>
-    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
@@ -3223,7 +3235,7 @@
       </c>
       <c r="C12" s="1"/>
     </row>
-    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>10</v>
       </c>
@@ -3232,7 +3244,7 @@
       </c>
       <c r="C13" s="1"/>
     </row>
-    <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>10</v>
       </c>
@@ -3241,7 +3253,7 @@
       </c>
       <c r="C14" s="1"/>
     </row>
-    <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>10</v>
       </c>
@@ -3250,7 +3262,7 @@
       </c>
       <c r="C15" s="1"/>
     </row>
-    <row r="16" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>10</v>
       </c>
@@ -3259,7 +3271,7 @@
       </c>
       <c r="C16" s="1"/>
     </row>
-    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>10</v>
       </c>
@@ -3268,7 +3280,7 @@
       </c>
       <c r="C17" s="1"/>
     </row>
-    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>10</v>
       </c>
@@ -3277,7 +3289,7 @@
       </c>
       <c r="C18" s="1"/>
     </row>
-    <row r="19" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>10</v>
       </c>
@@ -3286,7 +3298,7 @@
       </c>
       <c r="C19" s="1"/>
     </row>
-    <row r="20" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>10</v>
       </c>
@@ -3295,7 +3307,7 @@
       </c>
       <c r="C20" s="1"/>
     </row>
-    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>10</v>
       </c>
@@ -3304,7 +3316,7 @@
       </c>
       <c r="C21" s="1"/>
     </row>
-    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>10</v>
       </c>
@@ -3313,7 +3325,7 @@
       </c>
       <c r="C22" s="1"/>
     </row>
-    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>10</v>
       </c>
@@ -3322,7 +3334,7 @@
       </c>
       <c r="C23" s="1"/>
     </row>
-    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>10</v>
       </c>
@@ -3331,7 +3343,7 @@
       </c>
       <c r="C24" s="1"/>
     </row>
-    <row r="25" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>10</v>
       </c>
@@ -3340,7 +3352,7 @@
       </c>
       <c r="C25" s="1"/>
     </row>
-    <row r="26" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>10</v>
       </c>
@@ -3349,7 +3361,7 @@
       </c>
       <c r="C26" s="1"/>
     </row>
-    <row r="27" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>10</v>
       </c>
@@ -3358,7 +3370,7 @@
       </c>
       <c r="C27" s="1"/>
     </row>
-    <row r="28" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>10</v>
       </c>
@@ -3367,7 +3379,7 @@
       </c>
       <c r="C28" s="1"/>
     </row>
-    <row r="29" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>10</v>
       </c>
@@ -3376,7 +3388,7 @@
       </c>
       <c r="C29" s="1"/>
     </row>
-    <row r="30" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>10</v>
       </c>
@@ -3385,7 +3397,7 @@
       </c>
       <c r="C30" s="1"/>
     </row>
-    <row r="31" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>32</v>
       </c>
@@ -3394,7 +3406,7 @@
       </c>
       <c r="C31" s="1"/>
     </row>
-    <row r="32" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>32</v>
       </c>
@@ -3403,7 +3415,7 @@
       </c>
       <c r="C32" s="1"/>
     </row>
-    <row r="33" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>32</v>
       </c>
@@ -3412,7 +3424,7 @@
       </c>
       <c r="C33" s="1"/>
     </row>
-    <row r="34" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>32</v>
       </c>
@@ -3421,7 +3433,7 @@
       </c>
       <c r="C34" s="1"/>
     </row>
-    <row r="35" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>32</v>
       </c>
@@ -3430,7 +3442,7 @@
       </c>
       <c r="C35" s="1"/>
     </row>
-    <row r="36" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>32</v>
       </c>
@@ -3439,7 +3451,7 @@
       </c>
       <c r="C36" s="1"/>
     </row>
-    <row r="37" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>32</v>
       </c>
@@ -3448,7 +3460,7 @@
       </c>
       <c r="C37" s="1"/>
     </row>
-    <row r="38" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>32</v>
       </c>
@@ -3457,7 +3469,7 @@
       </c>
       <c r="C38" s="1"/>
     </row>
-    <row r="39" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3466,7 +3478,7 @@
       </c>
       <c r="C39" s="1"/>
     </row>
-    <row r="40" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>32</v>
       </c>
@@ -3475,7 +3487,7 @@
       </c>
       <c r="C40" s="1"/>
     </row>
-    <row r="41" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>32</v>
       </c>
@@ -3484,7 +3496,7 @@
       </c>
       <c r="C41" s="1"/>
     </row>
-    <row r="42" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>32</v>
       </c>
@@ -3493,7 +3505,7 @@
       </c>
       <c r="C42" s="1"/>
     </row>
-    <row r="43" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>32</v>
       </c>
@@ -3502,7 +3514,7 @@
       </c>
       <c r="C43" s="1"/>
     </row>
-    <row r="44" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>32</v>
       </c>
@@ -3511,7 +3523,7 @@
       </c>
       <c r="C44" s="1"/>
     </row>
-    <row r="45" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>32</v>
       </c>
@@ -3520,7 +3532,7 @@
       </c>
       <c r="C45" s="1"/>
     </row>
-    <row r="46" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>32</v>
       </c>
@@ -3529,7 +3541,7 @@
       </c>
       <c r="C46" s="1"/>
     </row>
-    <row r="47" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>32</v>
       </c>
@@ -3538,7 +3550,7 @@
       </c>
       <c r="C47" s="1"/>
     </row>
-    <row r="48" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>32</v>
       </c>
@@ -3547,7 +3559,7 @@
       </c>
       <c r="C48" s="1"/>
     </row>
-    <row r="49" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>32</v>
       </c>
@@ -3556,7 +3568,7 @@
       </c>
       <c r="C49" s="1"/>
     </row>
-    <row r="50" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>32</v>
       </c>
@@ -3565,7 +3577,7 @@
       </c>
       <c r="C50" s="1"/>
     </row>
-    <row r="51" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>32</v>
       </c>
@@ -3574,7 +3586,7 @@
       </c>
       <c r="C51" s="1"/>
     </row>
-    <row r="52" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>32</v>
       </c>
@@ -3583,7 +3595,7 @@
       </c>
       <c r="C52" s="1"/>
     </row>
-    <row r="53" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>32</v>
       </c>
@@ -3592,7 +3604,7 @@
       </c>
       <c r="C53" s="1"/>
     </row>
-    <row r="54" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>32</v>
       </c>
@@ -3601,7 +3613,7 @@
       </c>
       <c r="C54" s="1"/>
     </row>
-    <row r="55" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>32</v>
       </c>
@@ -3610,7 +3622,7 @@
       </c>
       <c r="C55" s="1"/>
     </row>
-    <row r="56" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>32</v>
       </c>
@@ -3619,7 +3631,7 @@
       </c>
       <c r="C56" s="1"/>
     </row>
-    <row r="57" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>32</v>
       </c>
@@ -3943,7 +3955,7 @@
       </c>
       <c r="C92" s="1"/>
     </row>
-    <row r="93" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>12</v>
       </c>
@@ -3952,7 +3964,7 @@
       </c>
       <c r="C93" s="1"/>
     </row>
-    <row r="94" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>12</v>
       </c>
@@ -3961,7 +3973,7 @@
       </c>
       <c r="C94" s="1"/>
     </row>
-    <row r="95" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>12</v>
       </c>
@@ -3970,7 +3982,7 @@
       </c>
       <c r="C95" s="1"/>
     </row>
-    <row r="96" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>12</v>
       </c>
@@ -3979,7 +3991,7 @@
       </c>
       <c r="C96" s="1"/>
     </row>
-    <row r="97" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>12</v>
       </c>
@@ -3988,7 +4000,7 @@
       </c>
       <c r="C97" s="1"/>
     </row>
-    <row r="98" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>12</v>
       </c>
@@ -3997,7 +4009,7 @@
       </c>
       <c r="C98" s="1"/>
     </row>
-    <row r="99" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>12</v>
       </c>
@@ -4006,7 +4018,7 @@
       </c>
       <c r="C99" s="1"/>
     </row>
-    <row r="100" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>12</v>
       </c>
@@ -4015,7 +4027,7 @@
       </c>
       <c r="C100" s="1"/>
     </row>
-    <row r="101" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>12</v>
       </c>
@@ -4024,7 +4036,7 @@
       </c>
       <c r="C101" s="1"/>
     </row>
-    <row r="102" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>12</v>
       </c>
@@ -4033,7 +4045,7 @@
       </c>
       <c r="C102" s="1"/>
     </row>
-    <row r="103" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>12</v>
       </c>
@@ -4042,7 +4054,7 @@
       </c>
       <c r="C103" s="1"/>
     </row>
-    <row r="104" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>12</v>
       </c>
@@ -4051,7 +4063,7 @@
       </c>
       <c r="C104" s="1"/>
     </row>
-    <row r="105" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>12</v>
       </c>
@@ -4060,7 +4072,7 @@
       </c>
       <c r="C105" s="1"/>
     </row>
-    <row r="106" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>12</v>
       </c>
@@ -4069,7 +4081,7 @@
       </c>
       <c r="C106" s="1"/>
     </row>
-    <row r="107" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>12</v>
       </c>
@@ -4078,7 +4090,7 @@
       </c>
       <c r="C107" s="1"/>
     </row>
-    <row r="108" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>12</v>
       </c>
@@ -4087,7 +4099,7 @@
       </c>
       <c r="C108" s="1"/>
     </row>
-    <row r="109" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>12</v>
       </c>
@@ -4096,7 +4108,7 @@
       </c>
       <c r="C109" s="1"/>
     </row>
-    <row r="110" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>12</v>
       </c>
@@ -4105,7 +4117,7 @@
       </c>
       <c r="C110" s="1"/>
     </row>
-    <row r="111" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>12</v>
       </c>
@@ -4114,7 +4126,7 @@
       </c>
       <c r="C111" s="1"/>
     </row>
-    <row r="112" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>12</v>
       </c>
@@ -4123,7 +4135,7 @@
       </c>
       <c r="C112" s="1"/>
     </row>
-    <row r="113" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>12</v>
       </c>
@@ -4132,7 +4144,7 @@
       </c>
       <c r="C113" s="1"/>
     </row>
-    <row r="114" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>12</v>
       </c>
@@ -4141,7 +4153,7 @@
       </c>
       <c r="C114" s="1"/>
     </row>
-    <row r="115" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>12</v>
       </c>
@@ -4150,7 +4162,7 @@
       </c>
       <c r="C115" s="1"/>
     </row>
-    <row r="116" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>12</v>
       </c>
@@ -4159,7 +4171,7 @@
       </c>
       <c r="C116" s="1"/>
     </row>
-    <row r="117" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>12</v>
       </c>
@@ -4168,7 +4180,7 @@
       </c>
       <c r="C117" s="1"/>
     </row>
-    <row r="118" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>12</v>
       </c>
@@ -4177,7 +4189,7 @@
       </c>
       <c r="C118" s="1"/>
     </row>
-    <row r="119" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>12</v>
       </c>
@@ -4186,7 +4198,7 @@
       </c>
       <c r="C119" s="1"/>
     </row>
-    <row r="120" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>12</v>
       </c>
@@ -4195,7 +4207,7 @@
       </c>
       <c r="C120" s="1"/>
     </row>
-    <row r="121" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>12</v>
       </c>
@@ -4204,7 +4216,7 @@
       </c>
       <c r="C121" s="1"/>
     </row>
-    <row r="122" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>12</v>
       </c>
@@ -4213,7 +4225,7 @@
       </c>
       <c r="C122" s="1"/>
     </row>
-    <row r="123" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>12</v>
       </c>
@@ -4222,7 +4234,7 @@
       </c>
       <c r="C123" s="1"/>
     </row>
-    <row r="124" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>12</v>
       </c>
@@ -4231,7 +4243,7 @@
       </c>
       <c r="C124" s="1"/>
     </row>
-    <row r="125" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>12</v>
       </c>
@@ -4240,7 +4252,7 @@
       </c>
       <c r="C125" s="1"/>
     </row>
-    <row r="126" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>12</v>
       </c>
@@ -4249,7 +4261,7 @@
       </c>
       <c r="C126" s="1"/>
     </row>
-    <row r="127" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>12</v>
       </c>
@@ -4258,7 +4270,7 @@
       </c>
       <c r="C127" s="1"/>
     </row>
-    <row r="128" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>12</v>
       </c>
@@ -4267,7 +4279,7 @@
       </c>
       <c r="C128" s="1"/>
     </row>
-    <row r="129" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>12</v>
       </c>
@@ -4276,7 +4288,7 @@
       </c>
       <c r="C129" s="1"/>
     </row>
-    <row r="130" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>12</v>
       </c>
@@ -4285,7 +4297,7 @@
       </c>
       <c r="C130" s="1"/>
     </row>
-    <row r="131" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>23</v>
       </c>
@@ -4294,7 +4306,7 @@
       </c>
       <c r="C131" s="1"/>
     </row>
-    <row r="132" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>167</v>
       </c>
@@ -4303,7 +4315,7 @@
       </c>
       <c r="C132" s="1"/>
     </row>
-    <row r="133" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>167</v>
       </c>
@@ -4312,7 +4324,7 @@
       </c>
       <c r="C133" s="1"/>
     </row>
-    <row r="134" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>167</v>
       </c>
@@ -4321,7 +4333,7 @@
       </c>
       <c r="C134" s="1"/>
     </row>
-    <row r="135" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>167</v>
       </c>
@@ -4330,7 +4342,7 @@
       </c>
       <c r="C135" s="1"/>
     </row>
-    <row r="136" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>167</v>
       </c>
@@ -4339,7 +4351,7 @@
       </c>
       <c r="C136" s="1"/>
     </row>
-    <row r="137" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>167</v>
       </c>
@@ -4348,7 +4360,7 @@
       </c>
       <c r="C137" s="1"/>
     </row>
-    <row r="138" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>167</v>
       </c>
@@ -4357,7 +4369,7 @@
       </c>
       <c r="C138" s="1"/>
     </row>
-    <row r="139" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>167</v>
       </c>
@@ -4366,7 +4378,7 @@
       </c>
       <c r="C139" s="1"/>
     </row>
-    <row r="140" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>167</v>
       </c>
@@ -4375,7 +4387,7 @@
       </c>
       <c r="C140" s="1"/>
     </row>
-    <row r="141" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>167</v>
       </c>
@@ -4384,7 +4396,7 @@
       </c>
       <c r="C141" s="1"/>
     </row>
-    <row r="142" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>167</v>
       </c>
@@ -4393,7 +4405,7 @@
       </c>
       <c r="C142" s="1"/>
     </row>
-    <row r="143" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>167</v>
       </c>
@@ -4402,7 +4414,7 @@
       </c>
       <c r="C143" s="1"/>
     </row>
-    <row r="144" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>167</v>
       </c>
@@ -4411,7 +4423,7 @@
       </c>
       <c r="C144" s="1"/>
     </row>
-    <row r="145" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>167</v>
       </c>
@@ -4420,7 +4432,7 @@
       </c>
       <c r="C145" s="1"/>
     </row>
-    <row r="146" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>167</v>
       </c>
@@ -4429,7 +4441,7 @@
       </c>
       <c r="C146" s="1"/>
     </row>
-    <row r="147" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>167</v>
       </c>
@@ -4438,7 +4450,7 @@
       </c>
       <c r="C147" s="1"/>
     </row>
-    <row r="148" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>167</v>
       </c>
@@ -4447,7 +4459,7 @@
       </c>
       <c r="C148" s="1"/>
     </row>
-    <row r="149" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>167</v>
       </c>
@@ -4456,7 +4468,7 @@
       </c>
       <c r="C149" s="1"/>
     </row>
-    <row r="150" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>167</v>
       </c>
@@ -4465,7 +4477,7 @@
       </c>
       <c r="C150" s="1"/>
     </row>
-    <row r="151" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>167</v>
       </c>
@@ -4474,7 +4486,7 @@
       </c>
       <c r="C151" s="1"/>
     </row>
-    <row r="152" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>167</v>
       </c>
@@ -4483,7 +4495,7 @@
       </c>
       <c r="C152" s="1"/>
     </row>
-    <row r="153" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>167</v>
       </c>
@@ -4492,7 +4504,7 @@
       </c>
       <c r="C153" s="1"/>
     </row>
-    <row r="154" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>167</v>
       </c>
@@ -4501,7 +4513,7 @@
       </c>
       <c r="C154" s="1"/>
     </row>
-    <row r="155" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>167</v>
       </c>
@@ -4510,7 +4522,7 @@
       </c>
       <c r="C155" s="1"/>
     </row>
-    <row r="156" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>167</v>
       </c>
@@ -4519,7 +4531,7 @@
       </c>
       <c r="C156" s="1"/>
     </row>
-    <row r="157" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>167</v>
       </c>
@@ -4528,7 +4540,7 @@
       </c>
       <c r="C157" s="1"/>
     </row>
-    <row r="158" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
         <v>167</v>
       </c>
@@ -4537,7 +4549,7 @@
       </c>
       <c r="C158" s="1"/>
     </row>
-    <row r="159" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
         <v>167</v>
       </c>
@@ -4546,7 +4558,7 @@
       </c>
       <c r="C159" s="1"/>
     </row>
-    <row r="160" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
         <v>167</v>
       </c>
@@ -4555,7 +4567,7 @@
       </c>
       <c r="C160" s="1"/>
     </row>
-    <row r="161" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
         <v>167</v>
       </c>
@@ -4564,7 +4576,7 @@
       </c>
       <c r="C161" s="1"/>
     </row>
-    <row r="162" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
         <v>167</v>
       </c>
@@ -4573,7 +4585,7 @@
       </c>
       <c r="C162" s="1"/>
     </row>
-    <row r="163" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
         <v>167</v>
       </c>
@@ -4582,7 +4594,7 @@
       </c>
       <c r="C163" s="1"/>
     </row>
-    <row r="164" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
         <v>167</v>
       </c>
@@ -4591,7 +4603,7 @@
       </c>
       <c r="C164" s="1"/>
     </row>
-    <row r="165" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
         <v>35</v>
       </c>
@@ -4600,7 +4612,7 @@
       </c>
       <c r="C165" s="1"/>
     </row>
-    <row r="166" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
         <v>33</v>
       </c>
@@ -4609,7 +4621,7 @@
       </c>
       <c r="C166" s="1"/>
     </row>
-    <row r="167" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
         <v>33</v>
       </c>
@@ -4618,7 +4630,7 @@
       </c>
       <c r="C167" s="1"/>
     </row>
-    <row r="168" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
         <v>15</v>
       </c>
@@ -4627,7 +4639,7 @@
       </c>
       <c r="C168" s="1"/>
     </row>
-    <row r="169" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
         <v>15</v>
       </c>
@@ -4636,7 +4648,7 @@
       </c>
       <c r="C169" s="1"/>
     </row>
-    <row r="170" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
         <v>15</v>
       </c>
@@ -4645,7 +4657,7 @@
       </c>
       <c r="C170" s="1"/>
     </row>
-    <row r="171" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
         <v>15</v>
       </c>
@@ -4654,7 +4666,7 @@
       </c>
       <c r="C171" s="1"/>
     </row>
-    <row r="172" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
         <v>15</v>
       </c>
@@ -4663,7 +4675,7 @@
       </c>
       <c r="C172" s="1"/>
     </row>
-    <row r="173" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
         <v>15</v>
       </c>
@@ -4672,7 +4684,7 @@
       </c>
       <c r="C173" s="1"/>
     </row>
-    <row r="174" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
         <v>15</v>
       </c>
@@ -4681,7 +4693,7 @@
       </c>
       <c r="C174" s="1"/>
     </row>
-    <row r="175" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
         <v>15</v>
       </c>
@@ -4690,7 +4702,7 @@
       </c>
       <c r="C175" s="1"/>
     </row>
-    <row r="176" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
         <v>15</v>
       </c>
@@ -4699,7 +4711,7 @@
       </c>
       <c r="C176" s="1"/>
     </row>
-    <row r="177" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
         <v>15</v>
       </c>
@@ -4708,7 +4720,7 @@
       </c>
       <c r="C177" s="1"/>
     </row>
-    <row r="178" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
         <v>15</v>
       </c>
@@ -4717,7 +4729,7 @@
       </c>
       <c r="C178" s="1"/>
     </row>
-    <row r="179" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
         <v>28</v>
       </c>
@@ -4726,7 +4738,7 @@
       </c>
       <c r="C179" s="1"/>
     </row>
-    <row r="180" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
         <v>28</v>
       </c>
@@ -4735,7 +4747,7 @@
       </c>
       <c r="C180" s="1"/>
     </row>
-    <row r="181" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
         <v>2</v>
       </c>
@@ -4744,7 +4756,7 @@
       </c>
       <c r="C181" s="1"/>
     </row>
-    <row r="182" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
         <v>2</v>
       </c>
@@ -4753,7 +4765,7 @@
       </c>
       <c r="C182" s="1"/>
     </row>
-    <row r="183" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
         <v>2</v>
       </c>
@@ -4762,7 +4774,7 @@
       </c>
       <c r="C183" s="1"/>
     </row>
-    <row r="184" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
         <v>2</v>
       </c>
@@ -4771,7 +4783,7 @@
       </c>
       <c r="C184" s="1"/>
     </row>
-    <row r="185" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
         <v>2</v>
       </c>
@@ -4780,7 +4792,7 @@
       </c>
       <c r="C185" s="1"/>
     </row>
-    <row r="186" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
         <v>2</v>
       </c>
@@ -4789,7 +4801,7 @@
       </c>
       <c r="C186" s="1"/>
     </row>
-    <row r="187" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
         <v>2</v>
       </c>
@@ -4798,7 +4810,7 @@
       </c>
       <c r="C187" s="1"/>
     </row>
-    <row r="188" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
         <v>2</v>
       </c>
@@ -4807,7 +4819,7 @@
       </c>
       <c r="C188" s="1"/>
     </row>
-    <row r="189" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
         <v>2</v>
       </c>
@@ -4816,7 +4828,7 @@
       </c>
       <c r="C189" s="1"/>
     </row>
-    <row r="190" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
         <v>2</v>
       </c>
@@ -4825,7 +4837,7 @@
       </c>
       <c r="C190" s="1"/>
     </row>
-    <row r="191" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
         <v>2</v>
       </c>
@@ -4834,7 +4846,7 @@
       </c>
       <c r="C191" s="1"/>
     </row>
-    <row r="192" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
         <v>2</v>
       </c>
@@ -4843,7 +4855,7 @@
       </c>
       <c r="C192" s="1"/>
     </row>
-    <row r="193" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
         <v>2</v>
       </c>
@@ -4852,7 +4864,7 @@
       </c>
       <c r="C193" s="1"/>
     </row>
-    <row r="194" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
         <v>2</v>
       </c>
@@ -4861,7 +4873,7 @@
       </c>
       <c r="C194" s="1"/>
     </row>
-    <row r="195" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
         <v>2</v>
       </c>
@@ -4870,7 +4882,7 @@
       </c>
       <c r="C195" s="1"/>
     </row>
-    <row r="196" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
         <v>2</v>
       </c>
@@ -4879,7 +4891,7 @@
       </c>
       <c r="C196" s="1"/>
     </row>
-    <row r="197" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
         <v>2</v>
       </c>
@@ -4888,7 +4900,7 @@
       </c>
       <c r="C197" s="1"/>
     </row>
-    <row r="198" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
         <v>2</v>
       </c>
@@ -4897,7 +4909,7 @@
       </c>
       <c r="C198" s="1"/>
     </row>
-    <row r="199" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
         <v>2</v>
       </c>
@@ -4906,7 +4918,7 @@
       </c>
       <c r="C199" s="1"/>
     </row>
-    <row r="200" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
         <v>2</v>
       </c>
@@ -4915,7 +4927,7 @@
       </c>
       <c r="C200" s="1"/>
     </row>
-    <row r="201" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
         <v>2</v>
       </c>
@@ -4924,7 +4936,7 @@
       </c>
       <c r="C201" s="1"/>
     </row>
-    <row r="202" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
         <v>2</v>
       </c>
@@ -4933,7 +4945,7 @@
       </c>
       <c r="C202" s="1"/>
     </row>
-    <row r="203" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
         <v>2</v>
       </c>
@@ -4942,7 +4954,7 @@
       </c>
       <c r="C203" s="1"/>
     </row>
-    <row r="204" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
         <v>2</v>
       </c>
@@ -4951,7 +4963,7 @@
       </c>
       <c r="C204" s="1"/>
     </row>
-    <row r="205" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
         <v>2</v>
       </c>
@@ -4960,7 +4972,7 @@
       </c>
       <c r="C205" s="1"/>
     </row>
-    <row r="206" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
         <v>2</v>
       </c>
@@ -4969,7 +4981,7 @@
       </c>
       <c r="C206" s="1"/>
     </row>
-    <row r="207" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
         <v>2</v>
       </c>
@@ -4978,7 +4990,7 @@
       </c>
       <c r="C207" s="1"/>
     </row>
-    <row r="208" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
         <v>2</v>
       </c>
@@ -4987,7 +4999,7 @@
       </c>
       <c r="C208" s="1"/>
     </row>
-    <row r="209" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
         <v>2</v>
       </c>
@@ -4996,7 +5008,7 @@
       </c>
       <c r="C209" s="1"/>
     </row>
-    <row r="210" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
         <v>2</v>
       </c>
@@ -5005,7 +5017,7 @@
       </c>
       <c r="C210" s="1"/>
     </row>
-    <row r="211" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
         <v>2</v>
       </c>
@@ -5014,7 +5026,7 @@
       </c>
       <c r="C211" s="1"/>
     </row>
-    <row r="212" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
         <v>2</v>
       </c>
@@ -5023,7 +5035,7 @@
       </c>
       <c r="C212" s="1"/>
     </row>
-    <row r="213" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
         <v>2</v>
       </c>
@@ -5032,7 +5044,7 @@
       </c>
       <c r="C213" s="1"/>
     </row>
-    <row r="214" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
         <v>9</v>
       </c>
@@ -5041,7 +5053,7 @@
       </c>
       <c r="C214" s="1"/>
     </row>
-    <row r="215" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
         <v>9</v>
       </c>
@@ -5050,7 +5062,7 @@
       </c>
       <c r="C215" s="1"/>
     </row>
-    <row r="216" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
         <v>9</v>
       </c>
@@ -5059,7 +5071,7 @@
       </c>
       <c r="C216" s="1"/>
     </row>
-    <row r="217" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
         <v>9</v>
       </c>
@@ -5068,7 +5080,7 @@
       </c>
       <c r="C217" s="1"/>
     </row>
-    <row r="218" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
         <v>9</v>
       </c>
@@ -5077,7 +5089,7 @@
       </c>
       <c r="C218" s="1"/>
     </row>
-    <row r="219" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
         <v>9</v>
       </c>
@@ -5086,7 +5098,7 @@
       </c>
       <c r="C219" s="1"/>
     </row>
-    <row r="220" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
         <v>9</v>
       </c>
@@ -5095,7 +5107,7 @@
       </c>
       <c r="C220" s="1"/>
     </row>
-    <row r="221" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
         <v>9</v>
       </c>
@@ -5104,7 +5116,7 @@
       </c>
       <c r="C221" s="1"/>
     </row>
-    <row r="222" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
         <v>9</v>
       </c>
@@ -5113,7 +5125,7 @@
       </c>
       <c r="C222" s="1"/>
     </row>
-    <row r="223" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
         <v>9</v>
       </c>
@@ -5122,7 +5134,7 @@
       </c>
       <c r="C223" s="1"/>
     </row>
-    <row r="224" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
         <v>9</v>
       </c>
@@ -5131,7 +5143,7 @@
       </c>
       <c r="C224" s="1"/>
     </row>
-    <row r="225" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
         <v>9</v>
       </c>
@@ -5140,7 +5152,7 @@
       </c>
       <c r="C225" s="1"/>
     </row>
-    <row r="226" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
         <v>9</v>
       </c>
@@ -5149,7 +5161,7 @@
       </c>
       <c r="C226" s="1"/>
     </row>
-    <row r="227" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
         <v>9</v>
       </c>
@@ -5158,7 +5170,7 @@
       </c>
       <c r="C227" s="1"/>
     </row>
-    <row r="228" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
         <v>9</v>
       </c>
@@ -5167,7 +5179,7 @@
       </c>
       <c r="C228" s="1"/>
     </row>
-    <row r="229" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
         <v>9</v>
       </c>
@@ -5176,7 +5188,7 @@
       </c>
       <c r="C229" s="1"/>
     </row>
-    <row r="230" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
         <v>9</v>
       </c>
@@ -5185,7 +5197,7 @@
       </c>
       <c r="C230" s="1"/>
     </row>
-    <row r="231" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
         <v>9</v>
       </c>
@@ -5194,7 +5206,7 @@
       </c>
       <c r="C231" s="1"/>
     </row>
-    <row r="232" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
         <v>9</v>
       </c>
@@ -5203,7 +5215,7 @@
       </c>
       <c r="C232" s="1"/>
     </row>
-    <row r="233" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
         <v>9</v>
       </c>
@@ -5212,7 +5224,7 @@
       </c>
       <c r="C233" s="1"/>
     </row>
-    <row r="234" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
         <v>9</v>
       </c>
@@ -5221,7 +5233,7 @@
       </c>
       <c r="C234" s="1"/>
     </row>
-    <row r="235" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
         <v>9</v>
       </c>
@@ -5230,7 +5242,7 @@
       </c>
       <c r="C235" s="1"/>
     </row>
-    <row r="236" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
         <v>7</v>
       </c>
@@ -5239,7 +5251,7 @@
       </c>
       <c r="C236" s="1"/>
     </row>
-    <row r="237" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
         <v>7</v>
       </c>
@@ -5248,7 +5260,7 @@
       </c>
       <c r="C237" s="1"/>
     </row>
-    <row r="238" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
         <v>7</v>
       </c>
@@ -5257,7 +5269,7 @@
       </c>
       <c r="C238" s="1"/>
     </row>
-    <row r="239" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
         <v>7</v>
       </c>
@@ -5266,7 +5278,7 @@
       </c>
       <c r="C239" s="1"/>
     </row>
-    <row r="240" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
         <v>7</v>
       </c>
@@ -5275,7 +5287,7 @@
       </c>
       <c r="C240" s="1"/>
     </row>
-    <row r="241" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
         <v>7</v>
       </c>
@@ -5284,7 +5296,7 @@
       </c>
       <c r="C241" s="1"/>
     </row>
-    <row r="242" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
         <v>7</v>
       </c>
@@ -5293,7 +5305,7 @@
       </c>
       <c r="C242" s="1"/>
     </row>
-    <row r="243" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
         <v>7</v>
       </c>
@@ -5302,7 +5314,7 @@
       </c>
       <c r="C243" s="1"/>
     </row>
-    <row r="244" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
         <v>7</v>
       </c>
@@ -5311,7 +5323,7 @@
       </c>
       <c r="C244" s="1"/>
     </row>
-    <row r="245" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
         <v>7</v>
       </c>
@@ -5320,7 +5332,7 @@
       </c>
       <c r="C245" s="1"/>
     </row>
-    <row r="246" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
         <v>7</v>
       </c>
@@ -5329,7 +5341,7 @@
       </c>
       <c r="C246" s="1"/>
     </row>
-    <row r="247" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
         <v>7</v>
       </c>
@@ -5338,7 +5350,7 @@
       </c>
       <c r="C247" s="1"/>
     </row>
-    <row r="248" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
         <v>11</v>
       </c>
@@ -5347,7 +5359,7 @@
       </c>
       <c r="C248" s="1"/>
     </row>
-    <row r="249" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
         <v>11</v>
       </c>
@@ -5356,7 +5368,7 @@
       </c>
       <c r="C249" s="1"/>
     </row>
-    <row r="250" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
         <v>11</v>
       </c>
@@ -5365,7 +5377,7 @@
       </c>
       <c r="C250" s="1"/>
     </row>
-    <row r="251" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
         <v>11</v>
       </c>
@@ -5374,7 +5386,7 @@
       </c>
       <c r="C251" s="1"/>
     </row>
-    <row r="252" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
         <v>11</v>
       </c>
@@ -5383,7 +5395,7 @@
       </c>
       <c r="C252" s="1"/>
     </row>
-    <row r="253" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
         <v>11</v>
       </c>
@@ -5392,7 +5404,7 @@
       </c>
       <c r="C253" s="1"/>
     </row>
-    <row r="254" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
         <v>11</v>
       </c>
@@ -5401,7 +5413,7 @@
       </c>
       <c r="C254" s="1"/>
     </row>
-    <row r="255" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
         <v>11</v>
       </c>
@@ -5410,7 +5422,7 @@
       </c>
       <c r="C255" s="1"/>
     </row>
-    <row r="256" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
         <v>11</v>
       </c>
@@ -5419,7 +5431,7 @@
       </c>
       <c r="C256" s="1"/>
     </row>
-    <row r="257" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
         <v>11</v>
       </c>
@@ -5428,7 +5440,7 @@
       </c>
       <c r="C257" s="1"/>
     </row>
-    <row r="258" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
         <v>11</v>
       </c>
@@ -5437,7 +5449,7 @@
       </c>
       <c r="C258" s="1"/>
     </row>
-    <row r="259" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
         <v>11</v>
       </c>
@@ -5446,7 +5458,7 @@
       </c>
       <c r="C259" s="1"/>
     </row>
-    <row r="260" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
         <v>11</v>
       </c>
@@ -5455,7 +5467,7 @@
       </c>
       <c r="C260" s="1"/>
     </row>
-    <row r="261" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
         <v>11</v>
       </c>
@@ -5464,7 +5476,7 @@
       </c>
       <c r="C261" s="1"/>
     </row>
-    <row r="262" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
         <v>11</v>
       </c>
@@ -5473,7 +5485,7 @@
       </c>
       <c r="C262" s="1"/>
     </row>
-    <row r="263" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
         <v>11</v>
       </c>
@@ -5482,7 +5494,7 @@
       </c>
       <c r="C263" s="1"/>
     </row>
-    <row r="264" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
         <v>11</v>
       </c>
@@ -5491,7 +5503,7 @@
       </c>
       <c r="C264" s="1"/>
     </row>
-    <row r="265" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
         <v>11</v>
       </c>
@@ -5500,7 +5512,7 @@
       </c>
       <c r="C265" s="1"/>
     </row>
-    <row r="266" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
         <v>11</v>
       </c>
@@ -5509,7 +5521,7 @@
       </c>
       <c r="C266" s="1"/>
     </row>
-    <row r="267" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
         <v>11</v>
       </c>
@@ -5518,7 +5530,7 @@
       </c>
       <c r="C267" s="1"/>
     </row>
-    <row r="268" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
         <v>19</v>
       </c>
@@ -5527,7 +5539,7 @@
       </c>
       <c r="C268" s="1"/>
     </row>
-    <row r="269" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
         <v>19</v>
       </c>
@@ -5536,7 +5548,7 @@
       </c>
       <c r="C269" s="1"/>
     </row>
-    <row r="270" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
         <v>19</v>
       </c>
@@ -5545,7 +5557,7 @@
       </c>
       <c r="C270" s="1"/>
     </row>
-    <row r="271" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
         <v>19</v>
       </c>
@@ -5554,7 +5566,7 @@
       </c>
       <c r="C271" s="1"/>
     </row>
-    <row r="272" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
         <v>19</v>
       </c>
@@ -5563,7 +5575,7 @@
       </c>
       <c r="C272" s="1"/>
     </row>
-    <row r="273" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
         <v>19</v>
       </c>
@@ -5572,7 +5584,7 @@
       </c>
       <c r="C273" s="1"/>
     </row>
-    <row r="274" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
         <v>19</v>
       </c>
@@ -5581,7 +5593,7 @@
       </c>
       <c r="C274" s="1"/>
     </row>
-    <row r="275" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
         <v>19</v>
       </c>
@@ -5590,7 +5602,7 @@
       </c>
       <c r="C275" s="1"/>
     </row>
-    <row r="276" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
         <v>19</v>
       </c>
@@ -5599,7 +5611,7 @@
       </c>
       <c r="C276" s="1"/>
     </row>
-    <row r="277" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
         <v>19</v>
       </c>
@@ -5608,7 +5620,7 @@
       </c>
       <c r="C277" s="1"/>
     </row>
-    <row r="278" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
         <v>19</v>
       </c>
@@ -5617,7 +5629,7 @@
       </c>
       <c r="C278" s="1"/>
     </row>
-    <row r="279" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
         <v>19</v>
       </c>
@@ -5626,7 +5638,7 @@
       </c>
       <c r="C279" s="1"/>
     </row>
-    <row r="280" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
         <v>19</v>
       </c>
@@ -5635,7 +5647,7 @@
       </c>
       <c r="C280" s="1"/>
     </row>
-    <row r="281" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
         <v>19</v>
       </c>
@@ -5644,7 +5656,7 @@
       </c>
       <c r="C281" s="1"/>
     </row>
-    <row r="282" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
         <v>19</v>
       </c>
@@ -5653,7 +5665,7 @@
       </c>
       <c r="C282" s="1"/>
     </row>
-    <row r="283" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
         <v>19</v>
       </c>
@@ -5662,7 +5674,7 @@
       </c>
       <c r="C283" s="1"/>
     </row>
-    <row r="284" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
         <v>19</v>
       </c>
@@ -5671,7 +5683,7 @@
       </c>
       <c r="C284" s="1"/>
     </row>
-    <row r="285" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
         <v>19</v>
       </c>
@@ -5680,7 +5692,7 @@
       </c>
       <c r="C285" s="1"/>
     </row>
-    <row r="286" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
         <v>19</v>
       </c>
@@ -5689,7 +5701,7 @@
       </c>
       <c r="C286" s="1"/>
     </row>
-    <row r="287" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
         <v>19</v>
       </c>
@@ -5698,7 +5710,7 @@
       </c>
       <c r="C287" s="1"/>
     </row>
-    <row r="288" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
         <v>19</v>
       </c>
@@ -5707,7 +5719,7 @@
       </c>
       <c r="C288" s="1"/>
     </row>
-    <row r="289" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
         <v>19</v>
       </c>
@@ -5716,7 +5728,7 @@
       </c>
       <c r="C289" s="1"/>
     </row>
-    <row r="290" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
         <v>19</v>
       </c>
@@ -5725,7 +5737,7 @@
       </c>
       <c r="C290" s="1"/>
     </row>
-    <row r="291" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
         <v>19</v>
       </c>
@@ -5734,7 +5746,7 @@
       </c>
       <c r="C291" s="1"/>
     </row>
-    <row r="292" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
         <v>3</v>
       </c>
@@ -5743,7 +5755,7 @@
       </c>
       <c r="C292" s="1"/>
     </row>
-    <row r="293" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
         <v>3</v>
       </c>
@@ -5752,7 +5764,7 @@
       </c>
       <c r="C293" s="1"/>
     </row>
-    <row r="294" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
         <v>3</v>
       </c>
@@ -5761,7 +5773,7 @@
       </c>
       <c r="C294" s="1"/>
     </row>
-    <row r="295" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
         <v>3</v>
       </c>
@@ -5770,7 +5782,7 @@
       </c>
       <c r="C295" s="1"/>
     </row>
-    <row r="296" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
         <v>3</v>
       </c>
@@ -5779,7 +5791,7 @@
       </c>
       <c r="C296" s="1"/>
     </row>
-    <row r="297" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
         <v>3</v>
       </c>
@@ -5788,7 +5800,7 @@
       </c>
       <c r="C297" s="1"/>
     </row>
-    <row r="298" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
         <v>3</v>
       </c>
@@ -5797,7 +5809,7 @@
       </c>
       <c r="C298" s="1"/>
     </row>
-    <row r="299" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
         <v>3</v>
       </c>
@@ -5806,7 +5818,7 @@
       </c>
       <c r="C299" s="1"/>
     </row>
-    <row r="300" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
         <v>3</v>
       </c>
@@ -5815,7 +5827,7 @@
       </c>
       <c r="C300" s="1"/>
     </row>
-    <row r="301" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
         <v>3</v>
       </c>
@@ -5824,7 +5836,7 @@
       </c>
       <c r="C301" s="1"/>
     </row>
-    <row r="302" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
         <v>3</v>
       </c>
@@ -5833,7 +5845,7 @@
       </c>
       <c r="C302" s="1"/>
     </row>
-    <row r="303" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
         <v>3</v>
       </c>
@@ -5842,7 +5854,7 @@
       </c>
       <c r="C303" s="1"/>
     </row>
-    <row r="304" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="s">
         <v>3</v>
       </c>
@@ -5851,7 +5863,7 @@
       </c>
       <c r="C304" s="1"/>
     </row>
-    <row r="305" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="s">
         <v>3</v>
       </c>
@@ -5860,7 +5872,7 @@
       </c>
       <c r="C305" s="1"/>
     </row>
-    <row r="306" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="s">
         <v>3</v>
       </c>
@@ -5869,7 +5881,7 @@
       </c>
       <c r="C306" s="1"/>
     </row>
-    <row r="307" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
         <v>3</v>
       </c>
@@ -5878,7 +5890,7 @@
       </c>
       <c r="C307" s="1"/>
     </row>
-    <row r="308" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A308" s="1" t="s">
         <v>3</v>
       </c>
@@ -5887,7 +5899,7 @@
       </c>
       <c r="C308" s="1"/>
     </row>
-    <row r="309" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="s">
         <v>3</v>
       </c>
@@ -5896,7 +5908,7 @@
       </c>
       <c r="C309" s="1"/>
     </row>
-    <row r="310" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="s">
         <v>3</v>
       </c>
@@ -5905,7 +5917,7 @@
       </c>
       <c r="C310" s="1"/>
     </row>
-    <row r="311" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
         <v>3</v>
       </c>
@@ -5914,7 +5926,7 @@
       </c>
       <c r="C311" s="1"/>
     </row>
-    <row r="312" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
         <v>3</v>
       </c>
@@ -5923,7 +5935,7 @@
       </c>
       <c r="C312" s="1"/>
     </row>
-    <row r="313" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
         <v>3</v>
       </c>
@@ -5932,7 +5944,7 @@
       </c>
       <c r="C313" s="1"/>
     </row>
-    <row r="314" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="s">
         <v>3</v>
       </c>
@@ -5941,7 +5953,7 @@
       </c>
       <c r="C314" s="1"/>
     </row>
-    <row r="315" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A315" s="1" t="s">
         <v>3</v>
       </c>
@@ -5950,7 +5962,7 @@
       </c>
       <c r="C315" s="1"/>
     </row>
-    <row r="316" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
         <v>3</v>
       </c>
@@ -5959,7 +5971,7 @@
       </c>
       <c r="C316" s="1"/>
     </row>
-    <row r="317" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
         <v>3</v>
       </c>
@@ -5968,7 +5980,7 @@
       </c>
       <c r="C317" s="1"/>
     </row>
-    <row r="318" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
         <v>3</v>
       </c>
@@ -5977,7 +5989,7 @@
       </c>
       <c r="C318" s="1"/>
     </row>
-    <row r="319" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
         <v>3</v>
       </c>
@@ -5986,7 +5998,7 @@
       </c>
       <c r="C319" s="1"/>
     </row>
-    <row r="320" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
         <v>3</v>
       </c>
@@ -5995,7 +6007,7 @@
       </c>
       <c r="C320" s="1"/>
     </row>
-    <row r="321" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
         <v>3</v>
       </c>
@@ -6004,7 +6016,7 @@
       </c>
       <c r="C321" s="1"/>
     </row>
-    <row r="322" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
         <v>3</v>
       </c>
@@ -6013,7 +6025,7 @@
       </c>
       <c r="C322" s="1"/>
     </row>
-    <row r="323" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A323" s="1" t="s">
         <v>16</v>
       </c>
@@ -6022,7 +6034,7 @@
       </c>
       <c r="C323" s="1"/>
     </row>
-    <row r="324" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A324" s="1" t="s">
         <v>16</v>
       </c>
@@ -6031,7 +6043,7 @@
       </c>
       <c r="C324" s="1"/>
     </row>
-    <row r="325" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="s">
         <v>16</v>
       </c>
@@ -6040,7 +6052,7 @@
       </c>
       <c r="C325" s="1"/>
     </row>
-    <row r="326" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="s">
         <v>16</v>
       </c>
@@ -6049,7 +6061,7 @@
       </c>
       <c r="C326" s="1"/>
     </row>
-    <row r="327" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
         <v>16</v>
       </c>
@@ -6058,7 +6070,7 @@
       </c>
       <c r="C327" s="1"/>
     </row>
-    <row r="328" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
         <v>16</v>
       </c>
@@ -6067,7 +6079,7 @@
       </c>
       <c r="C328" s="1"/>
     </row>
-    <row r="329" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
         <v>16</v>
       </c>
@@ -6076,7 +6088,7 @@
       </c>
       <c r="C329" s="1"/>
     </row>
-    <row r="330" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
         <v>16</v>
       </c>
@@ -6085,7 +6097,7 @@
       </c>
       <c r="C330" s="1"/>
     </row>
-    <row r="331" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
         <v>16</v>
       </c>
@@ -6094,7 +6106,7 @@
       </c>
       <c r="C331" s="1"/>
     </row>
-    <row r="332" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
         <v>16</v>
       </c>
@@ -6103,7 +6115,7 @@
       </c>
       <c r="C332" s="1"/>
     </row>
-    <row r="333" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
         <v>16</v>
       </c>
@@ -6112,7 +6124,7 @@
       </c>
       <c r="C333" s="1"/>
     </row>
-    <row r="334" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A334" s="1" t="s">
         <v>16</v>
       </c>
@@ -6121,7 +6133,7 @@
       </c>
       <c r="C334" s="1"/>
     </row>
-    <row r="335" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="s">
         <v>16</v>
       </c>
@@ -6130,7 +6142,7 @@
       </c>
       <c r="C335" s="1"/>
     </row>
-    <row r="336" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="s">
         <v>16</v>
       </c>
@@ -6139,7 +6151,7 @@
       </c>
       <c r="C336" s="1"/>
     </row>
-    <row r="337" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
         <v>36</v>
       </c>
@@ -6148,7 +6160,7 @@
       </c>
       <c r="C337" s="1"/>
     </row>
-    <row r="338" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
         <v>36</v>
       </c>
@@ -6157,7 +6169,7 @@
       </c>
       <c r="C338" s="1"/>
     </row>
-    <row r="339" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
         <v>25</v>
       </c>
@@ -6166,7 +6178,7 @@
       </c>
       <c r="C339" s="1"/>
     </row>
-    <row r="340" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A340" s="1" t="s">
         <v>14</v>
       </c>
@@ -6175,7 +6187,7 @@
       </c>
       <c r="C340" s="1"/>
     </row>
-    <row r="341" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A341" s="1" t="s">
         <v>14</v>
       </c>
@@ -6184,7 +6196,7 @@
       </c>
       <c r="C341" s="1"/>
     </row>
-    <row r="342" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A342" s="1" t="s">
         <v>14</v>
       </c>
@@ -6193,7 +6205,7 @@
       </c>
       <c r="C342" s="1"/>
     </row>
-    <row r="343" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A343" s="1" t="s">
         <v>14</v>
       </c>
@@ -6202,7 +6214,7 @@
       </c>
       <c r="C343" s="1"/>
     </row>
-    <row r="344" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A344" s="1" t="s">
         <v>14</v>
       </c>
@@ -6211,7 +6223,7 @@
       </c>
       <c r="C344" s="1"/>
     </row>
-    <row r="345" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
         <v>14</v>
       </c>
@@ -6220,7 +6232,7 @@
       </c>
       <c r="C345" s="1"/>
     </row>
-    <row r="346" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
         <v>14</v>
       </c>
@@ -6229,7 +6241,7 @@
       </c>
       <c r="C346" s="1"/>
     </row>
-    <row r="347" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
         <v>14</v>
       </c>
@@ -6238,7 +6250,7 @@
       </c>
       <c r="C347" s="1"/>
     </row>
-    <row r="348" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A348" s="1" t="s">
         <v>14</v>
       </c>
@@ -6247,7 +6259,7 @@
       </c>
       <c r="C348" s="1"/>
     </row>
-    <row r="349" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="s">
         <v>14</v>
       </c>
@@ -6256,7 +6268,7 @@
       </c>
       <c r="C349" s="1"/>
     </row>
-    <row r="350" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
         <v>14</v>
       </c>
@@ -6265,7 +6277,7 @@
       </c>
       <c r="C350" s="1"/>
     </row>
-    <row r="351" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="s">
         <v>14</v>
       </c>
@@ -6274,7 +6286,7 @@
       </c>
       <c r="C351" s="1"/>
     </row>
-    <row r="352" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="s">
         <v>14</v>
       </c>
@@ -6283,7 +6295,7 @@
       </c>
       <c r="C352" s="1"/>
     </row>
-    <row r="353" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="s">
         <v>14</v>
       </c>
@@ -6292,7 +6304,7 @@
       </c>
       <c r="C353" s="1"/>
     </row>
-    <row r="354" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="s">
         <v>14</v>
       </c>
@@ -6301,7 +6313,7 @@
       </c>
       <c r="C354" s="1"/>
     </row>
-    <row r="355" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="s">
         <v>14</v>
       </c>
@@ -6310,7 +6322,7 @@
       </c>
       <c r="C355" s="1"/>
     </row>
-    <row r="356" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A356" s="1" t="s">
         <v>14</v>
       </c>
@@ -6319,7 +6331,7 @@
       </c>
       <c r="C356" s="1"/>
     </row>
-    <row r="357" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A357" s="1" t="s">
         <v>14</v>
       </c>
@@ -6328,7 +6340,7 @@
       </c>
       <c r="C357" s="1"/>
     </row>
-    <row r="358" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A358" s="1" t="s">
         <v>14</v>
       </c>
@@ -6337,7 +6349,7 @@
       </c>
       <c r="C358" s="1"/>
     </row>
-    <row r="359" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A359" s="1" t="s">
         <v>14</v>
       </c>
@@ -6346,7 +6358,7 @@
       </c>
       <c r="C359" s="1"/>
     </row>
-    <row r="360" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A360" s="1" t="s">
         <v>14</v>
       </c>
@@ -6355,7 +6367,7 @@
       </c>
       <c r="C360" s="1"/>
     </row>
-    <row r="361" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A361" s="1" t="s">
         <v>14</v>
       </c>
@@ -6364,7 +6376,7 @@
       </c>
       <c r="C361" s="1"/>
     </row>
-    <row r="362" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A362" s="1" t="s">
         <v>14</v>
       </c>
@@ -6373,7 +6385,7 @@
       </c>
       <c r="C362" s="1"/>
     </row>
-    <row r="363" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A363" s="1" t="s">
         <v>14</v>
       </c>
@@ -6382,7 +6394,7 @@
       </c>
       <c r="C363" s="1"/>
     </row>
-    <row r="364" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A364" s="1" t="s">
         <v>14</v>
       </c>
@@ -6391,7 +6403,7 @@
       </c>
       <c r="C364" s="1"/>
     </row>
-    <row r="365" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A365" s="1" t="s">
         <v>14</v>
       </c>
@@ -6400,7 +6412,7 @@
       </c>
       <c r="C365" s="1"/>
     </row>
-    <row r="366" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A366" s="1" t="s">
         <v>14</v>
       </c>
@@ -6409,7 +6421,7 @@
       </c>
       <c r="C366" s="1"/>
     </row>
-    <row r="367" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A367" s="1" t="s">
         <v>14</v>
       </c>
@@ -6418,7 +6430,7 @@
       </c>
       <c r="C367" s="1"/>
     </row>
-    <row r="368" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A368" s="1" t="s">
         <v>14</v>
       </c>
@@ -6427,7 +6439,7 @@
       </c>
       <c r="C368" s="1"/>
     </row>
-    <row r="369" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A369" s="1" t="s">
         <v>14</v>
       </c>
@@ -6436,7 +6448,7 @@
       </c>
       <c r="C369" s="1"/>
     </row>
-    <row r="370" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A370" s="1" t="s">
         <v>14</v>
       </c>
@@ -6445,7 +6457,7 @@
       </c>
       <c r="C370" s="1"/>
     </row>
-    <row r="371" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A371" s="1" t="s">
         <v>14</v>
       </c>
@@ -6454,7 +6466,7 @@
       </c>
       <c r="C371" s="1"/>
     </row>
-    <row r="372" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A372" s="1" t="s">
         <v>14</v>
       </c>
@@ -6463,7 +6475,7 @@
       </c>
       <c r="C372" s="1"/>
     </row>
-    <row r="373" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A373" s="1" t="s">
         <v>14</v>
       </c>
@@ -6472,7 +6484,7 @@
       </c>
       <c r="C373" s="1"/>
     </row>
-    <row r="374" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A374" s="1" t="s">
         <v>14</v>
       </c>
@@ -6481,7 +6493,7 @@
       </c>
       <c r="C374" s="1"/>
     </row>
-    <row r="375" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A375" s="1" t="s">
         <v>14</v>
       </c>
@@ -6490,7 +6502,7 @@
       </c>
       <c r="C375" s="1"/>
     </row>
-    <row r="376" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A376" s="1" t="s">
         <v>14</v>
       </c>
@@ -6499,7 +6511,7 @@
       </c>
       <c r="C376" s="1"/>
     </row>
-    <row r="377" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A377" s="1" t="s">
         <v>14</v>
       </c>
@@ -6508,7 +6520,7 @@
       </c>
       <c r="C377" s="1"/>
     </row>
-    <row r="378" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A378" s="1" t="s">
         <v>14</v>
       </c>
@@ -6517,7 +6529,7 @@
       </c>
       <c r="C378" s="1"/>
     </row>
-    <row r="379" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A379" s="1" t="s">
         <v>14</v>
       </c>
@@ -6526,7 +6538,7 @@
       </c>
       <c r="C379" s="1"/>
     </row>
-    <row r="380" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A380" s="1" t="s">
         <v>14</v>
       </c>
@@ -6535,7 +6547,7 @@
       </c>
       <c r="C380" s="1"/>
     </row>
-    <row r="381" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A381" s="1" t="s">
         <v>14</v>
       </c>
@@ -6544,7 +6556,7 @@
       </c>
       <c r="C381" s="1"/>
     </row>
-    <row r="382" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A382" s="1" t="s">
         <v>14</v>
       </c>
@@ -6553,7 +6565,7 @@
       </c>
       <c r="C382" s="1"/>
     </row>
-    <row r="383" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A383" s="1" t="s">
         <v>14</v>
       </c>
@@ -6562,7 +6574,7 @@
       </c>
       <c r="C383" s="1"/>
     </row>
-    <row r="384" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A384" s="1" t="s">
         <v>14</v>
       </c>
@@ -6571,7 +6583,7 @@
       </c>
       <c r="C384" s="1"/>
     </row>
-    <row r="385" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A385" s="1" t="s">
         <v>14</v>
       </c>
@@ -6580,7 +6592,7 @@
       </c>
       <c r="C385" s="1"/>
     </row>
-    <row r="386" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A386" s="1" t="s">
         <v>14</v>
       </c>
@@ -6589,7 +6601,7 @@
       </c>
       <c r="C386" s="1"/>
     </row>
-    <row r="387" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A387" s="1" t="s">
         <v>14</v>
       </c>
@@ -6598,7 +6610,7 @@
       </c>
       <c r="C387" s="1"/>
     </row>
-    <row r="388" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A388" s="1" t="s">
         <v>14</v>
       </c>
@@ -6607,7 +6619,7 @@
       </c>
       <c r="C388" s="1"/>
     </row>
-    <row r="389" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A389" s="1" t="s">
         <v>14</v>
       </c>
@@ -6616,7 +6628,7 @@
       </c>
       <c r="C389" s="1"/>
     </row>
-    <row r="390" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A390" s="1" t="s">
         <v>14</v>
       </c>
@@ -6625,7 +6637,7 @@
       </c>
       <c r="C390" s="1"/>
     </row>
-    <row r="391" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A391" s="1" t="s">
         <v>14</v>
       </c>
@@ -6634,7 +6646,7 @@
       </c>
       <c r="C391" s="1"/>
     </row>
-    <row r="392" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A392" s="1" t="s">
         <v>14</v>
       </c>
@@ -6643,7 +6655,7 @@
       </c>
       <c r="C392" s="1"/>
     </row>
-    <row r="393" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A393" s="1" t="s">
         <v>14</v>
       </c>
@@ -6652,7 +6664,7 @@
       </c>
       <c r="C393" s="1"/>
     </row>
-    <row r="394" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A394" s="1" t="s">
         <v>14</v>
       </c>
@@ -6661,7 +6673,7 @@
       </c>
       <c r="C394" s="1"/>
     </row>
-    <row r="395" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A395" s="1" t="s">
         <v>1</v>
       </c>
@@ -6670,7 +6682,7 @@
       </c>
       <c r="C395" s="1"/>
     </row>
-    <row r="396" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A396" s="1" t="s">
         <v>1</v>
       </c>
@@ -6679,7 +6691,7 @@
       </c>
       <c r="C396" s="1"/>
     </row>
-    <row r="397" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A397" s="1" t="s">
         <v>1</v>
       </c>
@@ -6688,7 +6700,7 @@
       </c>
       <c r="C397" s="1"/>
     </row>
-    <row r="398" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A398" s="1" t="s">
         <v>1</v>
       </c>
@@ -6697,7 +6709,7 @@
       </c>
       <c r="C398" s="1"/>
     </row>
-    <row r="399" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A399" s="1" t="s">
         <v>1</v>
       </c>
@@ -6706,7 +6718,7 @@
       </c>
       <c r="C399" s="1"/>
     </row>
-    <row r="400" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A400" s="1" t="s">
         <v>1</v>
       </c>
@@ -6715,7 +6727,7 @@
       </c>
       <c r="C400" s="1"/>
     </row>
-    <row r="401" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A401" s="1" t="s">
         <v>1</v>
       </c>
@@ -6724,7 +6736,7 @@
       </c>
       <c r="C401" s="1"/>
     </row>
-    <row r="402" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A402" s="1" t="s">
         <v>1</v>
       </c>
@@ -6733,7 +6745,7 @@
       </c>
       <c r="C402" s="1"/>
     </row>
-    <row r="403" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A403" s="1" t="s">
         <v>1</v>
       </c>
@@ -6742,7 +6754,7 @@
       </c>
       <c r="C403" s="1"/>
     </row>
-    <row r="404" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A404" s="1" t="s">
         <v>1</v>
       </c>
@@ -6751,7 +6763,7 @@
       </c>
       <c r="C404" s="1"/>
     </row>
-    <row r="405" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A405" s="1" t="s">
         <v>1</v>
       </c>
@@ -6760,7 +6772,7 @@
       </c>
       <c r="C405" s="1"/>
     </row>
-    <row r="406" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A406" s="1" t="s">
         <v>1</v>
       </c>
@@ -6769,7 +6781,7 @@
       </c>
       <c r="C406" s="1"/>
     </row>
-    <row r="407" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A407" s="1" t="s">
         <v>1</v>
       </c>
@@ -6778,7 +6790,7 @@
       </c>
       <c r="C407" s="1"/>
     </row>
-    <row r="408" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A408" s="1" t="s">
         <v>1</v>
       </c>
@@ -6787,7 +6799,7 @@
       </c>
       <c r="C408" s="1"/>
     </row>
-    <row r="409" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A409" s="1" t="s">
         <v>1</v>
       </c>
@@ -6796,7 +6808,7 @@
       </c>
       <c r="C409" s="1"/>
     </row>
-    <row r="410" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A410" s="1" t="s">
         <v>1</v>
       </c>
@@ -6805,7 +6817,7 @@
       </c>
       <c r="C410" s="1"/>
     </row>
-    <row r="411" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A411" s="1" t="s">
         <v>1</v>
       </c>
@@ -6814,7 +6826,7 @@
       </c>
       <c r="C411" s="1"/>
     </row>
-    <row r="412" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A412" s="1" t="s">
         <v>1</v>
       </c>
@@ -6823,7 +6835,7 @@
       </c>
       <c r="C412" s="1"/>
     </row>
-    <row r="413" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A413" s="1" t="s">
         <v>1</v>
       </c>
@@ -6832,7 +6844,7 @@
       </c>
       <c r="C413" s="1"/>
     </row>
-    <row r="414" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A414" s="1" t="s">
         <v>1</v>
       </c>
@@ -6841,7 +6853,7 @@
       </c>
       <c r="C414" s="1"/>
     </row>
-    <row r="415" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A415" s="1" t="s">
         <v>1</v>
       </c>
@@ -6850,7 +6862,7 @@
       </c>
       <c r="C415" s="1"/>
     </row>
-    <row r="416" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A416" s="1" t="s">
         <v>1</v>
       </c>
@@ -6859,7 +6871,7 @@
       </c>
       <c r="C416" s="1"/>
     </row>
-    <row r="417" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A417" s="1" t="s">
         <v>1</v>
       </c>
@@ -6868,7 +6880,7 @@
       </c>
       <c r="C417" s="1"/>
     </row>
-    <row r="418" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A418" s="1" t="s">
         <v>1</v>
       </c>
@@ -6877,7 +6889,7 @@
       </c>
       <c r="C418" s="1"/>
     </row>
-    <row r="419" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A419" s="1" t="s">
         <v>1</v>
       </c>
@@ -6886,7 +6898,7 @@
       </c>
       <c r="C419" s="1"/>
     </row>
-    <row r="420" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A420" s="1" t="s">
         <v>1</v>
       </c>
@@ -6895,7 +6907,7 @@
       </c>
       <c r="C420" s="1"/>
     </row>
-    <row r="421" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A421" s="1" t="s">
         <v>1</v>
       </c>
@@ -6904,7 +6916,7 @@
       </c>
       <c r="C421" s="1"/>
     </row>
-    <row r="422" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A422" s="1" t="s">
         <v>1</v>
       </c>
@@ -6913,7 +6925,7 @@
       </c>
       <c r="C422" s="1"/>
     </row>
-    <row r="423" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A423" s="1" t="s">
         <v>1</v>
       </c>
@@ -6922,7 +6934,7 @@
       </c>
       <c r="C423" s="1"/>
     </row>
-    <row r="424" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A424" s="1" t="s">
         <v>1</v>
       </c>
@@ -6931,7 +6943,7 @@
       </c>
       <c r="C424" s="1"/>
     </row>
-    <row r="425" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A425" s="1" t="s">
         <v>1</v>
       </c>
@@ -6940,7 +6952,7 @@
       </c>
       <c r="C425" s="1"/>
     </row>
-    <row r="426" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A426" s="1" t="s">
         <v>1</v>
       </c>
@@ -6949,7 +6961,7 @@
       </c>
       <c r="C426" s="1"/>
     </row>
-    <row r="427" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A427" s="1" t="s">
         <v>1</v>
       </c>
@@ -6958,7 +6970,7 @@
       </c>
       <c r="C427" s="1"/>
     </row>
-    <row r="428" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A428" s="1" t="s">
         <v>1</v>
       </c>
@@ -6967,7 +6979,7 @@
       </c>
       <c r="C428" s="1"/>
     </row>
-    <row r="429" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A429" s="1" t="s">
         <v>1</v>
       </c>
@@ -6976,7 +6988,7 @@
       </c>
       <c r="C429" s="1"/>
     </row>
-    <row r="430" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A430" s="1" t="s">
         <v>1</v>
       </c>
@@ -6985,7 +6997,7 @@
       </c>
       <c r="C430" s="1"/>
     </row>
-    <row r="431" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A431" s="1" t="s">
         <v>26</v>
       </c>
@@ -6994,7 +7006,7 @@
       </c>
       <c r="C431" s="1"/>
     </row>
-    <row r="432" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A432" s="1" t="s">
         <v>26</v>
       </c>
@@ -7003,7 +7015,7 @@
       </c>
       <c r="C432" s="1"/>
     </row>
-    <row r="433" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A433" s="1" t="s">
         <v>26</v>
       </c>
@@ -7012,7 +7024,7 @@
       </c>
       <c r="C433" s="1"/>
     </row>
-    <row r="434" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A434" s="1" t="s">
         <v>26</v>
       </c>
@@ -7021,7 +7033,7 @@
       </c>
       <c r="C434" s="1"/>
     </row>
-    <row r="435" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A435" s="1" t="s">
         <v>26</v>
       </c>
@@ -7030,7 +7042,7 @@
       </c>
       <c r="C435" s="1"/>
     </row>
-    <row r="436" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A436" s="1" t="s">
         <v>26</v>
       </c>
@@ -7039,7 +7051,7 @@
       </c>
       <c r="C436" s="1"/>
     </row>
-    <row r="437" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A437" s="1" t="s">
         <v>26</v>
       </c>
@@ -7048,7 +7060,7 @@
       </c>
       <c r="C437" s="1"/>
     </row>
-    <row r="438" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A438" s="1" t="s">
         <v>26</v>
       </c>
@@ -7057,7 +7069,7 @@
       </c>
       <c r="C438" s="1"/>
     </row>
-    <row r="439" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A439" s="1" t="s">
         <v>26</v>
       </c>
@@ -7066,7 +7078,7 @@
       </c>
       <c r="C439" s="1"/>
     </row>
-    <row r="440" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A440" s="1" t="s">
         <v>26</v>
       </c>
@@ -7075,7 +7087,7 @@
       </c>
       <c r="C440" s="1"/>
     </row>
-    <row r="441" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A441" s="1" t="s">
         <v>26</v>
       </c>
@@ -7084,7 +7096,7 @@
       </c>
       <c r="C441" s="1"/>
     </row>
-    <row r="442" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A442" s="1" t="s">
         <v>26</v>
       </c>
@@ -7093,7 +7105,7 @@
       </c>
       <c r="C442" s="1"/>
     </row>
-    <row r="443" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A443" s="1" t="s">
         <v>26</v>
       </c>
@@ -7102,7 +7114,7 @@
       </c>
       <c r="C443" s="1"/>
     </row>
-    <row r="444" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A444" s="1" t="s">
         <v>26</v>
       </c>
@@ -7111,7 +7123,7 @@
       </c>
       <c r="C444" s="1"/>
     </row>
-    <row r="445" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A445" s="1" t="s">
         <v>26</v>
       </c>
@@ -7120,7 +7132,7 @@
       </c>
       <c r="C445" s="1"/>
     </row>
-    <row r="446" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A446" s="1" t="s">
         <v>26</v>
       </c>
@@ -7129,7 +7141,7 @@
       </c>
       <c r="C446" s="1"/>
     </row>
-    <row r="447" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A447" s="1" t="s">
         <v>30</v>
       </c>
@@ -7138,7 +7150,7 @@
       </c>
       <c r="C447" s="1"/>
     </row>
-    <row r="448" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A448" s="1" t="s">
         <v>30</v>
       </c>
@@ -7147,7 +7159,7 @@
       </c>
       <c r="C448" s="1"/>
     </row>
-    <row r="449" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A449" s="1" t="s">
         <v>30</v>
       </c>
@@ -7156,7 +7168,7 @@
       </c>
       <c r="C449" s="1"/>
     </row>
-    <row r="450" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A450" s="1" t="s">
         <v>30</v>
       </c>
@@ -7165,7 +7177,7 @@
       </c>
       <c r="C450" s="1"/>
     </row>
-    <row r="451" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A451" s="1" t="s">
         <v>30</v>
       </c>
@@ -7174,7 +7186,7 @@
       </c>
       <c r="C451" s="1"/>
     </row>
-    <row r="452" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A452" s="1" t="s">
         <v>30</v>
       </c>
@@ -7183,7 +7195,7 @@
       </c>
       <c r="C452" s="1"/>
     </row>
-    <row r="453" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A453" s="1" t="s">
         <v>30</v>
       </c>
@@ -7192,7 +7204,7 @@
       </c>
       <c r="C453" s="1"/>
     </row>
-    <row r="454" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A454" s="1" t="s">
         <v>30</v>
       </c>
@@ -7201,7 +7213,7 @@
       </c>
       <c r="C454" s="1"/>
     </row>
-    <row r="455" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A455" s="1" t="s">
         <v>30</v>
       </c>
@@ -7210,7 +7222,7 @@
       </c>
       <c r="C455" s="1"/>
     </row>
-    <row r="456" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A456" s="1" t="s">
         <v>30</v>
       </c>
@@ -7219,7 +7231,7 @@
       </c>
       <c r="C456" s="1"/>
     </row>
-    <row r="457" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A457" s="1" t="s">
         <v>30</v>
       </c>
@@ -7228,7 +7240,7 @@
       </c>
       <c r="C457" s="1"/>
     </row>
-    <row r="458" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A458" s="1" t="s">
         <v>30</v>
       </c>
@@ -7237,7 +7249,7 @@
       </c>
       <c r="C458" s="1"/>
     </row>
-    <row r="459" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A459" s="1" t="s">
         <v>29</v>
       </c>
@@ -7246,7 +7258,7 @@
       </c>
       <c r="C459" s="1"/>
     </row>
-    <row r="460" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A460" s="1" t="s">
         <v>29</v>
       </c>
@@ -7255,7 +7267,7 @@
       </c>
       <c r="C460" s="1"/>
     </row>
-    <row r="461" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A461" s="1" t="s">
         <v>29</v>
       </c>
@@ -7264,7 +7276,7 @@
       </c>
       <c r="C461" s="1"/>
     </row>
-    <row r="462" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A462" s="1" t="s">
         <v>29</v>
       </c>
@@ -7273,7 +7285,7 @@
       </c>
       <c r="C462" s="1"/>
     </row>
-    <row r="463" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A463" s="1" t="s">
         <v>29</v>
       </c>
@@ -7282,7 +7294,7 @@
       </c>
       <c r="C463" s="1"/>
     </row>
-    <row r="464" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A464" s="1" t="s">
         <v>29</v>
       </c>
@@ -7291,7 +7303,7 @@
       </c>
       <c r="C464" s="1"/>
     </row>
-    <row r="465" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A465" s="1" t="s">
         <v>29</v>
       </c>
@@ -7300,7 +7312,7 @@
       </c>
       <c r="C465" s="1"/>
     </row>
-    <row r="466" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A466" s="1" t="s">
         <v>29</v>
       </c>
@@ -7309,7 +7321,7 @@
       </c>
       <c r="C466" s="1"/>
     </row>
-    <row r="467" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A467" s="1" t="s">
         <v>29</v>
       </c>
@@ -7318,7 +7330,7 @@
       </c>
       <c r="C467" s="1"/>
     </row>
-    <row r="468" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A468" s="1" t="s">
         <v>29</v>
       </c>
@@ -7327,7 +7339,7 @@
       </c>
       <c r="C468" s="1"/>
     </row>
-    <row r="469" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A469" s="1" t="s">
         <v>29</v>
       </c>
@@ -7336,7 +7348,7 @@
       </c>
       <c r="C469" s="1"/>
     </row>
-    <row r="470" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A470" s="1" t="s">
         <v>24</v>
       </c>
@@ -7345,7 +7357,7 @@
       </c>
       <c r="C470" s="1"/>
     </row>
-    <row r="471" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A471" s="1" t="s">
         <v>24</v>
       </c>
@@ -7354,7 +7366,7 @@
       </c>
       <c r="C471" s="1"/>
     </row>
-    <row r="472" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A472" s="1" t="s">
         <v>24</v>
       </c>
@@ -7363,7 +7375,7 @@
       </c>
       <c r="C472" s="1"/>
     </row>
-    <row r="473" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A473" s="1" t="s">
         <v>24</v>
       </c>
@@ -7372,7 +7384,7 @@
       </c>
       <c r="C473" s="1"/>
     </row>
-    <row r="474" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A474" s="1" t="s">
         <v>24</v>
       </c>
@@ -7381,7 +7393,7 @@
       </c>
       <c r="C474" s="1"/>
     </row>
-    <row r="475" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A475" s="1" t="s">
         <v>24</v>
       </c>
@@ -7390,7 +7402,7 @@
       </c>
       <c r="C475" s="1"/>
     </row>
-    <row r="476" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A476" s="1" t="s">
         <v>24</v>
       </c>
@@ -7399,7 +7411,7 @@
       </c>
       <c r="C476" s="1"/>
     </row>
-    <row r="477" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A477" s="1" t="s">
         <v>24</v>
       </c>
@@ -7408,7 +7420,7 @@
       </c>
       <c r="C477" s="1"/>
     </row>
-    <row r="478" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A478" s="1" t="s">
         <v>24</v>
       </c>
@@ -7417,7 +7429,7 @@
       </c>
       <c r="C478" s="1"/>
     </row>
-    <row r="479" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A479" s="1" t="s">
         <v>24</v>
       </c>
@@ -7426,7 +7438,7 @@
       </c>
       <c r="C479" s="1"/>
     </row>
-    <row r="480" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A480" s="1" t="s">
         <v>24</v>
       </c>
@@ -7435,7 +7447,7 @@
       </c>
       <c r="C480" s="1"/>
     </row>
-    <row r="481" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A481" s="1" t="s">
         <v>24</v>
       </c>
@@ -7444,7 +7456,7 @@
       </c>
       <c r="C481" s="1"/>
     </row>
-    <row r="482" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A482" s="1" t="s">
         <v>24</v>
       </c>
@@ -7453,7 +7465,7 @@
       </c>
       <c r="C482" s="1"/>
     </row>
-    <row r="483" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A483" s="1" t="s">
         <v>24</v>
       </c>
@@ -7462,7 +7474,7 @@
       </c>
       <c r="C483" s="1"/>
     </row>
-    <row r="484" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A484" s="1" t="s">
         <v>24</v>
       </c>
@@ -7471,7 +7483,7 @@
       </c>
       <c r="C484" s="1"/>
     </row>
-    <row r="485" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A485" s="1" t="s">
         <v>24</v>
       </c>
@@ -7480,7 +7492,7 @@
       </c>
       <c r="C485" s="1"/>
     </row>
-    <row r="486" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A486" s="1" t="s">
         <v>17</v>
       </c>
@@ -7489,7 +7501,7 @@
       </c>
       <c r="C486" s="1"/>
     </row>
-    <row r="487" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A487" s="1" t="s">
         <v>17</v>
       </c>
@@ -7498,7 +7510,7 @@
       </c>
       <c r="C487" s="1"/>
     </row>
-    <row r="488" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A488" s="1" t="s">
         <v>17</v>
       </c>
@@ -7507,7 +7519,7 @@
       </c>
       <c r="C488" s="1"/>
     </row>
-    <row r="489" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A489" s="1" t="s">
         <v>17</v>
       </c>
@@ -7516,7 +7528,7 @@
       </c>
       <c r="C489" s="1"/>
     </row>
-    <row r="490" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A490" s="1" t="s">
         <v>17</v>
       </c>
@@ -7525,7 +7537,7 @@
       </c>
       <c r="C490" s="1"/>
     </row>
-    <row r="491" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A491" s="1" t="s">
         <v>17</v>
       </c>
@@ -7534,7 +7546,7 @@
       </c>
       <c r="C491" s="1"/>
     </row>
-    <row r="492" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A492" s="1" t="s">
         <v>17</v>
       </c>
@@ -7543,7 +7555,7 @@
       </c>
       <c r="C492" s="1"/>
     </row>
-    <row r="493" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A493" s="1" t="s">
         <v>17</v>
       </c>
@@ -7552,7 +7564,7 @@
       </c>
       <c r="C493" s="1"/>
     </row>
-    <row r="494" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A494" s="1" t="s">
         <v>17</v>
       </c>
@@ -7561,7 +7573,7 @@
       </c>
       <c r="C494" s="1"/>
     </row>
-    <row r="495" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A495" s="1" t="s">
         <v>17</v>
       </c>
@@ -7570,7 +7582,7 @@
       </c>
       <c r="C495" s="1"/>
     </row>
-    <row r="496" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A496" s="1" t="s">
         <v>17</v>
       </c>
@@ -7579,7 +7591,7 @@
       </c>
       <c r="C496" s="1"/>
     </row>
-    <row r="497" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A497" s="1" t="s">
         <v>17</v>
       </c>
@@ -7588,7 +7600,7 @@
       </c>
       <c r="C497" s="1"/>
     </row>
-    <row r="498" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A498" s="1" t="s">
         <v>17</v>
       </c>
@@ -7597,7 +7609,7 @@
       </c>
       <c r="C498" s="1"/>
     </row>
-    <row r="499" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A499" s="1" t="s">
         <v>17</v>
       </c>
@@ -7606,7 +7618,7 @@
       </c>
       <c r="C499" s="1"/>
     </row>
-    <row r="500" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A500" s="1" t="s">
         <v>17</v>
       </c>
@@ -7615,7 +7627,7 @@
       </c>
       <c r="C500" s="1"/>
     </row>
-    <row r="501" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A501" s="1" t="s">
         <v>17</v>
       </c>
@@ -7624,7 +7636,7 @@
       </c>
       <c r="C501" s="1"/>
     </row>
-    <row r="502" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A502" s="1" t="s">
         <v>17</v>
       </c>
@@ -7633,7 +7645,7 @@
       </c>
       <c r="C502" s="1"/>
     </row>
-    <row r="503" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A503" s="1" t="s">
         <v>17</v>
       </c>
@@ -7642,7 +7654,7 @@
       </c>
       <c r="C503" s="1"/>
     </row>
-    <row r="504" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A504" s="1" t="s">
         <v>17</v>
       </c>
@@ -7651,7 +7663,7 @@
       </c>
       <c r="C504" s="1"/>
     </row>
-    <row r="505" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A505" s="1" t="s">
         <v>17</v>
       </c>
@@ -7660,7 +7672,7 @@
       </c>
       <c r="C505" s="1"/>
     </row>
-    <row r="506" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A506" s="1" t="s">
         <v>17</v>
       </c>
@@ -7669,7 +7681,7 @@
       </c>
       <c r="C506" s="1"/>
     </row>
-    <row r="507" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A507" s="1" t="s">
         <v>17</v>
       </c>
@@ -7678,7 +7690,7 @@
       </c>
       <c r="C507" s="1"/>
     </row>
-    <row r="508" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A508" s="1" t="s">
         <v>17</v>
       </c>
@@ -7687,7 +7699,7 @@
       </c>
       <c r="C508" s="1"/>
     </row>
-    <row r="509" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A509" s="1" t="s">
         <v>17</v>
       </c>
@@ -7696,7 +7708,7 @@
       </c>
       <c r="C509" s="1"/>
     </row>
-    <row r="510" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A510" s="1" t="s">
         <v>17</v>
       </c>
@@ -7705,7 +7717,7 @@
       </c>
       <c r="C510" s="1"/>
     </row>
-    <row r="511" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A511" s="1" t="s">
         <v>17</v>
       </c>
@@ -7714,7 +7726,7 @@
       </c>
       <c r="C511" s="1"/>
     </row>
-    <row r="512" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A512" s="1" t="s">
         <v>17</v>
       </c>
@@ -7723,7 +7735,7 @@
       </c>
       <c r="C512" s="1"/>
     </row>
-    <row r="513" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A513" s="1" t="s">
         <v>17</v>
       </c>
@@ -7732,7 +7744,7 @@
       </c>
       <c r="C513" s="1"/>
     </row>
-    <row r="514" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A514" s="1" t="s">
         <v>17</v>
       </c>
@@ -7741,7 +7753,7 @@
       </c>
       <c r="C514" s="1"/>
     </row>
-    <row r="515" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A515" s="1" t="s">
         <v>17</v>
       </c>
@@ -7750,7 +7762,7 @@
       </c>
       <c r="C515" s="1"/>
     </row>
-    <row r="516" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A516" s="1" t="s">
         <v>34</v>
       </c>
@@ -7759,7 +7771,7 @@
       </c>
       <c r="C516" s="1"/>
     </row>
-    <row r="517" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A517" s="1" t="s">
         <v>34</v>
       </c>
@@ -7768,7 +7780,7 @@
       </c>
       <c r="C517" s="1"/>
     </row>
-    <row r="518" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A518" s="1" t="s">
         <v>34</v>
       </c>
@@ -7777,7 +7789,7 @@
       </c>
       <c r="C518" s="1"/>
     </row>
-    <row r="519" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A519" s="1" t="s">
         <v>34</v>
       </c>
@@ -7786,7 +7798,7 @@
       </c>
       <c r="C519" s="1"/>
     </row>
-    <row r="520" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A520" s="1" t="s">
         <v>6</v>
       </c>
@@ -7795,7 +7807,7 @@
       </c>
       <c r="C520" s="1"/>
     </row>
-    <row r="521" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A521" s="1" t="s">
         <v>6</v>
       </c>
@@ -7804,7 +7816,7 @@
       </c>
       <c r="C521" s="1"/>
     </row>
-    <row r="522" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A522" s="1" t="s">
         <v>6</v>
       </c>
@@ -7813,7 +7825,7 @@
       </c>
       <c r="C522" s="1"/>
     </row>
-    <row r="523" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A523" s="1" t="s">
         <v>6</v>
       </c>
@@ -7822,7 +7834,7 @@
       </c>
       <c r="C523" s="1"/>
     </row>
-    <row r="524" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A524" s="1" t="s">
         <v>6</v>
       </c>
@@ -7831,7 +7843,7 @@
       </c>
       <c r="C524" s="1"/>
     </row>
-    <row r="525" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A525" s="1" t="s">
         <v>6</v>
       </c>
@@ -7840,7 +7852,7 @@
       </c>
       <c r="C525" s="1"/>
     </row>
-    <row r="526" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A526" s="1" t="s">
         <v>6</v>
       </c>
@@ -7849,7 +7861,7 @@
       </c>
       <c r="C526" s="1"/>
     </row>
-    <row r="527" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A527" s="1" t="s">
         <v>6</v>
       </c>
@@ -7858,7 +7870,7 @@
       </c>
       <c r="C527" s="1"/>
     </row>
-    <row r="528" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A528" s="1" t="s">
         <v>6</v>
       </c>
@@ -7867,7 +7879,7 @@
       </c>
       <c r="C528" s="1"/>
     </row>
-    <row r="529" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A529" s="1" t="s">
         <v>6</v>
       </c>
@@ -7876,7 +7888,7 @@
       </c>
       <c r="C529" s="1"/>
     </row>
-    <row r="530" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A530" s="1" t="s">
         <v>6</v>
       </c>
@@ -7885,7 +7897,7 @@
       </c>
       <c r="C530" s="1"/>
     </row>
-    <row r="531" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A531" s="1" t="s">
         <v>6</v>
       </c>
@@ -7894,7 +7906,7 @@
       </c>
       <c r="C531" s="1"/>
     </row>
-    <row r="532" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A532" s="1" t="s">
         <v>6</v>
       </c>
@@ -7903,7 +7915,7 @@
       </c>
       <c r="C532" s="1"/>
     </row>
-    <row r="533" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A533" s="1" t="s">
         <v>6</v>
       </c>
@@ -7912,7 +7924,7 @@
       </c>
       <c r="C533" s="1"/>
     </row>
-    <row r="534" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A534" s="1" t="s">
         <v>6</v>
       </c>
@@ -7921,7 +7933,7 @@
       </c>
       <c r="C534" s="1"/>
     </row>
-    <row r="535" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A535" s="1" t="s">
         <v>6</v>
       </c>
@@ -7930,7 +7942,7 @@
       </c>
       <c r="C535" s="1"/>
     </row>
-    <row r="536" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A536" s="1" t="s">
         <v>6</v>
       </c>
@@ -7939,7 +7951,7 @@
       </c>
       <c r="C536" s="1"/>
     </row>
-    <row r="537" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A537" s="1" t="s">
         <v>6</v>
       </c>
@@ -7948,7 +7960,7 @@
       </c>
       <c r="C537" s="1"/>
     </row>
-    <row r="538" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A538" s="1" t="s">
         <v>6</v>
       </c>
@@ -7957,7 +7969,7 @@
       </c>
       <c r="C538" s="1"/>
     </row>
-    <row r="539" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A539" s="1" t="s">
         <v>6</v>
       </c>
@@ -7966,7 +7978,7 @@
       </c>
       <c r="C539" s="1"/>
     </row>
-    <row r="540" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A540" s="1" t="s">
         <v>6</v>
       </c>
@@ -7975,7 +7987,7 @@
       </c>
       <c r="C540" s="1"/>
     </row>
-    <row r="541" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A541" s="1" t="s">
         <v>6</v>
       </c>
@@ -7984,7 +7996,7 @@
       </c>
       <c r="C541" s="1"/>
     </row>
-    <row r="542" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A542" s="1" t="s">
         <v>6</v>
       </c>
@@ -7993,7 +8005,7 @@
       </c>
       <c r="C542" s="1"/>
     </row>
-    <row r="543" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A543" s="1" t="s">
         <v>18</v>
       </c>
@@ -8002,7 +8014,7 @@
       </c>
       <c r="C543" s="1"/>
     </row>
-    <row r="544" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A544" s="1" t="s">
         <v>18</v>
       </c>
@@ -8011,7 +8023,7 @@
       </c>
       <c r="C544" s="1"/>
     </row>
-    <row r="545" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A545" s="1" t="s">
         <v>18</v>
       </c>
@@ -8020,7 +8032,7 @@
       </c>
       <c r="C545" s="1"/>
     </row>
-    <row r="546" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A546" s="1" t="s">
         <v>18</v>
       </c>
@@ -8029,7 +8041,7 @@
       </c>
       <c r="C546" s="1"/>
     </row>
-    <row r="547" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A547" s="1" t="s">
         <v>18</v>
       </c>
@@ -8038,7 +8050,7 @@
       </c>
       <c r="C547" s="1"/>
     </row>
-    <row r="548" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A548" s="1" t="s">
         <v>18</v>
       </c>
@@ -8047,7 +8059,7 @@
       </c>
       <c r="C548" s="1"/>
     </row>
-    <row r="549" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A549" s="1" t="s">
         <v>18</v>
       </c>
@@ -8056,7 +8068,7 @@
       </c>
       <c r="C549" s="1"/>
     </row>
-    <row r="550" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A550" s="1" t="s">
         <v>18</v>
       </c>
@@ -8065,7 +8077,7 @@
       </c>
       <c r="C550" s="1"/>
     </row>
-    <row r="551" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A551" s="1" t="s">
         <v>18</v>
       </c>
@@ -8074,7 +8086,7 @@
       </c>
       <c r="C551" s="1"/>
     </row>
-    <row r="552" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A552" s="1" t="s">
         <v>18</v>
       </c>
@@ -8083,7 +8095,7 @@
       </c>
       <c r="C552" s="1"/>
     </row>
-    <row r="553" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A553" s="1" t="s">
         <v>18</v>
       </c>
@@ -8092,7 +8104,7 @@
       </c>
       <c r="C553" s="1"/>
     </row>
-    <row r="554" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A554" s="1" t="s">
         <v>18</v>
       </c>
@@ -8101,7 +8113,7 @@
       </c>
       <c r="C554" s="1"/>
     </row>
-    <row r="555" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A555" s="1" t="s">
         <v>18</v>
       </c>
@@ -8110,7 +8122,7 @@
       </c>
       <c r="C555" s="1"/>
     </row>
-    <row r="556" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A556" s="1" t="s">
         <v>18</v>
       </c>
@@ -8119,7 +8131,7 @@
       </c>
       <c r="C556" s="1"/>
     </row>
-    <row r="557" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A557" s="1" t="s">
         <v>18</v>
       </c>
@@ -8128,7 +8140,7 @@
       </c>
       <c r="C557" s="1"/>
     </row>
-    <row r="558" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A558" s="1" t="s">
         <v>18</v>
       </c>
@@ -8137,7 +8149,7 @@
       </c>
       <c r="C558" s="1"/>
     </row>
-    <row r="559" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A559" s="1" t="s">
         <v>18</v>
       </c>
@@ -8146,7 +8158,7 @@
       </c>
       <c r="C559" s="1"/>
     </row>
-    <row r="560" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A560" s="1" t="s">
         <v>18</v>
       </c>
@@ -8155,7 +8167,7 @@
       </c>
       <c r="C560" s="1"/>
     </row>
-    <row r="561" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A561" s="1" t="s">
         <v>18</v>
       </c>
@@ -8164,7 +8176,7 @@
       </c>
       <c r="C561" s="1"/>
     </row>
-    <row r="562" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A562" s="1" t="s">
         <v>18</v>
       </c>
@@ -8173,7 +8185,7 @@
       </c>
       <c r="C562" s="1"/>
     </row>
-    <row r="563" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A563" s="1" t="s">
         <v>18</v>
       </c>
@@ -8182,7 +8194,7 @@
       </c>
       <c r="C563" s="1"/>
     </row>
-    <row r="564" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A564" s="1" t="s">
         <v>18</v>
       </c>
@@ -8191,7 +8203,7 @@
       </c>
       <c r="C564" s="1"/>
     </row>
-    <row r="565" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A565" s="1" t="s">
         <v>18</v>
       </c>
@@ -8200,7 +8212,7 @@
       </c>
       <c r="C565" s="1"/>
     </row>
-    <row r="566" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A566" s="1" t="s">
         <v>18</v>
       </c>
@@ -8209,7 +8221,7 @@
       </c>
       <c r="C566" s="1"/>
     </row>
-    <row r="567" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A567" s="1" t="s">
         <v>18</v>
       </c>
@@ -8218,7 +8230,7 @@
       </c>
       <c r="C567" s="1"/>
     </row>
-    <row r="568" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A568" s="1" t="s">
         <v>18</v>
       </c>
@@ -8227,7 +8239,7 @@
       </c>
       <c r="C568" s="1"/>
     </row>
-    <row r="569" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A569" s="1" t="s">
         <v>18</v>
       </c>
@@ -8236,7 +8248,7 @@
       </c>
       <c r="C569" s="1"/>
     </row>
-    <row r="570" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A570" s="1" t="s">
         <v>18</v>
       </c>
@@ -8245,7 +8257,7 @@
       </c>
       <c r="C570" s="1"/>
     </row>
-    <row r="571" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A571" s="1" t="s">
         <v>18</v>
       </c>
@@ -8254,7 +8266,7 @@
       </c>
       <c r="C571" s="1"/>
     </row>
-    <row r="572" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A572" s="1" t="s">
         <v>18</v>
       </c>
@@ -8263,7 +8275,7 @@
       </c>
       <c r="C572" s="1"/>
     </row>
-    <row r="573" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A573" s="1" t="s">
         <v>18</v>
       </c>
@@ -8272,7 +8284,7 @@
       </c>
       <c r="C573" s="1"/>
     </row>
-    <row r="574" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A574" s="1" t="s">
         <v>18</v>
       </c>
@@ -8281,7 +8293,7 @@
       </c>
       <c r="C574" s="1"/>
     </row>
-    <row r="575" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A575" s="1" t="s">
         <v>18</v>
       </c>
@@ -8290,7 +8302,7 @@
       </c>
       <c r="C575" s="1"/>
     </row>
-    <row r="576" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A576" s="1" t="s">
         <v>18</v>
       </c>
@@ -8299,7 +8311,7 @@
       </c>
       <c r="C576" s="1"/>
     </row>
-    <row r="577" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A577" s="1" t="s">
         <v>18</v>
       </c>
@@ -8308,7 +8320,7 @@
       </c>
       <c r="C577" s="1"/>
     </row>
-    <row r="578" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A578" s="1" t="s">
         <v>18</v>
       </c>
@@ -8317,7 +8329,7 @@
       </c>
       <c r="C578" s="1"/>
     </row>
-    <row r="579" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A579" s="1" t="s">
         <v>18</v>
       </c>
@@ -8326,7 +8338,7 @@
       </c>
       <c r="C579" s="1"/>
     </row>
-    <row r="580" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A580" s="1" t="s">
         <v>18</v>
       </c>
@@ -8335,7 +8347,7 @@
       </c>
       <c r="C580" s="1"/>
     </row>
-    <row r="581" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A581" s="1" t="s">
         <v>18</v>
       </c>
@@ -8344,7 +8356,7 @@
       </c>
       <c r="C581" s="1"/>
     </row>
-    <row r="582" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A582" s="1" t="s">
         <v>18</v>
       </c>
@@ -8353,7 +8365,7 @@
       </c>
       <c r="C582" s="1"/>
     </row>
-    <row r="583" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A583" s="1" t="s">
         <v>18</v>
       </c>
@@ -8362,7 +8374,7 @@
       </c>
       <c r="C583" s="1"/>
     </row>
-    <row r="584" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A584" s="1" t="s">
         <v>18</v>
       </c>
@@ -8371,7 +8383,7 @@
       </c>
       <c r="C584" s="1"/>
     </row>
-    <row r="585" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A585" s="1" t="s">
         <v>18</v>
       </c>
@@ -8380,7 +8392,7 @@
       </c>
       <c r="C585" s="1"/>
     </row>
-    <row r="586" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A586" s="1" t="s">
         <v>18</v>
       </c>
@@ -8389,7 +8401,7 @@
       </c>
       <c r="C586" s="1"/>
     </row>
-    <row r="587" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A587" s="1" t="s">
         <v>18</v>
       </c>
@@ -8398,7 +8410,7 @@
       </c>
       <c r="C587" s="1"/>
     </row>
-    <row r="588" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A588" s="1" t="s">
         <v>18</v>
       </c>
@@ -8407,7 +8419,7 @@
       </c>
       <c r="C588" s="1"/>
     </row>
-    <row r="589" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A589" s="1" t="s">
         <v>18</v>
       </c>
@@ -8416,7 +8428,7 @@
       </c>
       <c r="C589" s="1"/>
     </row>
-    <row r="590" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A590" s="1" t="s">
         <v>18</v>
       </c>
@@ -8425,7 +8437,7 @@
       </c>
       <c r="C590" s="1"/>
     </row>
-    <row r="591" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A591" s="1" t="s">
         <v>18</v>
       </c>
@@ -8434,7 +8446,7 @@
       </c>
       <c r="C591" s="1"/>
     </row>
-    <row r="592" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A592" s="1" t="s">
         <v>18</v>
       </c>
@@ -8443,7 +8455,7 @@
       </c>
       <c r="C592" s="1"/>
     </row>
-    <row r="593" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A593" s="1" t="s">
         <v>31</v>
       </c>
@@ -8452,7 +8464,7 @@
       </c>
       <c r="C593" s="1"/>
     </row>
-    <row r="594" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A594" s="1" t="s">
         <v>31</v>
       </c>
@@ -8461,7 +8473,7 @@
       </c>
       <c r="C594" s="1"/>
     </row>
-    <row r="595" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A595" s="1" t="s">
         <v>31</v>
       </c>
@@ -8470,7 +8482,7 @@
       </c>
       <c r="C595" s="1"/>
     </row>
-    <row r="596" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A596" s="1" t="s">
         <v>31</v>
       </c>
@@ -8479,7 +8491,7 @@
       </c>
       <c r="C596" s="1"/>
     </row>
-    <row r="597" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A597" s="1" t="s">
         <v>31</v>
       </c>
@@ -8488,7 +8500,7 @@
       </c>
       <c r="C597" s="1"/>
     </row>
-    <row r="598" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A598" s="1" t="s">
         <v>31</v>
       </c>
@@ -8497,7 +8509,7 @@
       </c>
       <c r="C598" s="1"/>
     </row>
-    <row r="599" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A599" s="1" t="s">
         <v>5</v>
       </c>
@@ -8506,7 +8518,7 @@
       </c>
       <c r="C599" s="1"/>
     </row>
-    <row r="600" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A600" s="1" t="s">
         <v>5</v>
       </c>
@@ -8515,7 +8527,7 @@
       </c>
       <c r="C600" s="1"/>
     </row>
-    <row r="601" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A601" s="1" t="s">
         <v>5</v>
       </c>
@@ -8524,7 +8536,7 @@
       </c>
       <c r="C601" s="1"/>
     </row>
-    <row r="602" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A602" s="1" t="s">
         <v>5</v>
       </c>
@@ -8533,7 +8545,7 @@
       </c>
       <c r="C602" s="1"/>
     </row>
-    <row r="603" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A603" s="1" t="s">
         <v>5</v>
       </c>
@@ -8542,7 +8554,7 @@
       </c>
       <c r="C603" s="1"/>
     </row>
-    <row r="604" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A604" s="1" t="s">
         <v>5</v>
       </c>
@@ -8551,7 +8563,7 @@
       </c>
       <c r="C604" s="1"/>
     </row>
-    <row r="605" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A605" s="1" t="s">
         <v>5</v>
       </c>
@@ -8560,7 +8572,7 @@
       </c>
       <c r="C605" s="1"/>
     </row>
-    <row r="606" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A606" s="1" t="s">
         <v>5</v>
       </c>
@@ -8569,7 +8581,7 @@
       </c>
       <c r="C606" s="1"/>
     </row>
-    <row r="607" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A607" s="1" t="s">
         <v>5</v>
       </c>
@@ -8578,7 +8590,7 @@
       </c>
       <c r="C607" s="1"/>
     </row>
-    <row r="608" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A608" s="1" t="s">
         <v>5</v>
       </c>
@@ -8587,7 +8599,7 @@
       </c>
       <c r="C608" s="1"/>
     </row>
-    <row r="609" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A609" s="1" t="s">
         <v>5</v>
       </c>
@@ -8596,7 +8608,7 @@
       </c>
       <c r="C609" s="1"/>
     </row>
-    <row r="610" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A610" s="1" t="s">
         <v>5</v>
       </c>
@@ -8605,7 +8617,7 @@
       </c>
       <c r="C610" s="1"/>
     </row>
-    <row r="611" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A611" s="1" t="s">
         <v>5</v>
       </c>
@@ -8614,7 +8626,7 @@
       </c>
       <c r="C611" s="1"/>
     </row>
-    <row r="612" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A612" s="1" t="s">
         <v>5</v>
       </c>
@@ -8623,7 +8635,7 @@
       </c>
       <c r="C612" s="1"/>
     </row>
-    <row r="613" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A613" s="1" t="s">
         <v>5</v>
       </c>
@@ -8632,7 +8644,7 @@
       </c>
       <c r="C613" s="1"/>
     </row>
-    <row r="614" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A614" s="1" t="s">
         <v>5</v>
       </c>
@@ -8641,7 +8653,7 @@
       </c>
       <c r="C614" s="1"/>
     </row>
-    <row r="615" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A615" s="1" t="s">
         <v>5</v>
       </c>
@@ -8650,7 +8662,7 @@
       </c>
       <c r="C615" s="1"/>
     </row>
-    <row r="616" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A616" s="1" t="s">
         <v>5</v>
       </c>
@@ -8659,7 +8671,7 @@
       </c>
       <c r="C616" s="1"/>
     </row>
-    <row r="617" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A617" s="1" t="s">
         <v>5</v>
       </c>
@@ -8668,7 +8680,7 @@
       </c>
       <c r="C617" s="1"/>
     </row>
-    <row r="618" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A618" s="1" t="s">
         <v>5</v>
       </c>
@@ -8677,7 +8689,7 @@
       </c>
       <c r="C618" s="1"/>
     </row>
-    <row r="619" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A619" s="1" t="s">
         <v>5</v>
       </c>
@@ -8686,7 +8698,7 @@
       </c>
       <c r="C619" s="1"/>
     </row>
-    <row r="620" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A620" s="1" t="s">
         <v>5</v>
       </c>
@@ -8695,7 +8707,7 @@
       </c>
       <c r="C620" s="1"/>
     </row>
-    <row r="621" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A621" s="1" t="s">
         <v>5</v>
       </c>
@@ -8704,7 +8716,7 @@
       </c>
       <c r="C621" s="1"/>
     </row>
-    <row r="622" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A622" s="1" t="s">
         <v>5</v>
       </c>
@@ -8713,7 +8725,7 @@
       </c>
       <c r="C622" s="1"/>
     </row>
-    <row r="623" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A623" s="1" t="s">
         <v>5</v>
       </c>
@@ -8722,7 +8734,7 @@
       </c>
       <c r="C623" s="1"/>
     </row>
-    <row r="624" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A624" s="1" t="s">
         <v>5</v>
       </c>
@@ -8731,7 +8743,7 @@
       </c>
       <c r="C624" s="1"/>
     </row>
-    <row r="625" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A625" s="1" t="s">
         <v>5</v>
       </c>
@@ -8740,7 +8752,7 @@
       </c>
       <c r="C625" s="1"/>
     </row>
-    <row r="626" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A626" s="1" t="s">
         <v>5</v>
       </c>
@@ -8749,7 +8761,7 @@
       </c>
       <c r="C626" s="1"/>
     </row>
-    <row r="627" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A627" s="1" t="s">
         <v>5</v>
       </c>
@@ -8758,7 +8770,7 @@
       </c>
       <c r="C627" s="1"/>
     </row>
-    <row r="628" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A628" s="1" t="s">
         <v>5</v>
       </c>
@@ -8767,7 +8779,7 @@
       </c>
       <c r="C628" s="1"/>
     </row>
-    <row r="629" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A629" s="1" t="s">
         <v>5</v>
       </c>
@@ -8776,7 +8788,7 @@
       </c>
       <c r="C629" s="1"/>
     </row>
-    <row r="630" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A630" s="1" t="s">
         <v>5</v>
       </c>
@@ -8785,7 +8797,7 @@
       </c>
       <c r="C630" s="1"/>
     </row>
-    <row r="631" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A631" s="1" t="s">
         <v>5</v>
       </c>
@@ -8794,7 +8806,7 @@
       </c>
       <c r="C631" s="1"/>
     </row>
-    <row r="632" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A632" s="1" t="s">
         <v>5</v>
       </c>
@@ -8803,7 +8815,7 @@
       </c>
       <c r="C632" s="1"/>
     </row>
-    <row r="633" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A633" s="1" t="s">
         <v>5</v>
       </c>
@@ -8812,7 +8824,7 @@
       </c>
       <c r="C633" s="1"/>
     </row>
-    <row r="634" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A634" s="1" t="s">
         <v>5</v>
       </c>
@@ -8821,7 +8833,7 @@
       </c>
       <c r="C634" s="1"/>
     </row>
-    <row r="635" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A635" s="1" t="s">
         <v>5</v>
       </c>
@@ -8830,7 +8842,7 @@
       </c>
       <c r="C635" s="1"/>
     </row>
-    <row r="636" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A636" s="1" t="s">
         <v>5</v>
       </c>
@@ -8839,7 +8851,7 @@
       </c>
       <c r="C636" s="1"/>
     </row>
-    <row r="637" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A637" s="1" t="s">
         <v>8</v>
       </c>
@@ -8848,7 +8860,7 @@
       </c>
       <c r="C637" s="1"/>
     </row>
-    <row r="638" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A638" s="1" t="s">
         <v>8</v>
       </c>
@@ -8857,7 +8869,7 @@
       </c>
       <c r="C638" s="1"/>
     </row>
-    <row r="639" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A639" s="1" t="s">
         <v>8</v>
       </c>
@@ -8866,7 +8878,7 @@
       </c>
       <c r="C639" s="1"/>
     </row>
-    <row r="640" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A640" s="1" t="s">
         <v>8</v>
       </c>
@@ -8875,7 +8887,7 @@
       </c>
       <c r="C640" s="1"/>
     </row>
-    <row r="641" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A641" s="1" t="s">
         <v>8</v>
       </c>
@@ -8884,7 +8896,7 @@
       </c>
       <c r="C641" s="1"/>
     </row>
-    <row r="642" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A642" s="1" t="s">
         <v>8</v>
       </c>
@@ -8893,7 +8905,7 @@
       </c>
       <c r="C642" s="1"/>
     </row>
-    <row r="643" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A643" s="1" t="s">
         <v>8</v>
       </c>
@@ -8902,7 +8914,7 @@
       </c>
       <c r="C643" s="1"/>
     </row>
-    <row r="644" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A644" s="1" t="s">
         <v>8</v>
       </c>
@@ -8911,7 +8923,7 @@
       </c>
       <c r="C644" s="1"/>
     </row>
-    <row r="645" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A645" s="1" t="s">
         <v>8</v>
       </c>
@@ -8920,7 +8932,7 @@
       </c>
       <c r="C645" s="1"/>
     </row>
-    <row r="646" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A646" s="1" t="s">
         <v>8</v>
       </c>
@@ -8929,7 +8941,7 @@
       </c>
       <c r="C646" s="1"/>
     </row>
-    <row r="647" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A647" s="1" t="s">
         <v>8</v>
       </c>
@@ -8938,7 +8950,7 @@
       </c>
       <c r="C647" s="1"/>
     </row>
-    <row r="648" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A648" s="1" t="s">
         <v>8</v>
       </c>
@@ -8947,7 +8959,7 @@
       </c>
       <c r="C648" s="1"/>
     </row>
-    <row r="649" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A649" s="1" t="s">
         <v>8</v>
       </c>
@@ -8956,7 +8968,7 @@
       </c>
       <c r="C649" s="1"/>
     </row>
-    <row r="650" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A650" s="1" t="s">
         <v>8</v>
       </c>
@@ -8965,7 +8977,7 @@
       </c>
       <c r="C650" s="1"/>
     </row>
-    <row r="651" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A651" s="1" t="s">
         <v>8</v>
       </c>
@@ -8974,7 +8986,7 @@
       </c>
       <c r="C651" s="1"/>
     </row>
-    <row r="652" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A652" s="1" t="s">
         <v>8</v>
       </c>
@@ -8983,7 +8995,7 @@
       </c>
       <c r="C652" s="1"/>
     </row>
-    <row r="653" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A653" s="1" t="s">
         <v>8</v>
       </c>
@@ -8992,7 +9004,7 @@
       </c>
       <c r="C653" s="1"/>
     </row>
-    <row r="654" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A654" s="1" t="s">
         <v>8</v>
       </c>
@@ -9001,7 +9013,7 @@
       </c>
       <c r="C654" s="1"/>
     </row>
-    <row r="655" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A655" s="1" t="s">
         <v>8</v>
       </c>
@@ -9010,7 +9022,7 @@
       </c>
       <c r="C655" s="1"/>
     </row>
-    <row r="656" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A656" s="1" t="s">
         <v>8</v>
       </c>
@@ -9019,7 +9031,7 @@
       </c>
       <c r="C656" s="1"/>
     </row>
-    <row r="657" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A657" s="1" t="s">
         <v>8</v>
       </c>
@@ -9028,7 +9040,7 @@
       </c>
       <c r="C657" s="1"/>
     </row>
-    <row r="658" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A658" s="1" t="s">
         <v>8</v>
       </c>
@@ -9037,7 +9049,7 @@
       </c>
       <c r="C658" s="1"/>
     </row>
-    <row r="659" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A659" s="1" t="s">
         <v>8</v>
       </c>
@@ -9046,7 +9058,7 @@
       </c>
       <c r="C659" s="1"/>
     </row>
-    <row r="660" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A660" s="1" t="s">
         <v>8</v>
       </c>
@@ -9055,7 +9067,7 @@
       </c>
       <c r="C660" s="1"/>
     </row>
-    <row r="661" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A661" s="1" t="s">
         <v>8</v>
       </c>
@@ -9064,7 +9076,7 @@
       </c>
       <c r="C661" s="1"/>
     </row>
-    <row r="662" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A662" s="1" t="s">
         <v>8</v>
       </c>
@@ -9073,7 +9085,7 @@
       </c>
       <c r="C662" s="1"/>
     </row>
-    <row r="663" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A663" s="1" t="s">
         <v>8</v>
       </c>
@@ -9082,7 +9094,7 @@
       </c>
       <c r="C663" s="1"/>
     </row>
-    <row r="664" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A664" s="1" t="s">
         <v>8</v>
       </c>
@@ -9091,7 +9103,7 @@
       </c>
       <c r="C664" s="1"/>
     </row>
-    <row r="665" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A665" s="1" t="s">
         <v>8</v>
       </c>
@@ -9100,7 +9112,7 @@
       </c>
       <c r="C665" s="1"/>
     </row>
-    <row r="666" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A666" s="1" t="s">
         <v>8</v>
       </c>
@@ -9109,7 +9121,7 @@
       </c>
       <c r="C666" s="1"/>
     </row>
-    <row r="667" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A667" s="1" t="s">
         <v>8</v>
       </c>
@@ -9118,7 +9130,7 @@
       </c>
       <c r="C667" s="1"/>
     </row>
-    <row r="668" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A668" s="1" t="s">
         <v>8</v>
       </c>
@@ -9127,7 +9139,7 @@
       </c>
       <c r="C668" s="1"/>
     </row>
-    <row r="669" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A669" s="1" t="s">
         <v>8</v>
       </c>
@@ -9136,7 +9148,7 @@
       </c>
       <c r="C669" s="1"/>
     </row>
-    <row r="670" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A670" s="1" t="s">
         <v>27</v>
       </c>
@@ -9145,7 +9157,7 @@
       </c>
       <c r="C670" s="1"/>
     </row>
-    <row r="671" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A671" s="1" t="s">
         <v>27</v>
       </c>
@@ -9154,7 +9166,7 @@
       </c>
       <c r="C671" s="1"/>
     </row>
-    <row r="672" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A672" s="1" t="s">
         <v>27</v>
       </c>
@@ -9163,7 +9175,7 @@
       </c>
       <c r="C672" s="1"/>
     </row>
-    <row r="673" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A673" s="1" t="s">
         <v>27</v>
       </c>
@@ -9172,7 +9184,7 @@
       </c>
       <c r="C673" s="1"/>
     </row>
-    <row r="674" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A674" s="1" t="s">
         <v>27</v>
       </c>
@@ -9181,7 +9193,7 @@
       </c>
       <c r="C674" s="1"/>
     </row>
-    <row r="675" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A675" s="1" t="s">
         <v>27</v>
       </c>
@@ -9190,7 +9202,7 @@
       </c>
       <c r="C675" s="1"/>
     </row>
-    <row r="676" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A676" s="1" t="s">
         <v>27</v>
       </c>
@@ -9199,7 +9211,7 @@
       </c>
       <c r="C676" s="1"/>
     </row>
-    <row r="677" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A677" s="1" t="s">
         <v>27</v>
       </c>
@@ -9208,7 +9220,7 @@
       </c>
       <c r="C677" s="1"/>
     </row>
-    <row r="678" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A678" s="1" t="s">
         <v>4</v>
       </c>
@@ -9217,7 +9229,7 @@
       </c>
       <c r="C678" s="1"/>
     </row>
-    <row r="679" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A679" s="1" t="s">
         <v>4</v>
       </c>
@@ -9226,7 +9238,7 @@
       </c>
       <c r="C679" s="1"/>
     </row>
-    <row r="680" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A680" s="1" t="s">
         <v>4</v>
       </c>
@@ -9235,7 +9247,7 @@
       </c>
       <c r="C680" s="1"/>
     </row>
-    <row r="681" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A681" s="1" t="s">
         <v>4</v>
       </c>
@@ -9244,7 +9256,7 @@
       </c>
       <c r="C681" s="1"/>
     </row>
-    <row r="682" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A682" s="1" t="s">
         <v>4</v>
       </c>
@@ -9253,7 +9265,7 @@
       </c>
       <c r="C682" s="1"/>
     </row>
-    <row r="683" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A683" s="1" t="s">
         <v>4</v>
       </c>
@@ -9262,7 +9274,7 @@
       </c>
       <c r="C683" s="1"/>
     </row>
-    <row r="684" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A684" s="1" t="s">
         <v>4</v>
       </c>
@@ -9271,7 +9283,7 @@
       </c>
       <c r="C684" s="1"/>
     </row>
-    <row r="685" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A685" s="1" t="s">
         <v>4</v>
       </c>
@@ -9280,7 +9292,7 @@
       </c>
       <c r="C685" s="1"/>
     </row>
-    <row r="686" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A686" s="1" t="s">
         <v>4</v>
       </c>
@@ -9289,7 +9301,7 @@
       </c>
       <c r="C686" s="1"/>
     </row>
-    <row r="687" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A687" s="1" t="s">
         <v>4</v>
       </c>
@@ -9298,7 +9310,7 @@
       </c>
       <c r="C687" s="1"/>
     </row>
-    <row r="688" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A688" s="1" t="s">
         <v>4</v>
       </c>
@@ -9307,7 +9319,7 @@
       </c>
       <c r="C688" s="1"/>
     </row>
-    <row r="689" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A689" s="1" t="s">
         <v>4</v>
       </c>
@@ -9316,7 +9328,7 @@
       </c>
       <c r="C689" s="1"/>
     </row>
-    <row r="690" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A690" s="1" t="s">
         <v>4</v>
       </c>
@@ -9325,7 +9337,7 @@
       </c>
       <c r="C690" s="1"/>
     </row>
-    <row r="691" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A691" s="1" t="s">
         <v>4</v>
       </c>
@@ -9334,7 +9346,7 @@
       </c>
       <c r="C691" s="1"/>
     </row>
-    <row r="692" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A692" s="1" t="s">
         <v>4</v>
       </c>
@@ -9343,7 +9355,7 @@
       </c>
       <c r="C692" s="1"/>
     </row>
-    <row r="693" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A693" s="1" t="s">
         <v>4</v>
       </c>
@@ -9352,7 +9364,7 @@
       </c>
       <c r="C693" s="1"/>
     </row>
-    <row r="694" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A694" s="1" t="s">
         <v>4</v>
       </c>
@@ -9361,7 +9373,7 @@
       </c>
       <c r="C694" s="1"/>
     </row>
-    <row r="695" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A695" s="1" t="s">
         <v>4</v>
       </c>
@@ -9370,7 +9382,7 @@
       </c>
       <c r="C695" s="1"/>
     </row>
-    <row r="696" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A696" s="1" t="s">
         <v>4</v>
       </c>
@@ -9379,7 +9391,7 @@
       </c>
       <c r="C696" s="1"/>
     </row>
-    <row r="697" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A697" s="1" t="s">
         <v>4</v>
       </c>
@@ -9388,7 +9400,7 @@
       </c>
       <c r="C697" s="1"/>
     </row>
-    <row r="698" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A698" s="1" t="s">
         <v>4</v>
       </c>
@@ -9397,7 +9409,7 @@
       </c>
       <c r="C698" s="1"/>
     </row>
-    <row r="699" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A699" s="1" t="s">
         <v>4</v>
       </c>
@@ -9406,7 +9418,7 @@
       </c>
       <c r="C699" s="1"/>
     </row>
-    <row r="700" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A700" s="1" t="s">
         <v>4</v>
       </c>
@@ -9415,7 +9427,7 @@
       </c>
       <c r="C700" s="1"/>
     </row>
-    <row r="701" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A701" s="1" t="s">
         <v>4</v>
       </c>
@@ -9424,7 +9436,7 @@
       </c>
       <c r="C701" s="1"/>
     </row>
-    <row r="702" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A702" s="1" t="s">
         <v>4</v>
       </c>
@@ -9433,7 +9445,7 @@
       </c>
       <c r="C702" s="1"/>
     </row>
-    <row r="703" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A703" s="1" t="s">
         <v>4</v>
       </c>
@@ -9442,7 +9454,7 @@
       </c>
       <c r="C703" s="1"/>
     </row>
-    <row r="704" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A704" s="1" t="s">
         <v>4</v>
       </c>
@@ -9451,7 +9463,7 @@
       </c>
       <c r="C704" s="1"/>
     </row>
-    <row r="705" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A705" s="1" t="s">
         <v>4</v>
       </c>
@@ -9460,7 +9472,7 @@
       </c>
       <c r="C705" s="1"/>
     </row>
-    <row r="706" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A706" s="1" t="s">
         <v>4</v>
       </c>
@@ -9469,7 +9481,7 @@
       </c>
       <c r="C706" s="1"/>
     </row>
-    <row r="707" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A707" s="1" t="s">
         <v>4</v>
       </c>
@@ -9478,7 +9490,7 @@
       </c>
       <c r="C707" s="1"/>
     </row>
-    <row r="708" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A708" s="1" t="s">
         <v>4</v>
       </c>
@@ -9487,7 +9499,7 @@
       </c>
       <c r="C708" s="1"/>
     </row>
-    <row r="709" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A709" s="1" t="s">
         <v>4</v>
       </c>
@@ -9496,7 +9508,7 @@
       </c>
       <c r="C709" s="1"/>
     </row>
-    <row r="710" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A710" s="1" t="s">
         <v>4</v>
       </c>
@@ -9505,7 +9517,7 @@
       </c>
       <c r="C710" s="1"/>
     </row>
-    <row r="711" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A711" s="1" t="s">
         <v>4</v>
       </c>
@@ -9514,7 +9526,7 @@
       </c>
       <c r="C711" s="1"/>
     </row>
-    <row r="712" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A712" s="1" t="s">
         <v>4</v>
       </c>
@@ -9523,7 +9535,7 @@
       </c>
       <c r="C712" s="1"/>
     </row>
-    <row r="713" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A713" s="1" t="s">
         <v>4</v>
       </c>
@@ -9532,7 +9544,7 @@
       </c>
       <c r="C713" s="1"/>
     </row>
-    <row r="714" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A714" s="1" t="s">
         <v>4</v>
       </c>
@@ -9541,7 +9553,7 @@
       </c>
       <c r="C714" s="1"/>
     </row>
-    <row r="715" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A715" s="1" t="s">
         <v>4</v>
       </c>
@@ -9550,7 +9562,7 @@
       </c>
       <c r="C715" s="1"/>
     </row>
-    <row r="716" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A716" s="1" t="s">
         <v>4</v>
       </c>
@@ -9559,7 +9571,7 @@
       </c>
       <c r="C716" s="1"/>
     </row>
-    <row r="717" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A717" s="1" t="s">
         <v>4</v>
       </c>
@@ -9568,7 +9580,7 @@
       </c>
       <c r="C717" s="1"/>
     </row>
-    <row r="718" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A718" s="1" t="s">
         <v>4</v>
       </c>
@@ -9577,7 +9589,7 @@
       </c>
       <c r="C718" s="1"/>
     </row>
-    <row r="719" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A719" s="1" t="s">
         <v>4</v>
       </c>
@@ -9586,7 +9598,7 @@
       </c>
       <c r="C719" s="1"/>
     </row>
-    <row r="720" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A720" s="1" t="s">
         <v>4</v>
       </c>
@@ -9595,7 +9607,7 @@
       </c>
       <c r="C720" s="1"/>
     </row>
-    <row r="721" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A721" s="1" t="s">
         <v>4</v>
       </c>
@@ -9604,7 +9616,7 @@
       </c>
       <c r="C721" s="1"/>
     </row>
-    <row r="722" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A722" s="1" t="s">
         <v>4</v>
       </c>
@@ -9613,7 +9625,7 @@
       </c>
       <c r="C722" s="1"/>
     </row>
-    <row r="723" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A723" s="1" t="s">
         <v>4</v>
       </c>
@@ -9622,7 +9634,7 @@
       </c>
       <c r="C723" s="1"/>
     </row>
-    <row r="724" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A724" s="1" t="s">
         <v>4</v>
       </c>
@@ -9631,7 +9643,7 @@
       </c>
       <c r="C724" s="1"/>
     </row>
-    <row r="725" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A725" s="1" t="s">
         <v>4</v>
       </c>
@@ -9640,7 +9652,7 @@
       </c>
       <c r="C725" s="1"/>
     </row>
-    <row r="726" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A726" s="1" t="s">
         <v>4</v>
       </c>
@@ -9649,7 +9661,7 @@
       </c>
       <c r="C726" s="1"/>
     </row>
-    <row r="727" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A727" s="1" t="s">
         <v>4</v>
       </c>
@@ -9658,7 +9670,7 @@
       </c>
       <c r="C727" s="1"/>
     </row>
-    <row r="728" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A728" s="1" t="s">
         <v>4</v>
       </c>
@@ -9667,7 +9679,7 @@
       </c>
       <c r="C728" s="1"/>
     </row>
-    <row r="729" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A729" s="1" t="s">
         <v>4</v>
       </c>
@@ -9676,7 +9688,7 @@
       </c>
       <c r="C729" s="1"/>
     </row>
-    <row r="730" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A730" s="1" t="s">
         <v>4</v>
       </c>
@@ -9685,7 +9697,7 @@
       </c>
       <c r="C730" s="1"/>
     </row>
-    <row r="731" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A731" s="1" t="s">
         <v>4</v>
       </c>
@@ -9694,7 +9706,7 @@
       </c>
       <c r="C731" s="1"/>
     </row>
-    <row r="732" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A732" s="1" t="s">
         <v>4</v>
       </c>
@@ -9703,7 +9715,7 @@
       </c>
       <c r="C732" s="1"/>
     </row>
-    <row r="733" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A733" s="1" t="s">
         <v>4</v>
       </c>
@@ -9712,7 +9724,7 @@
       </c>
       <c r="C733" s="1"/>
     </row>
-    <row r="734" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A734" s="1" t="s">
         <v>4</v>
       </c>
@@ -9721,7 +9733,7 @@
       </c>
       <c r="C734" s="1"/>
     </row>
-    <row r="735" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A735" s="1" t="s">
         <v>4</v>
       </c>
@@ -9730,7 +9742,7 @@
       </c>
       <c r="C735" s="1"/>
     </row>
-    <row r="736" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A736" s="1" t="s">
         <v>4</v>
       </c>
@@ -9739,7 +9751,7 @@
       </c>
       <c r="C736" s="1"/>
     </row>
-    <row r="737" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A737" s="1" t="s">
         <v>4</v>
       </c>
@@ -9748,7 +9760,7 @@
       </c>
       <c r="C737" s="1"/>
     </row>
-    <row r="738" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A738" s="1" t="s">
         <v>4</v>
       </c>
@@ -9757,7 +9769,7 @@
       </c>
       <c r="C738" s="1"/>
     </row>
-    <row r="739" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A739" s="1" t="s">
         <v>4</v>
       </c>
@@ -9766,7 +9778,7 @@
       </c>
       <c r="C739" s="1"/>
     </row>
-    <row r="740" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A740" s="1" t="s">
         <v>4</v>
       </c>
@@ -9775,7 +9787,7 @@
       </c>
       <c r="C740" s="1"/>
     </row>
-    <row r="741" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A741" s="1" t="s">
         <v>4</v>
       </c>
@@ -9784,7 +9796,7 @@
       </c>
       <c r="C741" s="1"/>
     </row>
-    <row r="742" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A742" s="1" t="s">
         <v>4</v>
       </c>
@@ -9793,7 +9805,7 @@
       </c>
       <c r="C742" s="1"/>
     </row>
-    <row r="743" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A743" s="1" t="s">
         <v>4</v>
       </c>
@@ -9802,7 +9814,7 @@
       </c>
       <c r="C743" s="1"/>
     </row>
-    <row r="744" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A744" s="1" t="s">
         <v>4</v>
       </c>
@@ -9811,7 +9823,7 @@
       </c>
       <c r="C744" s="1"/>
     </row>
-    <row r="745" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A745" s="1" t="s">
         <v>4</v>
       </c>
@@ -9820,7 +9832,7 @@
       </c>
       <c r="C745" s="1"/>
     </row>
-    <row r="746" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A746" s="1" t="s">
         <v>4</v>
       </c>
@@ -9829,7 +9841,7 @@
       </c>
       <c r="C746" s="1"/>
     </row>
-    <row r="747" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A747" s="1" t="s">
         <v>4</v>
       </c>
@@ -9838,7 +9850,7 @@
       </c>
       <c r="C747" s="1"/>
     </row>
-    <row r="748" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A748" s="1" t="s">
         <v>4</v>
       </c>
@@ -9847,7 +9859,7 @@
       </c>
       <c r="C748" s="1"/>
     </row>
-    <row r="749" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A749" s="1" t="s">
         <v>4</v>
       </c>
@@ -9856,7 +9868,7 @@
       </c>
       <c r="C749" s="1"/>
     </row>
-    <row r="750" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A750" s="1" t="s">
         <v>4</v>
       </c>
@@ -9865,7 +9877,7 @@
       </c>
       <c r="C750" s="1"/>
     </row>
-    <row r="751" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A751" s="1" t="s">
         <v>4</v>
       </c>
@@ -9874,7 +9886,7 @@
       </c>
       <c r="C751" s="1"/>
     </row>
-    <row r="752" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A752" s="1" t="s">
         <v>4</v>
       </c>
@@ -9883,7 +9895,7 @@
       </c>
       <c r="C752" s="1"/>
     </row>
-    <row r="753" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A753" s="1" t="s">
         <v>20</v>
       </c>
@@ -9892,7 +9904,7 @@
       </c>
       <c r="C753" s="1"/>
     </row>
-    <row r="754" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A754" s="1" t="s">
         <v>20</v>
       </c>
@@ -9901,7 +9913,7 @@
       </c>
       <c r="C754" s="1"/>
     </row>
-    <row r="755" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A755" s="1" t="s">
         <v>20</v>
       </c>
@@ -9910,7 +9922,7 @@
       </c>
       <c r="C755" s="1"/>
     </row>
-    <row r="756" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A756" s="1" t="s">
         <v>20</v>
       </c>
@@ -9919,7 +9931,7 @@
       </c>
       <c r="C756" s="1"/>
     </row>
-    <row r="757" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A757" s="1" t="s">
         <v>20</v>
       </c>
@@ -9928,7 +9940,7 @@
       </c>
       <c r="C757" s="1"/>
     </row>
-    <row r="758" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A758" s="1" t="s">
         <v>20</v>
       </c>
@@ -9937,7 +9949,7 @@
       </c>
       <c r="C758" s="1"/>
     </row>
-    <row r="759" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A759" s="1" t="s">
         <v>20</v>
       </c>
@@ -9946,7 +9958,7 @@
       </c>
       <c r="C759" s="1"/>
     </row>
-    <row r="760" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A760" s="1" t="s">
         <v>20</v>
       </c>
@@ -9955,7 +9967,7 @@
       </c>
       <c r="C760" s="1"/>
     </row>
-    <row r="761" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A761" s="1" t="s">
         <v>20</v>
       </c>
@@ -9964,7 +9976,7 @@
       </c>
       <c r="C761" s="1"/>
     </row>
-    <row r="762" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A762" s="1" t="s">
         <v>20</v>
       </c>
@@ -9973,7 +9985,7 @@
       </c>
       <c r="C762" s="1"/>
     </row>
-    <row r="763" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A763" s="1" t="s">
         <v>20</v>
       </c>
@@ -9982,7 +9994,7 @@
       </c>
       <c r="C763" s="1"/>
     </row>
-    <row r="764" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A764" s="1" t="s">
         <v>20</v>
       </c>
@@ -9991,7 +10003,7 @@
       </c>
       <c r="C764" s="1"/>
     </row>
-    <row r="765" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A765" s="1" t="s">
         <v>20</v>
       </c>
@@ -10000,7 +10012,7 @@
       </c>
       <c r="C765" s="1"/>
     </row>
-    <row r="766" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A766" s="1" t="s">
         <v>13</v>
       </c>
@@ -10009,7 +10021,7 @@
       </c>
       <c r="C766" s="1"/>
     </row>
-    <row r="767" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A767" s="1" t="s">
         <v>13</v>
       </c>
@@ -10018,7 +10030,7 @@
       </c>
       <c r="C767" s="1"/>
     </row>
-    <row r="768" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A768" s="1" t="s">
         <v>13</v>
       </c>
@@ -10027,7 +10039,7 @@
       </c>
       <c r="C768" s="1"/>
     </row>
-    <row r="769" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A769" s="1" t="s">
         <v>13</v>
       </c>
@@ -10036,7 +10048,7 @@
       </c>
       <c r="C769" s="1"/>
     </row>
-    <row r="770" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A770" s="1" t="s">
         <v>13</v>
       </c>
@@ -10045,7 +10057,7 @@
       </c>
       <c r="C770" s="1"/>
     </row>
-    <row r="771" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A771" s="1" t="s">
         <v>13</v>
       </c>
@@ -10054,7 +10066,7 @@
       </c>
       <c r="C771" s="1"/>
     </row>
-    <row r="772" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A772" s="1" t="s">
         <v>13</v>
       </c>
@@ -10063,7 +10075,7 @@
       </c>
       <c r="C772" s="1"/>
     </row>
-    <row r="773" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A773" s="1" t="s">
         <v>13</v>
       </c>
@@ -10072,7 +10084,7 @@
       </c>
       <c r="C773" s="1"/>
     </row>
-    <row r="774" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A774" s="1" t="s">
         <v>13</v>
       </c>
@@ -10081,7 +10093,7 @@
       </c>
       <c r="C774" s="1"/>
     </row>
-    <row r="775" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A775" s="1" t="s">
         <v>13</v>
       </c>
@@ -10090,7 +10102,7 @@
       </c>
       <c r="C775" s="1"/>
     </row>
-    <row r="776" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A776" s="1" t="s">
         <v>13</v>
       </c>
@@ -10099,7 +10111,7 @@
       </c>
       <c r="C776" s="1"/>
     </row>
-    <row r="777" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A777" s="1" t="s">
         <v>13</v>
       </c>
@@ -10108,7 +10120,7 @@
       </c>
       <c r="C777" s="1"/>
     </row>
-    <row r="778" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A778" s="1" t="s">
         <v>13</v>
       </c>
@@ -10117,7 +10129,7 @@
       </c>
       <c r="C778" s="1"/>
     </row>
-    <row r="779" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A779" s="1" t="s">
         <v>13</v>
       </c>
@@ -10126,7 +10138,7 @@
       </c>
       <c r="C779" s="1"/>
     </row>
-    <row r="780" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A780" s="1" t="s">
         <v>13</v>
       </c>
@@ -10135,7 +10147,7 @@
       </c>
       <c r="C780" s="1"/>
     </row>
-    <row r="781" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A781" s="1" t="s">
         <v>13</v>
       </c>
@@ -10144,7 +10156,7 @@
       </c>
       <c r="C781" s="1"/>
     </row>
-    <row r="782" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A782" s="1" t="s">
         <v>13</v>
       </c>
@@ -10153,7 +10165,7 @@
       </c>
       <c r="C782" s="1"/>
     </row>
-    <row r="783" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A783" s="1" t="s">
         <v>13</v>
       </c>
@@ -10162,7 +10174,7 @@
       </c>
       <c r="C783" s="1"/>
     </row>
-    <row r="784" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A784" s="1" t="s">
         <v>13</v>
       </c>
@@ -10171,7 +10183,7 @@
       </c>
       <c r="C784" s="1"/>
     </row>
-    <row r="785" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A785" s="1" t="s">
         <v>13</v>
       </c>
@@ -10180,7 +10192,7 @@
       </c>
       <c r="C785" s="1"/>
     </row>
-    <row r="786" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A786" s="1" t="s">
         <v>13</v>
       </c>
@@ -10189,7 +10201,7 @@
       </c>
       <c r="C786" s="1"/>
     </row>
-    <row r="787" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A787" s="1" t="s">
         <v>13</v>
       </c>
@@ -10198,7 +10210,7 @@
       </c>
       <c r="C787" s="1"/>
     </row>
-    <row r="788" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A788" s="1" t="s">
         <v>13</v>
       </c>
@@ -10209,15 +10221,47 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:C788" xr:uid="{6FDBB0FF-B482-4668-8D23-A62BD1FE53B2}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Assam"/>
-      </filters>
-    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A31:C57">
       <sortCondition ref="B1:B788"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49FF997F-2996-47DB-9E6D-08C1DA22C50A}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="26.28515625" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" t="s">
+        <v>826</v>
+      </c>
+      <c r="C1" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>828</v>
+      </c>
+      <c r="B2" t="s">
+        <v>829</v>
+      </c>
+      <c r="C2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/json-datasets/csv/State_District-Relation.xlsx
+++ b/json-datasets/csv/State_District-Relation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GITHUB\ifsc-code-india\json-datasets\csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DE231C3-318C-4B42-B9D3-0BBCAA212FF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77D5599F-D39E-49AB-A9A7-66B3DA82B029}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="State" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="District-old New Name" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">District!$A$1:$C$788</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">District!$A$1:$C$789</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">State!$A$1:$A$38</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="830">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1623" uniqueCount="831">
   <si>
     <t>STATE</t>
   </si>
@@ -2535,6 +2535,9 @@
   </si>
   <si>
     <t>Gurgaon</t>
+  </si>
+  <si>
+    <t>KHARAGPUR</t>
   </si>
 </sst>
 </file>
@@ -3118,7 +3121,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FDBB0FF-B482-4668-8D23-A62BD1FE53B2}">
-  <dimension ref="A1:C788"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:C789"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36" bestFit="1" customWidth="1"/>
@@ -3136,7 +3140,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>21</v>
       </c>
@@ -3145,7 +3149,7 @@
       </c>
       <c r="C2" s="1"/>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>21</v>
       </c>
@@ -3154,7 +3158,7 @@
       </c>
       <c r="C3" s="1"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>21</v>
       </c>
@@ -3163,7 +3167,7 @@
       </c>
       <c r="C4" s="1"/>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
@@ -3172,7 +3176,7 @@
       </c>
       <c r="C5" s="1"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -3181,7 +3185,7 @@
       </c>
       <c r="C6" s="1"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -3190,7 +3194,7 @@
       </c>
       <c r="C7" s="1"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
@@ -3199,7 +3203,7 @@
       </c>
       <c r="C8" s="1"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
@@ -3208,7 +3212,7 @@
       </c>
       <c r="C9" s="1"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
@@ -3217,7 +3221,7 @@
       </c>
       <c r="C10" s="1"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
@@ -3226,7 +3230,7 @@
       </c>
       <c r="C11" s="1"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
@@ -3235,7 +3239,7 @@
       </c>
       <c r="C12" s="1"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>10</v>
       </c>
@@ -3244,7 +3248,7 @@
       </c>
       <c r="C13" s="1"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>10</v>
       </c>
@@ -3253,7 +3257,7 @@
       </c>
       <c r="C14" s="1"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>10</v>
       </c>
@@ -3262,7 +3266,7 @@
       </c>
       <c r="C15" s="1"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>10</v>
       </c>
@@ -3271,7 +3275,7 @@
       </c>
       <c r="C16" s="1"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>10</v>
       </c>
@@ -3280,7 +3284,7 @@
       </c>
       <c r="C17" s="1"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>10</v>
       </c>
@@ -3289,7 +3293,7 @@
       </c>
       <c r="C18" s="1"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>10</v>
       </c>
@@ -3298,7 +3302,7 @@
       </c>
       <c r="C19" s="1"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>10</v>
       </c>
@@ -3307,7 +3311,7 @@
       </c>
       <c r="C20" s="1"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>10</v>
       </c>
@@ -3316,7 +3320,7 @@
       </c>
       <c r="C21" s="1"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>10</v>
       </c>
@@ -3325,7 +3329,7 @@
       </c>
       <c r="C22" s="1"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>10</v>
       </c>
@@ -3334,7 +3338,7 @@
       </c>
       <c r="C23" s="1"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>10</v>
       </c>
@@ -3343,7 +3347,7 @@
       </c>
       <c r="C24" s="1"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>10</v>
       </c>
@@ -3352,7 +3356,7 @@
       </c>
       <c r="C25" s="1"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>10</v>
       </c>
@@ -3361,7 +3365,7 @@
       </c>
       <c r="C26" s="1"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>10</v>
       </c>
@@ -3370,7 +3374,7 @@
       </c>
       <c r="C27" s="1"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>10</v>
       </c>
@@ -3379,7 +3383,7 @@
       </c>
       <c r="C28" s="1"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>10</v>
       </c>
@@ -3388,7 +3392,7 @@
       </c>
       <c r="C29" s="1"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>10</v>
       </c>
@@ -3397,7 +3401,7 @@
       </c>
       <c r="C30" s="1"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>32</v>
       </c>
@@ -3406,7 +3410,7 @@
       </c>
       <c r="C31" s="1"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>32</v>
       </c>
@@ -3415,7 +3419,7 @@
       </c>
       <c r="C32" s="1"/>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>32</v>
       </c>
@@ -3424,7 +3428,7 @@
       </c>
       <c r="C33" s="1"/>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>32</v>
       </c>
@@ -3433,7 +3437,7 @@
       </c>
       <c r="C34" s="1"/>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>32</v>
       </c>
@@ -3442,7 +3446,7 @@
       </c>
       <c r="C35" s="1"/>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>32</v>
       </c>
@@ -3451,7 +3455,7 @@
       </c>
       <c r="C36" s="1"/>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>32</v>
       </c>
@@ -3460,7 +3464,7 @@
       </c>
       <c r="C37" s="1"/>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>32</v>
       </c>
@@ -3469,7 +3473,7 @@
       </c>
       <c r="C38" s="1"/>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3478,7 +3482,7 @@
       </c>
       <c r="C39" s="1"/>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>32</v>
       </c>
@@ -3487,7 +3491,7 @@
       </c>
       <c r="C40" s="1"/>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>32</v>
       </c>
@@ -3496,7 +3500,7 @@
       </c>
       <c r="C41" s="1"/>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>32</v>
       </c>
@@ -3505,7 +3509,7 @@
       </c>
       <c r="C42" s="1"/>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>32</v>
       </c>
@@ -3514,7 +3518,7 @@
       </c>
       <c r="C43" s="1"/>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>32</v>
       </c>
@@ -3523,7 +3527,7 @@
       </c>
       <c r="C44" s="1"/>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>32</v>
       </c>
@@ -3532,7 +3536,7 @@
       </c>
       <c r="C45" s="1"/>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>32</v>
       </c>
@@ -3541,7 +3545,7 @@
       </c>
       <c r="C46" s="1"/>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>32</v>
       </c>
@@ -3550,7 +3554,7 @@
       </c>
       <c r="C47" s="1"/>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>32</v>
       </c>
@@ -3559,7 +3563,7 @@
       </c>
       <c r="C48" s="1"/>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>32</v>
       </c>
@@ -3568,7 +3572,7 @@
       </c>
       <c r="C49" s="1"/>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>32</v>
       </c>
@@ -3577,7 +3581,7 @@
       </c>
       <c r="C50" s="1"/>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>32</v>
       </c>
@@ -3586,7 +3590,7 @@
       </c>
       <c r="C51" s="1"/>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>32</v>
       </c>
@@ -3595,7 +3599,7 @@
       </c>
       <c r="C52" s="1"/>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>32</v>
       </c>
@@ -3604,7 +3608,7 @@
       </c>
       <c r="C53" s="1"/>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>32</v>
       </c>
@@ -3613,7 +3617,7 @@
       </c>
       <c r="C54" s="1"/>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>32</v>
       </c>
@@ -3622,7 +3626,7 @@
       </c>
       <c r="C55" s="1"/>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>32</v>
       </c>
@@ -3631,7 +3635,7 @@
       </c>
       <c r="C56" s="1"/>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>32</v>
       </c>
@@ -3640,7 +3644,7 @@
       </c>
       <c r="C57" s="1"/>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>22</v>
       </c>
@@ -3649,7 +3653,7 @@
       </c>
       <c r="C58" s="1"/>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>22</v>
       </c>
@@ -3658,7 +3662,7 @@
       </c>
       <c r="C59" s="1"/>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>22</v>
       </c>
@@ -3667,7 +3671,7 @@
       </c>
       <c r="C60" s="1"/>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>22</v>
       </c>
@@ -3676,7 +3680,7 @@
       </c>
       <c r="C61" s="1"/>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>22</v>
       </c>
@@ -3685,7 +3689,7 @@
       </c>
       <c r="C62" s="1"/>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>22</v>
       </c>
@@ -3694,7 +3698,7 @@
       </c>
       <c r="C63" s="1"/>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>22</v>
       </c>
@@ -3703,7 +3707,7 @@
       </c>
       <c r="C64" s="1"/>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>22</v>
       </c>
@@ -3712,7 +3716,7 @@
       </c>
       <c r="C65" s="1"/>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>22</v>
       </c>
@@ -3721,7 +3725,7 @@
       </c>
       <c r="C66" s="1"/>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>22</v>
       </c>
@@ -3730,7 +3734,7 @@
       </c>
       <c r="C67" s="1"/>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>22</v>
       </c>
@@ -3739,7 +3743,7 @@
       </c>
       <c r="C68" s="1"/>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>22</v>
       </c>
@@ -3748,7 +3752,7 @@
       </c>
       <c r="C69" s="1"/>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>22</v>
       </c>
@@ -3757,7 +3761,7 @@
       </c>
       <c r="C70" s="1"/>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>22</v>
       </c>
@@ -3766,7 +3770,7 @@
       </c>
       <c r="C71" s="1"/>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>22</v>
       </c>
@@ -3775,7 +3779,7 @@
       </c>
       <c r="C72" s="1"/>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>22</v>
       </c>
@@ -3784,7 +3788,7 @@
       </c>
       <c r="C73" s="1"/>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>22</v>
       </c>
@@ -3793,7 +3797,7 @@
       </c>
       <c r="C74" s="1"/>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>22</v>
       </c>
@@ -3802,7 +3806,7 @@
       </c>
       <c r="C75" s="1"/>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>22</v>
       </c>
@@ -3811,7 +3815,7 @@
       </c>
       <c r="C76" s="1"/>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>22</v>
       </c>
@@ -3820,7 +3824,7 @@
       </c>
       <c r="C77" s="1"/>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>22</v>
       </c>
@@ -3829,7 +3833,7 @@
       </c>
       <c r="C78" s="1"/>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>22</v>
       </c>
@@ -3838,7 +3842,7 @@
       </c>
       <c r="C79" s="1"/>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>22</v>
       </c>
@@ -3847,7 +3851,7 @@
       </c>
       <c r="C80" s="1"/>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>22</v>
       </c>
@@ -3856,7 +3860,7 @@
       </c>
       <c r="C81" s="1"/>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>22</v>
       </c>
@@ -3865,7 +3869,7 @@
       </c>
       <c r="C82" s="1"/>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>22</v>
       </c>
@@ -3874,7 +3878,7 @@
       </c>
       <c r="C83" s="1"/>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>22</v>
       </c>
@@ -3883,7 +3887,7 @@
       </c>
       <c r="C84" s="1"/>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>22</v>
       </c>
@@ -3892,7 +3896,7 @@
       </c>
       <c r="C85" s="1"/>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>22</v>
       </c>
@@ -3901,7 +3905,7 @@
       </c>
       <c r="C86" s="1"/>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>22</v>
       </c>
@@ -3910,7 +3914,7 @@
       </c>
       <c r="C87" s="1"/>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>22</v>
       </c>
@@ -3919,7 +3923,7 @@
       </c>
       <c r="C88" s="1"/>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>22</v>
       </c>
@@ -3928,7 +3932,7 @@
       </c>
       <c r="C89" s="1"/>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>22</v>
       </c>
@@ -3937,7 +3941,7 @@
       </c>
       <c r="C90" s="1"/>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>22</v>
       </c>
@@ -3946,7 +3950,7 @@
       </c>
       <c r="C91" s="1"/>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>22</v>
       </c>
@@ -3955,7 +3959,7 @@
       </c>
       <c r="C92" s="1"/>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>12</v>
       </c>
@@ -3964,7 +3968,7 @@
       </c>
       <c r="C93" s="1"/>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>12</v>
       </c>
@@ -3973,7 +3977,7 @@
       </c>
       <c r="C94" s="1"/>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>12</v>
       </c>
@@ -3982,7 +3986,7 @@
       </c>
       <c r="C95" s="1"/>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>12</v>
       </c>
@@ -3991,7 +3995,7 @@
       </c>
       <c r="C96" s="1"/>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>12</v>
       </c>
@@ -4000,7 +4004,7 @@
       </c>
       <c r="C97" s="1"/>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>12</v>
       </c>
@@ -4009,7 +4013,7 @@
       </c>
       <c r="C98" s="1"/>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>12</v>
       </c>
@@ -4018,7 +4022,7 @@
       </c>
       <c r="C99" s="1"/>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>12</v>
       </c>
@@ -4027,7 +4031,7 @@
       </c>
       <c r="C100" s="1"/>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>12</v>
       </c>
@@ -4036,7 +4040,7 @@
       </c>
       <c r="C101" s="1"/>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>12</v>
       </c>
@@ -4045,7 +4049,7 @@
       </c>
       <c r="C102" s="1"/>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>12</v>
       </c>
@@ -4054,7 +4058,7 @@
       </c>
       <c r="C103" s="1"/>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>12</v>
       </c>
@@ -4063,7 +4067,7 @@
       </c>
       <c r="C104" s="1"/>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>12</v>
       </c>
@@ -4072,7 +4076,7 @@
       </c>
       <c r="C105" s="1"/>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>12</v>
       </c>
@@ -4081,7 +4085,7 @@
       </c>
       <c r="C106" s="1"/>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>12</v>
       </c>
@@ -4090,7 +4094,7 @@
       </c>
       <c r="C107" s="1"/>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>12</v>
       </c>
@@ -4099,7 +4103,7 @@
       </c>
       <c r="C108" s="1"/>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>12</v>
       </c>
@@ -4108,7 +4112,7 @@
       </c>
       <c r="C109" s="1"/>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>12</v>
       </c>
@@ -4117,7 +4121,7 @@
       </c>
       <c r="C110" s="1"/>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>12</v>
       </c>
@@ -4126,7 +4130,7 @@
       </c>
       <c r="C111" s="1"/>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>12</v>
       </c>
@@ -4135,7 +4139,7 @@
       </c>
       <c r="C112" s="1"/>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>12</v>
       </c>
@@ -4144,7 +4148,7 @@
       </c>
       <c r="C113" s="1"/>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>12</v>
       </c>
@@ -4153,7 +4157,7 @@
       </c>
       <c r="C114" s="1"/>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>12</v>
       </c>
@@ -4162,7 +4166,7 @@
       </c>
       <c r="C115" s="1"/>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>12</v>
       </c>
@@ -4171,7 +4175,7 @@
       </c>
       <c r="C116" s="1"/>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>12</v>
       </c>
@@ -4180,7 +4184,7 @@
       </c>
       <c r="C117" s="1"/>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>12</v>
       </c>
@@ -4189,7 +4193,7 @@
       </c>
       <c r="C118" s="1"/>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>12</v>
       </c>
@@ -4198,7 +4202,7 @@
       </c>
       <c r="C119" s="1"/>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>12</v>
       </c>
@@ -4207,7 +4211,7 @@
       </c>
       <c r="C120" s="1"/>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>12</v>
       </c>
@@ -4216,7 +4220,7 @@
       </c>
       <c r="C121" s="1"/>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>12</v>
       </c>
@@ -4225,7 +4229,7 @@
       </c>
       <c r="C122" s="1"/>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>12</v>
       </c>
@@ -4234,7 +4238,7 @@
       </c>
       <c r="C123" s="1"/>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>12</v>
       </c>
@@ -4243,7 +4247,7 @@
       </c>
       <c r="C124" s="1"/>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>12</v>
       </c>
@@ -4252,7 +4256,7 @@
       </c>
       <c r="C125" s="1"/>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>12</v>
       </c>
@@ -4261,7 +4265,7 @@
       </c>
       <c r="C126" s="1"/>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>12</v>
       </c>
@@ -4270,7 +4274,7 @@
       </c>
       <c r="C127" s="1"/>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>12</v>
       </c>
@@ -4279,7 +4283,7 @@
       </c>
       <c r="C128" s="1"/>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>12</v>
       </c>
@@ -4288,7 +4292,7 @@
       </c>
       <c r="C129" s="1"/>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>12</v>
       </c>
@@ -4297,7 +4301,7 @@
       </c>
       <c r="C130" s="1"/>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>23</v>
       </c>
@@ -4306,7 +4310,7 @@
       </c>
       <c r="C131" s="1"/>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>167</v>
       </c>
@@ -4315,7 +4319,7 @@
       </c>
       <c r="C132" s="1"/>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>167</v>
       </c>
@@ -4324,7 +4328,7 @@
       </c>
       <c r="C133" s="1"/>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>167</v>
       </c>
@@ -4333,7 +4337,7 @@
       </c>
       <c r="C134" s="1"/>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>167</v>
       </c>
@@ -4342,7 +4346,7 @@
       </c>
       <c r="C135" s="1"/>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>167</v>
       </c>
@@ -4351,7 +4355,7 @@
       </c>
       <c r="C136" s="1"/>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>167</v>
       </c>
@@ -4360,7 +4364,7 @@
       </c>
       <c r="C137" s="1"/>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>167</v>
       </c>
@@ -4369,7 +4373,7 @@
       </c>
       <c r="C138" s="1"/>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>167</v>
       </c>
@@ -4378,7 +4382,7 @@
       </c>
       <c r="C139" s="1"/>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>167</v>
       </c>
@@ -4387,7 +4391,7 @@
       </c>
       <c r="C140" s="1"/>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>167</v>
       </c>
@@ -4396,7 +4400,7 @@
       </c>
       <c r="C141" s="1"/>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>167</v>
       </c>
@@ -4405,7 +4409,7 @@
       </c>
       <c r="C142" s="1"/>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>167</v>
       </c>
@@ -4414,7 +4418,7 @@
       </c>
       <c r="C143" s="1"/>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>167</v>
       </c>
@@ -4423,7 +4427,7 @@
       </c>
       <c r="C144" s="1"/>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>167</v>
       </c>
@@ -4432,7 +4436,7 @@
       </c>
       <c r="C145" s="1"/>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>167</v>
       </c>
@@ -4441,7 +4445,7 @@
       </c>
       <c r="C146" s="1"/>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>167</v>
       </c>
@@ -4450,7 +4454,7 @@
       </c>
       <c r="C147" s="1"/>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>167</v>
       </c>
@@ -4459,7 +4463,7 @@
       </c>
       <c r="C148" s="1"/>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>167</v>
       </c>
@@ -4468,7 +4472,7 @@
       </c>
       <c r="C149" s="1"/>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>167</v>
       </c>
@@ -4477,7 +4481,7 @@
       </c>
       <c r="C150" s="1"/>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>167</v>
       </c>
@@ -4486,7 +4490,7 @@
       </c>
       <c r="C151" s="1"/>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>167</v>
       </c>
@@ -4495,7 +4499,7 @@
       </c>
       <c r="C152" s="1"/>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>167</v>
       </c>
@@ -4504,7 +4508,7 @@
       </c>
       <c r="C153" s="1"/>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>167</v>
       </c>
@@ -4513,7 +4517,7 @@
       </c>
       <c r="C154" s="1"/>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>167</v>
       </c>
@@ -4522,7 +4526,7 @@
       </c>
       <c r="C155" s="1"/>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>167</v>
       </c>
@@ -4531,7 +4535,7 @@
       </c>
       <c r="C156" s="1"/>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>167</v>
       </c>
@@ -4540,7 +4544,7 @@
       </c>
       <c r="C157" s="1"/>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
         <v>167</v>
       </c>
@@ -4549,7 +4553,7 @@
       </c>
       <c r="C158" s="1"/>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
         <v>167</v>
       </c>
@@ -4558,7 +4562,7 @@
       </c>
       <c r="C159" s="1"/>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
         <v>167</v>
       </c>
@@ -4567,7 +4571,7 @@
       </c>
       <c r="C160" s="1"/>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
         <v>167</v>
       </c>
@@ -4576,7 +4580,7 @@
       </c>
       <c r="C161" s="1"/>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
         <v>167</v>
       </c>
@@ -4585,7 +4589,7 @@
       </c>
       <c r="C162" s="1"/>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
         <v>167</v>
       </c>
@@ -4594,7 +4598,7 @@
       </c>
       <c r="C163" s="1"/>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
         <v>167</v>
       </c>
@@ -4603,7 +4607,7 @@
       </c>
       <c r="C164" s="1"/>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
         <v>35</v>
       </c>
@@ -4612,7 +4616,7 @@
       </c>
       <c r="C165" s="1"/>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
         <v>33</v>
       </c>
@@ -4621,7 +4625,7 @@
       </c>
       <c r="C166" s="1"/>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
         <v>33</v>
       </c>
@@ -4630,7 +4634,7 @@
       </c>
       <c r="C167" s="1"/>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
         <v>15</v>
       </c>
@@ -4639,7 +4643,7 @@
       </c>
       <c r="C168" s="1"/>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
         <v>15</v>
       </c>
@@ -4648,7 +4652,7 @@
       </c>
       <c r="C169" s="1"/>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
         <v>15</v>
       </c>
@@ -4657,7 +4661,7 @@
       </c>
       <c r="C170" s="1"/>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
         <v>15</v>
       </c>
@@ -4666,7 +4670,7 @@
       </c>
       <c r="C171" s="1"/>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
         <v>15</v>
       </c>
@@ -4675,7 +4679,7 @@
       </c>
       <c r="C172" s="1"/>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
         <v>15</v>
       </c>
@@ -4684,7 +4688,7 @@
       </c>
       <c r="C173" s="1"/>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
         <v>15</v>
       </c>
@@ -4693,7 +4697,7 @@
       </c>
       <c r="C174" s="1"/>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
         <v>15</v>
       </c>
@@ -4702,7 +4706,7 @@
       </c>
       <c r="C175" s="1"/>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
         <v>15</v>
       </c>
@@ -4711,7 +4715,7 @@
       </c>
       <c r="C176" s="1"/>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
         <v>15</v>
       </c>
@@ -4720,7 +4724,7 @@
       </c>
       <c r="C177" s="1"/>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
         <v>15</v>
       </c>
@@ -4729,7 +4733,7 @@
       </c>
       <c r="C178" s="1"/>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
         <v>28</v>
       </c>
@@ -4738,7 +4742,7 @@
       </c>
       <c r="C179" s="1"/>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
         <v>28</v>
       </c>
@@ -4747,7 +4751,7 @@
       </c>
       <c r="C180" s="1"/>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
         <v>2</v>
       </c>
@@ -4756,7 +4760,7 @@
       </c>
       <c r="C181" s="1"/>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
         <v>2</v>
       </c>
@@ -4765,7 +4769,7 @@
       </c>
       <c r="C182" s="1"/>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
         <v>2</v>
       </c>
@@ -4774,7 +4778,7 @@
       </c>
       <c r="C183" s="1"/>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
         <v>2</v>
       </c>
@@ -4783,7 +4787,7 @@
       </c>
       <c r="C184" s="1"/>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
         <v>2</v>
       </c>
@@ -4792,7 +4796,7 @@
       </c>
       <c r="C185" s="1"/>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
         <v>2</v>
       </c>
@@ -4801,7 +4805,7 @@
       </c>
       <c r="C186" s="1"/>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
         <v>2</v>
       </c>
@@ -4810,7 +4814,7 @@
       </c>
       <c r="C187" s="1"/>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
         <v>2</v>
       </c>
@@ -4819,7 +4823,7 @@
       </c>
       <c r="C188" s="1"/>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
         <v>2</v>
       </c>
@@ -4828,7 +4832,7 @@
       </c>
       <c r="C189" s="1"/>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
         <v>2</v>
       </c>
@@ -4837,7 +4841,7 @@
       </c>
       <c r="C190" s="1"/>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
         <v>2</v>
       </c>
@@ -4846,7 +4850,7 @@
       </c>
       <c r="C191" s="1"/>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
         <v>2</v>
       </c>
@@ -4855,7 +4859,7 @@
       </c>
       <c r="C192" s="1"/>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
         <v>2</v>
       </c>
@@ -4864,7 +4868,7 @@
       </c>
       <c r="C193" s="1"/>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
         <v>2</v>
       </c>
@@ -4873,7 +4877,7 @@
       </c>
       <c r="C194" s="1"/>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
         <v>2</v>
       </c>
@@ -4882,7 +4886,7 @@
       </c>
       <c r="C195" s="1"/>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
         <v>2</v>
       </c>
@@ -4891,7 +4895,7 @@
       </c>
       <c r="C196" s="1"/>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
         <v>2</v>
       </c>
@@ -4900,7 +4904,7 @@
       </c>
       <c r="C197" s="1"/>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
         <v>2</v>
       </c>
@@ -4909,7 +4913,7 @@
       </c>
       <c r="C198" s="1"/>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
         <v>2</v>
       </c>
@@ -4918,7 +4922,7 @@
       </c>
       <c r="C199" s="1"/>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
         <v>2</v>
       </c>
@@ -4927,7 +4931,7 @@
       </c>
       <c r="C200" s="1"/>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
         <v>2</v>
       </c>
@@ -4936,7 +4940,7 @@
       </c>
       <c r="C201" s="1"/>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
         <v>2</v>
       </c>
@@ -4945,7 +4949,7 @@
       </c>
       <c r="C202" s="1"/>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
         <v>2</v>
       </c>
@@ -4954,7 +4958,7 @@
       </c>
       <c r="C203" s="1"/>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
         <v>2</v>
       </c>
@@ -4963,7 +4967,7 @@
       </c>
       <c r="C204" s="1"/>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
         <v>2</v>
       </c>
@@ -4972,7 +4976,7 @@
       </c>
       <c r="C205" s="1"/>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
         <v>2</v>
       </c>
@@ -4981,7 +4985,7 @@
       </c>
       <c r="C206" s="1"/>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
         <v>2</v>
       </c>
@@ -4990,7 +4994,7 @@
       </c>
       <c r="C207" s="1"/>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
         <v>2</v>
       </c>
@@ -4999,7 +5003,7 @@
       </c>
       <c r="C208" s="1"/>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
         <v>2</v>
       </c>
@@ -5008,7 +5012,7 @@
       </c>
       <c r="C209" s="1"/>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
         <v>2</v>
       </c>
@@ -5017,7 +5021,7 @@
       </c>
       <c r="C210" s="1"/>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
         <v>2</v>
       </c>
@@ -5026,7 +5030,7 @@
       </c>
       <c r="C211" s="1"/>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
         <v>2</v>
       </c>
@@ -5035,7 +5039,7 @@
       </c>
       <c r="C212" s="1"/>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
         <v>2</v>
       </c>
@@ -5044,7 +5048,7 @@
       </c>
       <c r="C213" s="1"/>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
         <v>9</v>
       </c>
@@ -5053,7 +5057,7 @@
       </c>
       <c r="C214" s="1"/>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
         <v>9</v>
       </c>
@@ -5062,7 +5066,7 @@
       </c>
       <c r="C215" s="1"/>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
         <v>9</v>
       </c>
@@ -5071,7 +5075,7 @@
       </c>
       <c r="C216" s="1"/>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
         <v>9</v>
       </c>
@@ -5080,7 +5084,7 @@
       </c>
       <c r="C217" s="1"/>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
         <v>9</v>
       </c>
@@ -5089,7 +5093,7 @@
       </c>
       <c r="C218" s="1"/>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
         <v>9</v>
       </c>
@@ -5098,7 +5102,7 @@
       </c>
       <c r="C219" s="1"/>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
         <v>9</v>
       </c>
@@ -5107,7 +5111,7 @@
       </c>
       <c r="C220" s="1"/>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
         <v>9</v>
       </c>
@@ -5116,7 +5120,7 @@
       </c>
       <c r="C221" s="1"/>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
         <v>9</v>
       </c>
@@ -5125,7 +5129,7 @@
       </c>
       <c r="C222" s="1"/>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
         <v>9</v>
       </c>
@@ -5134,7 +5138,7 @@
       </c>
       <c r="C223" s="1"/>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
         <v>9</v>
       </c>
@@ -5143,7 +5147,7 @@
       </c>
       <c r="C224" s="1"/>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
         <v>9</v>
       </c>
@@ -5152,7 +5156,7 @@
       </c>
       <c r="C225" s="1"/>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
         <v>9</v>
       </c>
@@ -5161,7 +5165,7 @@
       </c>
       <c r="C226" s="1"/>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
         <v>9</v>
       </c>
@@ -5170,7 +5174,7 @@
       </c>
       <c r="C227" s="1"/>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
         <v>9</v>
       </c>
@@ -5179,7 +5183,7 @@
       </c>
       <c r="C228" s="1"/>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
         <v>9</v>
       </c>
@@ -5188,7 +5192,7 @@
       </c>
       <c r="C229" s="1"/>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
         <v>9</v>
       </c>
@@ -5197,7 +5201,7 @@
       </c>
       <c r="C230" s="1"/>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
         <v>9</v>
       </c>
@@ -5206,7 +5210,7 @@
       </c>
       <c r="C231" s="1"/>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
         <v>9</v>
       </c>
@@ -5215,7 +5219,7 @@
       </c>
       <c r="C232" s="1"/>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
         <v>9</v>
       </c>
@@ -5224,7 +5228,7 @@
       </c>
       <c r="C233" s="1"/>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
         <v>9</v>
       </c>
@@ -5233,7 +5237,7 @@
       </c>
       <c r="C234" s="1"/>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
         <v>9</v>
       </c>
@@ -5242,7 +5246,7 @@
       </c>
       <c r="C235" s="1"/>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
         <v>7</v>
       </c>
@@ -5251,7 +5255,7 @@
       </c>
       <c r="C236" s="1"/>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
         <v>7</v>
       </c>
@@ -5260,7 +5264,7 @@
       </c>
       <c r="C237" s="1"/>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
         <v>7</v>
       </c>
@@ -5269,7 +5273,7 @@
       </c>
       <c r="C238" s="1"/>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
         <v>7</v>
       </c>
@@ -5278,7 +5282,7 @@
       </c>
       <c r="C239" s="1"/>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
         <v>7</v>
       </c>
@@ -5287,7 +5291,7 @@
       </c>
       <c r="C240" s="1"/>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
         <v>7</v>
       </c>
@@ -5296,7 +5300,7 @@
       </c>
       <c r="C241" s="1"/>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
         <v>7</v>
       </c>
@@ -5305,7 +5309,7 @@
       </c>
       <c r="C242" s="1"/>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
         <v>7</v>
       </c>
@@ -5314,7 +5318,7 @@
       </c>
       <c r="C243" s="1"/>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
         <v>7</v>
       </c>
@@ -5323,7 +5327,7 @@
       </c>
       <c r="C244" s="1"/>
     </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
         <v>7</v>
       </c>
@@ -5332,7 +5336,7 @@
       </c>
       <c r="C245" s="1"/>
     </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
         <v>7</v>
       </c>
@@ -5341,7 +5345,7 @@
       </c>
       <c r="C246" s="1"/>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
         <v>7</v>
       </c>
@@ -5350,7 +5354,7 @@
       </c>
       <c r="C247" s="1"/>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
         <v>11</v>
       </c>
@@ -5359,7 +5363,7 @@
       </c>
       <c r="C248" s="1"/>
     </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
         <v>11</v>
       </c>
@@ -5368,7 +5372,7 @@
       </c>
       <c r="C249" s="1"/>
     </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
         <v>11</v>
       </c>
@@ -5377,7 +5381,7 @@
       </c>
       <c r="C250" s="1"/>
     </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
         <v>11</v>
       </c>
@@ -5386,7 +5390,7 @@
       </c>
       <c r="C251" s="1"/>
     </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
         <v>11</v>
       </c>
@@ -5395,7 +5399,7 @@
       </c>
       <c r="C252" s="1"/>
     </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
         <v>11</v>
       </c>
@@ -5404,7 +5408,7 @@
       </c>
       <c r="C253" s="1"/>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
         <v>11</v>
       </c>
@@ -5413,7 +5417,7 @@
       </c>
       <c r="C254" s="1"/>
     </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
         <v>11</v>
       </c>
@@ -5422,7 +5426,7 @@
       </c>
       <c r="C255" s="1"/>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
         <v>11</v>
       </c>
@@ -5431,7 +5435,7 @@
       </c>
       <c r="C256" s="1"/>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
         <v>11</v>
       </c>
@@ -5440,7 +5444,7 @@
       </c>
       <c r="C257" s="1"/>
     </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
         <v>11</v>
       </c>
@@ -5449,7 +5453,7 @@
       </c>
       <c r="C258" s="1"/>
     </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
         <v>11</v>
       </c>
@@ -5458,7 +5462,7 @@
       </c>
       <c r="C259" s="1"/>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
         <v>11</v>
       </c>
@@ -5467,7 +5471,7 @@
       </c>
       <c r="C260" s="1"/>
     </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
         <v>11</v>
       </c>
@@ -5476,7 +5480,7 @@
       </c>
       <c r="C261" s="1"/>
     </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
         <v>11</v>
       </c>
@@ -5485,7 +5489,7 @@
       </c>
       <c r="C262" s="1"/>
     </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
         <v>11</v>
       </c>
@@ -5494,7 +5498,7 @@
       </c>
       <c r="C263" s="1"/>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
         <v>11</v>
       </c>
@@ -5503,7 +5507,7 @@
       </c>
       <c r="C264" s="1"/>
     </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
         <v>11</v>
       </c>
@@ -5512,7 +5516,7 @@
       </c>
       <c r="C265" s="1"/>
     </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
         <v>11</v>
       </c>
@@ -5521,7 +5525,7 @@
       </c>
       <c r="C266" s="1"/>
     </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
         <v>11</v>
       </c>
@@ -5530,7 +5534,7 @@
       </c>
       <c r="C267" s="1"/>
     </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
         <v>19</v>
       </c>
@@ -5539,7 +5543,7 @@
       </c>
       <c r="C268" s="1"/>
     </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
         <v>19</v>
       </c>
@@ -5548,7 +5552,7 @@
       </c>
       <c r="C269" s="1"/>
     </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
         <v>19</v>
       </c>
@@ -5557,7 +5561,7 @@
       </c>
       <c r="C270" s="1"/>
     </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
         <v>19</v>
       </c>
@@ -5566,7 +5570,7 @@
       </c>
       <c r="C271" s="1"/>
     </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
         <v>19</v>
       </c>
@@ -5575,7 +5579,7 @@
       </c>
       <c r="C272" s="1"/>
     </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
         <v>19</v>
       </c>
@@ -5584,7 +5588,7 @@
       </c>
       <c r="C273" s="1"/>
     </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
         <v>19</v>
       </c>
@@ -5593,7 +5597,7 @@
       </c>
       <c r="C274" s="1"/>
     </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
         <v>19</v>
       </c>
@@ -5602,7 +5606,7 @@
       </c>
       <c r="C275" s="1"/>
     </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
         <v>19</v>
       </c>
@@ -5611,7 +5615,7 @@
       </c>
       <c r="C276" s="1"/>
     </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
         <v>19</v>
       </c>
@@ -5620,7 +5624,7 @@
       </c>
       <c r="C277" s="1"/>
     </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
         <v>19</v>
       </c>
@@ -5629,7 +5633,7 @@
       </c>
       <c r="C278" s="1"/>
     </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
         <v>19</v>
       </c>
@@ -5638,7 +5642,7 @@
       </c>
       <c r="C279" s="1"/>
     </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
         <v>19</v>
       </c>
@@ -5647,7 +5651,7 @@
       </c>
       <c r="C280" s="1"/>
     </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
         <v>19</v>
       </c>
@@ -5656,7 +5660,7 @@
       </c>
       <c r="C281" s="1"/>
     </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
         <v>19</v>
       </c>
@@ -5665,7 +5669,7 @@
       </c>
       <c r="C282" s="1"/>
     </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
         <v>19</v>
       </c>
@@ -5674,7 +5678,7 @@
       </c>
       <c r="C283" s="1"/>
     </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
         <v>19</v>
       </c>
@@ -5683,7 +5687,7 @@
       </c>
       <c r="C284" s="1"/>
     </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
         <v>19</v>
       </c>
@@ -5692,7 +5696,7 @@
       </c>
       <c r="C285" s="1"/>
     </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
         <v>19</v>
       </c>
@@ -5701,7 +5705,7 @@
       </c>
       <c r="C286" s="1"/>
     </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
         <v>19</v>
       </c>
@@ -5710,7 +5714,7 @@
       </c>
       <c r="C287" s="1"/>
     </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
         <v>19</v>
       </c>
@@ -5719,7 +5723,7 @@
       </c>
       <c r="C288" s="1"/>
     </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
         <v>19</v>
       </c>
@@ -5728,7 +5732,7 @@
       </c>
       <c r="C289" s="1"/>
     </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
         <v>19</v>
       </c>
@@ -5737,7 +5741,7 @@
       </c>
       <c r="C290" s="1"/>
     </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
         <v>19</v>
       </c>
@@ -5746,7 +5750,7 @@
       </c>
       <c r="C291" s="1"/>
     </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
         <v>3</v>
       </c>
@@ -5755,7 +5759,7 @@
       </c>
       <c r="C292" s="1"/>
     </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
         <v>3</v>
       </c>
@@ -5764,7 +5768,7 @@
       </c>
       <c r="C293" s="1"/>
     </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
         <v>3</v>
       </c>
@@ -5773,7 +5777,7 @@
       </c>
       <c r="C294" s="1"/>
     </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
         <v>3</v>
       </c>
@@ -5782,7 +5786,7 @@
       </c>
       <c r="C295" s="1"/>
     </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
         <v>3</v>
       </c>
@@ -5791,7 +5795,7 @@
       </c>
       <c r="C296" s="1"/>
     </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
         <v>3</v>
       </c>
@@ -5800,7 +5804,7 @@
       </c>
       <c r="C297" s="1"/>
     </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
         <v>3</v>
       </c>
@@ -5809,7 +5813,7 @@
       </c>
       <c r="C298" s="1"/>
     </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
         <v>3</v>
       </c>
@@ -5818,7 +5822,7 @@
       </c>
       <c r="C299" s="1"/>
     </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
         <v>3</v>
       </c>
@@ -5827,7 +5831,7 @@
       </c>
       <c r="C300" s="1"/>
     </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
         <v>3</v>
       </c>
@@ -5836,7 +5840,7 @@
       </c>
       <c r="C301" s="1"/>
     </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
         <v>3</v>
       </c>
@@ -5845,7 +5849,7 @@
       </c>
       <c r="C302" s="1"/>
     </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
         <v>3</v>
       </c>
@@ -5854,7 +5858,7 @@
       </c>
       <c r="C303" s="1"/>
     </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="s">
         <v>3</v>
       </c>
@@ -5863,7 +5867,7 @@
       </c>
       <c r="C304" s="1"/>
     </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="s">
         <v>3</v>
       </c>
@@ -5872,7 +5876,7 @@
       </c>
       <c r="C305" s="1"/>
     </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="s">
         <v>3</v>
       </c>
@@ -5881,7 +5885,7 @@
       </c>
       <c r="C306" s="1"/>
     </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
         <v>3</v>
       </c>
@@ -5890,7 +5894,7 @@
       </c>
       <c r="C307" s="1"/>
     </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" s="1" t="s">
         <v>3</v>
       </c>
@@ -5899,7 +5903,7 @@
       </c>
       <c r="C308" s="1"/>
     </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="s">
         <v>3</v>
       </c>
@@ -5908,7 +5912,7 @@
       </c>
       <c r="C309" s="1"/>
     </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="s">
         <v>3</v>
       </c>
@@ -5917,7 +5921,7 @@
       </c>
       <c r="C310" s="1"/>
     </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
         <v>3</v>
       </c>
@@ -5926,7 +5930,7 @@
       </c>
       <c r="C311" s="1"/>
     </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
         <v>3</v>
       </c>
@@ -5935,7 +5939,7 @@
       </c>
       <c r="C312" s="1"/>
     </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
         <v>3</v>
       </c>
@@ -5944,7 +5948,7 @@
       </c>
       <c r="C313" s="1"/>
     </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="s">
         <v>3</v>
       </c>
@@ -5953,7 +5957,7 @@
       </c>
       <c r="C314" s="1"/>
     </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315" s="1" t="s">
         <v>3</v>
       </c>
@@ -5962,7 +5966,7 @@
       </c>
       <c r="C315" s="1"/>
     </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
         <v>3</v>
       </c>
@@ -5971,7 +5975,7 @@
       </c>
       <c r="C316" s="1"/>
     </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
         <v>3</v>
       </c>
@@ -5980,7 +5984,7 @@
       </c>
       <c r="C317" s="1"/>
     </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
         <v>3</v>
       </c>
@@ -5989,7 +5993,7 @@
       </c>
       <c r="C318" s="1"/>
     </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
         <v>3</v>
       </c>
@@ -5998,7 +6002,7 @@
       </c>
       <c r="C319" s="1"/>
     </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
         <v>3</v>
       </c>
@@ -6007,7 +6011,7 @@
       </c>
       <c r="C320" s="1"/>
     </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
         <v>3</v>
       </c>
@@ -6016,7 +6020,7 @@
       </c>
       <c r="C321" s="1"/>
     </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
         <v>3</v>
       </c>
@@ -6025,7 +6029,7 @@
       </c>
       <c r="C322" s="1"/>
     </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323" s="1" t="s">
         <v>16</v>
       </c>
@@ -6034,7 +6038,7 @@
       </c>
       <c r="C323" s="1"/>
     </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324" s="1" t="s">
         <v>16</v>
       </c>
@@ -6043,7 +6047,7 @@
       </c>
       <c r="C324" s="1"/>
     </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="s">
         <v>16</v>
       </c>
@@ -6052,7 +6056,7 @@
       </c>
       <c r="C325" s="1"/>
     </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="s">
         <v>16</v>
       </c>
@@ -6061,7 +6065,7 @@
       </c>
       <c r="C326" s="1"/>
     </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
         <v>16</v>
       </c>
@@ -6070,7 +6074,7 @@
       </c>
       <c r="C327" s="1"/>
     </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
         <v>16</v>
       </c>
@@ -6079,7 +6083,7 @@
       </c>
       <c r="C328" s="1"/>
     </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
         <v>16</v>
       </c>
@@ -6088,7 +6092,7 @@
       </c>
       <c r="C329" s="1"/>
     </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
         <v>16</v>
       </c>
@@ -6097,7 +6101,7 @@
       </c>
       <c r="C330" s="1"/>
     </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
         <v>16</v>
       </c>
@@ -6106,7 +6110,7 @@
       </c>
       <c r="C331" s="1"/>
     </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
         <v>16</v>
       </c>
@@ -6115,7 +6119,7 @@
       </c>
       <c r="C332" s="1"/>
     </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
         <v>16</v>
       </c>
@@ -6124,7 +6128,7 @@
       </c>
       <c r="C333" s="1"/>
     </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334" s="1" t="s">
         <v>16</v>
       </c>
@@ -6133,7 +6137,7 @@
       </c>
       <c r="C334" s="1"/>
     </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="s">
         <v>16</v>
       </c>
@@ -6142,7 +6146,7 @@
       </c>
       <c r="C335" s="1"/>
     </row>
-    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="s">
         <v>16</v>
       </c>
@@ -6151,7 +6155,7 @@
       </c>
       <c r="C336" s="1"/>
     </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
         <v>36</v>
       </c>
@@ -6160,7 +6164,7 @@
       </c>
       <c r="C337" s="1"/>
     </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
         <v>36</v>
       </c>
@@ -6169,7 +6173,7 @@
       </c>
       <c r="C338" s="1"/>
     </row>
-    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
         <v>25</v>
       </c>
@@ -6178,7 +6182,7 @@
       </c>
       <c r="C339" s="1"/>
     </row>
-    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340" s="1" t="s">
         <v>14</v>
       </c>
@@ -6187,7 +6191,7 @@
       </c>
       <c r="C340" s="1"/>
     </row>
-    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" s="1" t="s">
         <v>14</v>
       </c>
@@ -6196,7 +6200,7 @@
       </c>
       <c r="C341" s="1"/>
     </row>
-    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342" s="1" t="s">
         <v>14</v>
       </c>
@@ -6205,7 +6209,7 @@
       </c>
       <c r="C342" s="1"/>
     </row>
-    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343" s="1" t="s">
         <v>14</v>
       </c>
@@ -6214,7 +6218,7 @@
       </c>
       <c r="C343" s="1"/>
     </row>
-    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344" s="1" t="s">
         <v>14</v>
       </c>
@@ -6223,7 +6227,7 @@
       </c>
       <c r="C344" s="1"/>
     </row>
-    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
         <v>14</v>
       </c>
@@ -6232,7 +6236,7 @@
       </c>
       <c r="C345" s="1"/>
     </row>
-    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
         <v>14</v>
       </c>
@@ -6241,7 +6245,7 @@
       </c>
       <c r="C346" s="1"/>
     </row>
-    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
         <v>14</v>
       </c>
@@ -6250,7 +6254,7 @@
       </c>
       <c r="C347" s="1"/>
     </row>
-    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348" s="1" t="s">
         <v>14</v>
       </c>
@@ -6259,7 +6263,7 @@
       </c>
       <c r="C348" s="1"/>
     </row>
-    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="s">
         <v>14</v>
       </c>
@@ -6268,7 +6272,7 @@
       </c>
       <c r="C349" s="1"/>
     </row>
-    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
         <v>14</v>
       </c>
@@ -6277,7 +6281,7 @@
       </c>
       <c r="C350" s="1"/>
     </row>
-    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="s">
         <v>14</v>
       </c>
@@ -6286,7 +6290,7 @@
       </c>
       <c r="C351" s="1"/>
     </row>
-    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="s">
         <v>14</v>
       </c>
@@ -6295,7 +6299,7 @@
       </c>
       <c r="C352" s="1"/>
     </row>
-    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="s">
         <v>14</v>
       </c>
@@ -6304,7 +6308,7 @@
       </c>
       <c r="C353" s="1"/>
     </row>
-    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="s">
         <v>14</v>
       </c>
@@ -6313,7 +6317,7 @@
       </c>
       <c r="C354" s="1"/>
     </row>
-    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="s">
         <v>14</v>
       </c>
@@ -6322,7 +6326,7 @@
       </c>
       <c r="C355" s="1"/>
     </row>
-    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356" s="1" t="s">
         <v>14</v>
       </c>
@@ -6331,7 +6335,7 @@
       </c>
       <c r="C356" s="1"/>
     </row>
-    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357" s="1" t="s">
         <v>14</v>
       </c>
@@ -6340,7 +6344,7 @@
       </c>
       <c r="C357" s="1"/>
     </row>
-    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358" s="1" t="s">
         <v>14</v>
       </c>
@@ -6349,7 +6353,7 @@
       </c>
       <c r="C358" s="1"/>
     </row>
-    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359" s="1" t="s">
         <v>14</v>
       </c>
@@ -6358,7 +6362,7 @@
       </c>
       <c r="C359" s="1"/>
     </row>
-    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360" s="1" t="s">
         <v>14</v>
       </c>
@@ -6367,7 +6371,7 @@
       </c>
       <c r="C360" s="1"/>
     </row>
-    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361" s="1" t="s">
         <v>14</v>
       </c>
@@ -6376,7 +6380,7 @@
       </c>
       <c r="C361" s="1"/>
     </row>
-    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362" s="1" t="s">
         <v>14</v>
       </c>
@@ -6385,7 +6389,7 @@
       </c>
       <c r="C362" s="1"/>
     </row>
-    <row r="363" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363" s="1" t="s">
         <v>14</v>
       </c>
@@ -6394,7 +6398,7 @@
       </c>
       <c r="C363" s="1"/>
     </row>
-    <row r="364" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364" s="1" t="s">
         <v>14</v>
       </c>
@@ -6403,7 +6407,7 @@
       </c>
       <c r="C364" s="1"/>
     </row>
-    <row r="365" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365" s="1" t="s">
         <v>14</v>
       </c>
@@ -6412,7 +6416,7 @@
       </c>
       <c r="C365" s="1"/>
     </row>
-    <row r="366" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366" s="1" t="s">
         <v>14</v>
       </c>
@@ -6421,7 +6425,7 @@
       </c>
       <c r="C366" s="1"/>
     </row>
-    <row r="367" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367" s="1" t="s">
         <v>14</v>
       </c>
@@ -6430,7 +6434,7 @@
       </c>
       <c r="C367" s="1"/>
     </row>
-    <row r="368" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368" s="1" t="s">
         <v>14</v>
       </c>
@@ -6439,7 +6443,7 @@
       </c>
       <c r="C368" s="1"/>
     </row>
-    <row r="369" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369" s="1" t="s">
         <v>14</v>
       </c>
@@ -6448,7 +6452,7 @@
       </c>
       <c r="C369" s="1"/>
     </row>
-    <row r="370" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370" s="1" t="s">
         <v>14</v>
       </c>
@@ -6457,7 +6461,7 @@
       </c>
       <c r="C370" s="1"/>
     </row>
-    <row r="371" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371" s="1" t="s">
         <v>14</v>
       </c>
@@ -6466,7 +6470,7 @@
       </c>
       <c r="C371" s="1"/>
     </row>
-    <row r="372" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372" s="1" t="s">
         <v>14</v>
       </c>
@@ -6475,7 +6479,7 @@
       </c>
       <c r="C372" s="1"/>
     </row>
-    <row r="373" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373" s="1" t="s">
         <v>14</v>
       </c>
@@ -6484,7 +6488,7 @@
       </c>
       <c r="C373" s="1"/>
     </row>
-    <row r="374" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374" s="1" t="s">
         <v>14</v>
       </c>
@@ -6493,7 +6497,7 @@
       </c>
       <c r="C374" s="1"/>
     </row>
-    <row r="375" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375" s="1" t="s">
         <v>14</v>
       </c>
@@ -6502,7 +6506,7 @@
       </c>
       <c r="C375" s="1"/>
     </row>
-    <row r="376" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A376" s="1" t="s">
         <v>14</v>
       </c>
@@ -6511,7 +6515,7 @@
       </c>
       <c r="C376" s="1"/>
     </row>
-    <row r="377" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377" s="1" t="s">
         <v>14</v>
       </c>
@@ -6520,7 +6524,7 @@
       </c>
       <c r="C377" s="1"/>
     </row>
-    <row r="378" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A378" s="1" t="s">
         <v>14</v>
       </c>
@@ -6529,7 +6533,7 @@
       </c>
       <c r="C378" s="1"/>
     </row>
-    <row r="379" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379" s="1" t="s">
         <v>14</v>
       </c>
@@ -6538,7 +6542,7 @@
       </c>
       <c r="C379" s="1"/>
     </row>
-    <row r="380" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A380" s="1" t="s">
         <v>14</v>
       </c>
@@ -6547,7 +6551,7 @@
       </c>
       <c r="C380" s="1"/>
     </row>
-    <row r="381" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381" s="1" t="s">
         <v>14</v>
       </c>
@@ -6556,7 +6560,7 @@
       </c>
       <c r="C381" s="1"/>
     </row>
-    <row r="382" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A382" s="1" t="s">
         <v>14</v>
       </c>
@@ -6565,7 +6569,7 @@
       </c>
       <c r="C382" s="1"/>
     </row>
-    <row r="383" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A383" s="1" t="s">
         <v>14</v>
       </c>
@@ -6574,7 +6578,7 @@
       </c>
       <c r="C383" s="1"/>
     </row>
-    <row r="384" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A384" s="1" t="s">
         <v>14</v>
       </c>
@@ -6583,7 +6587,7 @@
       </c>
       <c r="C384" s="1"/>
     </row>
-    <row r="385" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A385" s="1" t="s">
         <v>14</v>
       </c>
@@ -6592,7 +6596,7 @@
       </c>
       <c r="C385" s="1"/>
     </row>
-    <row r="386" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A386" s="1" t="s">
         <v>14</v>
       </c>
@@ -6601,7 +6605,7 @@
       </c>
       <c r="C386" s="1"/>
     </row>
-    <row r="387" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387" s="1" t="s">
         <v>14</v>
       </c>
@@ -6610,7 +6614,7 @@
       </c>
       <c r="C387" s="1"/>
     </row>
-    <row r="388" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A388" s="1" t="s">
         <v>14</v>
       </c>
@@ -6619,7 +6623,7 @@
       </c>
       <c r="C388" s="1"/>
     </row>
-    <row r="389" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A389" s="1" t="s">
         <v>14</v>
       </c>
@@ -6628,7 +6632,7 @@
       </c>
       <c r="C389" s="1"/>
     </row>
-    <row r="390" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390" s="1" t="s">
         <v>14</v>
       </c>
@@ -6637,7 +6641,7 @@
       </c>
       <c r="C390" s="1"/>
     </row>
-    <row r="391" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A391" s="1" t="s">
         <v>14</v>
       </c>
@@ -6646,7 +6650,7 @@
       </c>
       <c r="C391" s="1"/>
     </row>
-    <row r="392" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392" s="1" t="s">
         <v>14</v>
       </c>
@@ -6655,7 +6659,7 @@
       </c>
       <c r="C392" s="1"/>
     </row>
-    <row r="393" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393" s="1" t="s">
         <v>14</v>
       </c>
@@ -6664,7 +6668,7 @@
       </c>
       <c r="C393" s="1"/>
     </row>
-    <row r="394" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A394" s="1" t="s">
         <v>14</v>
       </c>
@@ -6673,7 +6677,7 @@
       </c>
       <c r="C394" s="1"/>
     </row>
-    <row r="395" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395" s="1" t="s">
         <v>1</v>
       </c>
@@ -6682,7 +6686,7 @@
       </c>
       <c r="C395" s="1"/>
     </row>
-    <row r="396" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396" s="1" t="s">
         <v>1</v>
       </c>
@@ -6691,7 +6695,7 @@
       </c>
       <c r="C396" s="1"/>
     </row>
-    <row r="397" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397" s="1" t="s">
         <v>1</v>
       </c>
@@ -6700,7 +6704,7 @@
       </c>
       <c r="C397" s="1"/>
     </row>
-    <row r="398" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A398" s="1" t="s">
         <v>1</v>
       </c>
@@ -6709,7 +6713,7 @@
       </c>
       <c r="C398" s="1"/>
     </row>
-    <row r="399" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A399" s="1" t="s">
         <v>1</v>
       </c>
@@ -6718,7 +6722,7 @@
       </c>
       <c r="C399" s="1"/>
     </row>
-    <row r="400" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A400" s="1" t="s">
         <v>1</v>
       </c>
@@ -6727,7 +6731,7 @@
       </c>
       <c r="C400" s="1"/>
     </row>
-    <row r="401" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401" s="1" t="s">
         <v>1</v>
       </c>
@@ -6736,7 +6740,7 @@
       </c>
       <c r="C401" s="1"/>
     </row>
-    <row r="402" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A402" s="1" t="s">
         <v>1</v>
       </c>
@@ -6745,7 +6749,7 @@
       </c>
       <c r="C402" s="1"/>
     </row>
-    <row r="403" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A403" s="1" t="s">
         <v>1</v>
       </c>
@@ -6754,7 +6758,7 @@
       </c>
       <c r="C403" s="1"/>
     </row>
-    <row r="404" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A404" s="1" t="s">
         <v>1</v>
       </c>
@@ -6763,7 +6767,7 @@
       </c>
       <c r="C404" s="1"/>
     </row>
-    <row r="405" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405" s="1" t="s">
         <v>1</v>
       </c>
@@ -6772,7 +6776,7 @@
       </c>
       <c r="C405" s="1"/>
     </row>
-    <row r="406" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A406" s="1" t="s">
         <v>1</v>
       </c>
@@ -6781,7 +6785,7 @@
       </c>
       <c r="C406" s="1"/>
     </row>
-    <row r="407" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A407" s="1" t="s">
         <v>1</v>
       </c>
@@ -6790,7 +6794,7 @@
       </c>
       <c r="C407" s="1"/>
     </row>
-    <row r="408" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A408" s="1" t="s">
         <v>1</v>
       </c>
@@ -6799,7 +6803,7 @@
       </c>
       <c r="C408" s="1"/>
     </row>
-    <row r="409" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A409" s="1" t="s">
         <v>1</v>
       </c>
@@ -6808,7 +6812,7 @@
       </c>
       <c r="C409" s="1"/>
     </row>
-    <row r="410" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A410" s="1" t="s">
         <v>1</v>
       </c>
@@ -6817,7 +6821,7 @@
       </c>
       <c r="C410" s="1"/>
     </row>
-    <row r="411" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A411" s="1" t="s">
         <v>1</v>
       </c>
@@ -6826,7 +6830,7 @@
       </c>
       <c r="C411" s="1"/>
     </row>
-    <row r="412" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A412" s="1" t="s">
         <v>1</v>
       </c>
@@ -6835,7 +6839,7 @@
       </c>
       <c r="C412" s="1"/>
     </row>
-    <row r="413" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A413" s="1" t="s">
         <v>1</v>
       </c>
@@ -6844,7 +6848,7 @@
       </c>
       <c r="C413" s="1"/>
     </row>
-    <row r="414" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A414" s="1" t="s">
         <v>1</v>
       </c>
@@ -6853,7 +6857,7 @@
       </c>
       <c r="C414" s="1"/>
     </row>
-    <row r="415" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A415" s="1" t="s">
         <v>1</v>
       </c>
@@ -6862,7 +6866,7 @@
       </c>
       <c r="C415" s="1"/>
     </row>
-    <row r="416" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416" s="1" t="s">
         <v>1</v>
       </c>
@@ -6871,7 +6875,7 @@
       </c>
       <c r="C416" s="1"/>
     </row>
-    <row r="417" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A417" s="1" t="s">
         <v>1</v>
       </c>
@@ -6880,7 +6884,7 @@
       </c>
       <c r="C417" s="1"/>
     </row>
-    <row r="418" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A418" s="1" t="s">
         <v>1</v>
       </c>
@@ -6889,7 +6893,7 @@
       </c>
       <c r="C418" s="1"/>
     </row>
-    <row r="419" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A419" s="1" t="s">
         <v>1</v>
       </c>
@@ -6898,7 +6902,7 @@
       </c>
       <c r="C419" s="1"/>
     </row>
-    <row r="420" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A420" s="1" t="s">
         <v>1</v>
       </c>
@@ -6907,7 +6911,7 @@
       </c>
       <c r="C420" s="1"/>
     </row>
-    <row r="421" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A421" s="1" t="s">
         <v>1</v>
       </c>
@@ -6916,7 +6920,7 @@
       </c>
       <c r="C421" s="1"/>
     </row>
-    <row r="422" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A422" s="1" t="s">
         <v>1</v>
       </c>
@@ -6925,7 +6929,7 @@
       </c>
       <c r="C422" s="1"/>
     </row>
-    <row r="423" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A423" s="1" t="s">
         <v>1</v>
       </c>
@@ -6934,7 +6938,7 @@
       </c>
       <c r="C423" s="1"/>
     </row>
-    <row r="424" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A424" s="1" t="s">
         <v>1</v>
       </c>
@@ -6943,7 +6947,7 @@
       </c>
       <c r="C424" s="1"/>
     </row>
-    <row r="425" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A425" s="1" t="s">
         <v>1</v>
       </c>
@@ -6952,7 +6956,7 @@
       </c>
       <c r="C425" s="1"/>
     </row>
-    <row r="426" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A426" s="1" t="s">
         <v>1</v>
       </c>
@@ -6961,7 +6965,7 @@
       </c>
       <c r="C426" s="1"/>
     </row>
-    <row r="427" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A427" s="1" t="s">
         <v>1</v>
       </c>
@@ -6970,7 +6974,7 @@
       </c>
       <c r="C427" s="1"/>
     </row>
-    <row r="428" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A428" s="1" t="s">
         <v>1</v>
       </c>
@@ -6979,7 +6983,7 @@
       </c>
       <c r="C428" s="1"/>
     </row>
-    <row r="429" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A429" s="1" t="s">
         <v>1</v>
       </c>
@@ -6988,7 +6992,7 @@
       </c>
       <c r="C429" s="1"/>
     </row>
-    <row r="430" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A430" s="1" t="s">
         <v>1</v>
       </c>
@@ -6997,7 +7001,7 @@
       </c>
       <c r="C430" s="1"/>
     </row>
-    <row r="431" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A431" s="1" t="s">
         <v>26</v>
       </c>
@@ -7006,7 +7010,7 @@
       </c>
       <c r="C431" s="1"/>
     </row>
-    <row r="432" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A432" s="1" t="s">
         <v>26</v>
       </c>
@@ -7015,7 +7019,7 @@
       </c>
       <c r="C432" s="1"/>
     </row>
-    <row r="433" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A433" s="1" t="s">
         <v>26</v>
       </c>
@@ -7024,7 +7028,7 @@
       </c>
       <c r="C433" s="1"/>
     </row>
-    <row r="434" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A434" s="1" t="s">
         <v>26</v>
       </c>
@@ -7033,7 +7037,7 @@
       </c>
       <c r="C434" s="1"/>
     </row>
-    <row r="435" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A435" s="1" t="s">
         <v>26</v>
       </c>
@@ -7042,7 +7046,7 @@
       </c>
       <c r="C435" s="1"/>
     </row>
-    <row r="436" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A436" s="1" t="s">
         <v>26</v>
       </c>
@@ -7051,7 +7055,7 @@
       </c>
       <c r="C436" s="1"/>
     </row>
-    <row r="437" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A437" s="1" t="s">
         <v>26</v>
       </c>
@@ -7060,7 +7064,7 @@
       </c>
       <c r="C437" s="1"/>
     </row>
-    <row r="438" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A438" s="1" t="s">
         <v>26</v>
       </c>
@@ -7069,7 +7073,7 @@
       </c>
       <c r="C438" s="1"/>
     </row>
-    <row r="439" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A439" s="1" t="s">
         <v>26</v>
       </c>
@@ -7078,7 +7082,7 @@
       </c>
       <c r="C439" s="1"/>
     </row>
-    <row r="440" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A440" s="1" t="s">
         <v>26</v>
       </c>
@@ -7087,7 +7091,7 @@
       </c>
       <c r="C440" s="1"/>
     </row>
-    <row r="441" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A441" s="1" t="s">
         <v>26</v>
       </c>
@@ -7096,7 +7100,7 @@
       </c>
       <c r="C441" s="1"/>
     </row>
-    <row r="442" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A442" s="1" t="s">
         <v>26</v>
       </c>
@@ -7105,7 +7109,7 @@
       </c>
       <c r="C442" s="1"/>
     </row>
-    <row r="443" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A443" s="1" t="s">
         <v>26</v>
       </c>
@@ -7114,7 +7118,7 @@
       </c>
       <c r="C443" s="1"/>
     </row>
-    <row r="444" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A444" s="1" t="s">
         <v>26</v>
       </c>
@@ -7123,7 +7127,7 @@
       </c>
       <c r="C444" s="1"/>
     </row>
-    <row r="445" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A445" s="1" t="s">
         <v>26</v>
       </c>
@@ -7132,7 +7136,7 @@
       </c>
       <c r="C445" s="1"/>
     </row>
-    <row r="446" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A446" s="1" t="s">
         <v>26</v>
       </c>
@@ -7141,7 +7145,7 @@
       </c>
       <c r="C446" s="1"/>
     </row>
-    <row r="447" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A447" s="1" t="s">
         <v>30</v>
       </c>
@@ -7150,7 +7154,7 @@
       </c>
       <c r="C447" s="1"/>
     </row>
-    <row r="448" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A448" s="1" t="s">
         <v>30</v>
       </c>
@@ -7159,7 +7163,7 @@
       </c>
       <c r="C448" s="1"/>
     </row>
-    <row r="449" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A449" s="1" t="s">
         <v>30</v>
       </c>
@@ -7168,7 +7172,7 @@
       </c>
       <c r="C449" s="1"/>
     </row>
-    <row r="450" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A450" s="1" t="s">
         <v>30</v>
       </c>
@@ -7177,7 +7181,7 @@
       </c>
       <c r="C450" s="1"/>
     </row>
-    <row r="451" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A451" s="1" t="s">
         <v>30</v>
       </c>
@@ -7186,7 +7190,7 @@
       </c>
       <c r="C451" s="1"/>
     </row>
-    <row r="452" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A452" s="1" t="s">
         <v>30</v>
       </c>
@@ -7195,7 +7199,7 @@
       </c>
       <c r="C452" s="1"/>
     </row>
-    <row r="453" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A453" s="1" t="s">
         <v>30</v>
       </c>
@@ -7204,7 +7208,7 @@
       </c>
       <c r="C453" s="1"/>
     </row>
-    <row r="454" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A454" s="1" t="s">
         <v>30</v>
       </c>
@@ -7213,7 +7217,7 @@
       </c>
       <c r="C454" s="1"/>
     </row>
-    <row r="455" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A455" s="1" t="s">
         <v>30</v>
       </c>
@@ -7222,7 +7226,7 @@
       </c>
       <c r="C455" s="1"/>
     </row>
-    <row r="456" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A456" s="1" t="s">
         <v>30</v>
       </c>
@@ -7231,7 +7235,7 @@
       </c>
       <c r="C456" s="1"/>
     </row>
-    <row r="457" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A457" s="1" t="s">
         <v>30</v>
       </c>
@@ -7240,7 +7244,7 @@
       </c>
       <c r="C457" s="1"/>
     </row>
-    <row r="458" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A458" s="1" t="s">
         <v>30</v>
       </c>
@@ -7249,7 +7253,7 @@
       </c>
       <c r="C458" s="1"/>
     </row>
-    <row r="459" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A459" s="1" t="s">
         <v>29</v>
       </c>
@@ -7258,7 +7262,7 @@
       </c>
       <c r="C459" s="1"/>
     </row>
-    <row r="460" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A460" s="1" t="s">
         <v>29</v>
       </c>
@@ -7267,7 +7271,7 @@
       </c>
       <c r="C460" s="1"/>
     </row>
-    <row r="461" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A461" s="1" t="s">
         <v>29</v>
       </c>
@@ -7276,7 +7280,7 @@
       </c>
       <c r="C461" s="1"/>
     </row>
-    <row r="462" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A462" s="1" t="s">
         <v>29</v>
       </c>
@@ -7285,7 +7289,7 @@
       </c>
       <c r="C462" s="1"/>
     </row>
-    <row r="463" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A463" s="1" t="s">
         <v>29</v>
       </c>
@@ -7294,7 +7298,7 @@
       </c>
       <c r="C463" s="1"/>
     </row>
-    <row r="464" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A464" s="1" t="s">
         <v>29</v>
       </c>
@@ -7303,7 +7307,7 @@
       </c>
       <c r="C464" s="1"/>
     </row>
-    <row r="465" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A465" s="1" t="s">
         <v>29</v>
       </c>
@@ -7312,7 +7316,7 @@
       </c>
       <c r="C465" s="1"/>
     </row>
-    <row r="466" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A466" s="1" t="s">
         <v>29</v>
       </c>
@@ -7321,7 +7325,7 @@
       </c>
       <c r="C466" s="1"/>
     </row>
-    <row r="467" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A467" s="1" t="s">
         <v>29</v>
       </c>
@@ -7330,7 +7334,7 @@
       </c>
       <c r="C467" s="1"/>
     </row>
-    <row r="468" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A468" s="1" t="s">
         <v>29</v>
       </c>
@@ -7339,7 +7343,7 @@
       </c>
       <c r="C468" s="1"/>
     </row>
-    <row r="469" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A469" s="1" t="s">
         <v>29</v>
       </c>
@@ -7348,7 +7352,7 @@
       </c>
       <c r="C469" s="1"/>
     </row>
-    <row r="470" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A470" s="1" t="s">
         <v>24</v>
       </c>
@@ -7357,7 +7361,7 @@
       </c>
       <c r="C470" s="1"/>
     </row>
-    <row r="471" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A471" s="1" t="s">
         <v>24</v>
       </c>
@@ -7366,7 +7370,7 @@
       </c>
       <c r="C471" s="1"/>
     </row>
-    <row r="472" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A472" s="1" t="s">
         <v>24</v>
       </c>
@@ -7375,7 +7379,7 @@
       </c>
       <c r="C472" s="1"/>
     </row>
-    <row r="473" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A473" s="1" t="s">
         <v>24</v>
       </c>
@@ -7384,7 +7388,7 @@
       </c>
       <c r="C473" s="1"/>
     </row>
-    <row r="474" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A474" s="1" t="s">
         <v>24</v>
       </c>
@@ -7393,7 +7397,7 @@
       </c>
       <c r="C474" s="1"/>
     </row>
-    <row r="475" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A475" s="1" t="s">
         <v>24</v>
       </c>
@@ -7402,7 +7406,7 @@
       </c>
       <c r="C475" s="1"/>
     </row>
-    <row r="476" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A476" s="1" t="s">
         <v>24</v>
       </c>
@@ -7411,7 +7415,7 @@
       </c>
       <c r="C476" s="1"/>
     </row>
-    <row r="477" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A477" s="1" t="s">
         <v>24</v>
       </c>
@@ -7420,7 +7424,7 @@
       </c>
       <c r="C477" s="1"/>
     </row>
-    <row r="478" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A478" s="1" t="s">
         <v>24</v>
       </c>
@@ -7429,7 +7433,7 @@
       </c>
       <c r="C478" s="1"/>
     </row>
-    <row r="479" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A479" s="1" t="s">
         <v>24</v>
       </c>
@@ -7438,7 +7442,7 @@
       </c>
       <c r="C479" s="1"/>
     </row>
-    <row r="480" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A480" s="1" t="s">
         <v>24</v>
       </c>
@@ -7447,7 +7451,7 @@
       </c>
       <c r="C480" s="1"/>
     </row>
-    <row r="481" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A481" s="1" t="s">
         <v>24</v>
       </c>
@@ -7456,7 +7460,7 @@
       </c>
       <c r="C481" s="1"/>
     </row>
-    <row r="482" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A482" s="1" t="s">
         <v>24</v>
       </c>
@@ -7465,7 +7469,7 @@
       </c>
       <c r="C482" s="1"/>
     </row>
-    <row r="483" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A483" s="1" t="s">
         <v>24</v>
       </c>
@@ -7474,7 +7478,7 @@
       </c>
       <c r="C483" s="1"/>
     </row>
-    <row r="484" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A484" s="1" t="s">
         <v>24</v>
       </c>
@@ -7483,7 +7487,7 @@
       </c>
       <c r="C484" s="1"/>
     </row>
-    <row r="485" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A485" s="1" t="s">
         <v>24</v>
       </c>
@@ -7492,7 +7496,7 @@
       </c>
       <c r="C485" s="1"/>
     </row>
-    <row r="486" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A486" s="1" t="s">
         <v>17</v>
       </c>
@@ -7501,7 +7505,7 @@
       </c>
       <c r="C486" s="1"/>
     </row>
-    <row r="487" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A487" s="1" t="s">
         <v>17</v>
       </c>
@@ -7510,7 +7514,7 @@
       </c>
       <c r="C487" s="1"/>
     </row>
-    <row r="488" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A488" s="1" t="s">
         <v>17</v>
       </c>
@@ -7519,7 +7523,7 @@
       </c>
       <c r="C488" s="1"/>
     </row>
-    <row r="489" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A489" s="1" t="s">
         <v>17</v>
       </c>
@@ -7528,7 +7532,7 @@
       </c>
       <c r="C489" s="1"/>
     </row>
-    <row r="490" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A490" s="1" t="s">
         <v>17</v>
       </c>
@@ -7537,7 +7541,7 @@
       </c>
       <c r="C490" s="1"/>
     </row>
-    <row r="491" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A491" s="1" t="s">
         <v>17</v>
       </c>
@@ -7546,7 +7550,7 @@
       </c>
       <c r="C491" s="1"/>
     </row>
-    <row r="492" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A492" s="1" t="s">
         <v>17</v>
       </c>
@@ -7555,7 +7559,7 @@
       </c>
       <c r="C492" s="1"/>
     </row>
-    <row r="493" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A493" s="1" t="s">
         <v>17</v>
       </c>
@@ -7564,7 +7568,7 @@
       </c>
       <c r="C493" s="1"/>
     </row>
-    <row r="494" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A494" s="1" t="s">
         <v>17</v>
       </c>
@@ -7573,7 +7577,7 @@
       </c>
       <c r="C494" s="1"/>
     </row>
-    <row r="495" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A495" s="1" t="s">
         <v>17</v>
       </c>
@@ -7582,7 +7586,7 @@
       </c>
       <c r="C495" s="1"/>
     </row>
-    <row r="496" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A496" s="1" t="s">
         <v>17</v>
       </c>
@@ -7591,7 +7595,7 @@
       </c>
       <c r="C496" s="1"/>
     </row>
-    <row r="497" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A497" s="1" t="s">
         <v>17</v>
       </c>
@@ -7600,7 +7604,7 @@
       </c>
       <c r="C497" s="1"/>
     </row>
-    <row r="498" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A498" s="1" t="s">
         <v>17</v>
       </c>
@@ -7609,7 +7613,7 @@
       </c>
       <c r="C498" s="1"/>
     </row>
-    <row r="499" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A499" s="1" t="s">
         <v>17</v>
       </c>
@@ -7618,7 +7622,7 @@
       </c>
       <c r="C499" s="1"/>
     </row>
-    <row r="500" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A500" s="1" t="s">
         <v>17</v>
       </c>
@@ -7627,7 +7631,7 @@
       </c>
       <c r="C500" s="1"/>
     </row>
-    <row r="501" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A501" s="1" t="s">
         <v>17</v>
       </c>
@@ -7636,7 +7640,7 @@
       </c>
       <c r="C501" s="1"/>
     </row>
-    <row r="502" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A502" s="1" t="s">
         <v>17</v>
       </c>
@@ -7645,7 +7649,7 @@
       </c>
       <c r="C502" s="1"/>
     </row>
-    <row r="503" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A503" s="1" t="s">
         <v>17</v>
       </c>
@@ -7654,7 +7658,7 @@
       </c>
       <c r="C503" s="1"/>
     </row>
-    <row r="504" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A504" s="1" t="s">
         <v>17</v>
       </c>
@@ -7663,7 +7667,7 @@
       </c>
       <c r="C504" s="1"/>
     </row>
-    <row r="505" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A505" s="1" t="s">
         <v>17</v>
       </c>
@@ -7672,7 +7676,7 @@
       </c>
       <c r="C505" s="1"/>
     </row>
-    <row r="506" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A506" s="1" t="s">
         <v>17</v>
       </c>
@@ -7681,7 +7685,7 @@
       </c>
       <c r="C506" s="1"/>
     </row>
-    <row r="507" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A507" s="1" t="s">
         <v>17</v>
       </c>
@@ -7690,7 +7694,7 @@
       </c>
       <c r="C507" s="1"/>
     </row>
-    <row r="508" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A508" s="1" t="s">
         <v>17</v>
       </c>
@@ -7699,7 +7703,7 @@
       </c>
       <c r="C508" s="1"/>
     </row>
-    <row r="509" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A509" s="1" t="s">
         <v>17</v>
       </c>
@@ -7708,7 +7712,7 @@
       </c>
       <c r="C509" s="1"/>
     </row>
-    <row r="510" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A510" s="1" t="s">
         <v>17</v>
       </c>
@@ -7717,7 +7721,7 @@
       </c>
       <c r="C510" s="1"/>
     </row>
-    <row r="511" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A511" s="1" t="s">
         <v>17</v>
       </c>
@@ -7726,7 +7730,7 @@
       </c>
       <c r="C511" s="1"/>
     </row>
-    <row r="512" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A512" s="1" t="s">
         <v>17</v>
       </c>
@@ -7735,7 +7739,7 @@
       </c>
       <c r="C512" s="1"/>
     </row>
-    <row r="513" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A513" s="1" t="s">
         <v>17</v>
       </c>
@@ -7744,7 +7748,7 @@
       </c>
       <c r="C513" s="1"/>
     </row>
-    <row r="514" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A514" s="1" t="s">
         <v>17</v>
       </c>
@@ -7753,7 +7757,7 @@
       </c>
       <c r="C514" s="1"/>
     </row>
-    <row r="515" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A515" s="1" t="s">
         <v>17</v>
       </c>
@@ -7762,7 +7766,7 @@
       </c>
       <c r="C515" s="1"/>
     </row>
-    <row r="516" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A516" s="1" t="s">
         <v>34</v>
       </c>
@@ -7771,7 +7775,7 @@
       </c>
       <c r="C516" s="1"/>
     </row>
-    <row r="517" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A517" s="1" t="s">
         <v>34</v>
       </c>
@@ -7780,7 +7784,7 @@
       </c>
       <c r="C517" s="1"/>
     </row>
-    <row r="518" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A518" s="1" t="s">
         <v>34</v>
       </c>
@@ -7789,7 +7793,7 @@
       </c>
       <c r="C518" s="1"/>
     </row>
-    <row r="519" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A519" s="1" t="s">
         <v>34</v>
       </c>
@@ -7798,7 +7802,7 @@
       </c>
       <c r="C519" s="1"/>
     </row>
-    <row r="520" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A520" s="1" t="s">
         <v>6</v>
       </c>
@@ -7807,7 +7811,7 @@
       </c>
       <c r="C520" s="1"/>
     </row>
-    <row r="521" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A521" s="1" t="s">
         <v>6</v>
       </c>
@@ -7816,7 +7820,7 @@
       </c>
       <c r="C521" s="1"/>
     </row>
-    <row r="522" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A522" s="1" t="s">
         <v>6</v>
       </c>
@@ -7825,7 +7829,7 @@
       </c>
       <c r="C522" s="1"/>
     </row>
-    <row r="523" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A523" s="1" t="s">
         <v>6</v>
       </c>
@@ -7834,7 +7838,7 @@
       </c>
       <c r="C523" s="1"/>
     </row>
-    <row r="524" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A524" s="1" t="s">
         <v>6</v>
       </c>
@@ -7843,7 +7847,7 @@
       </c>
       <c r="C524" s="1"/>
     </row>
-    <row r="525" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A525" s="1" t="s">
         <v>6</v>
       </c>
@@ -7852,7 +7856,7 @@
       </c>
       <c r="C525" s="1"/>
     </row>
-    <row r="526" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A526" s="1" t="s">
         <v>6</v>
       </c>
@@ -7861,7 +7865,7 @@
       </c>
       <c r="C526" s="1"/>
     </row>
-    <row r="527" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A527" s="1" t="s">
         <v>6</v>
       </c>
@@ -7870,7 +7874,7 @@
       </c>
       <c r="C527" s="1"/>
     </row>
-    <row r="528" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A528" s="1" t="s">
         <v>6</v>
       </c>
@@ -7879,7 +7883,7 @@
       </c>
       <c r="C528" s="1"/>
     </row>
-    <row r="529" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A529" s="1" t="s">
         <v>6</v>
       </c>
@@ -7888,7 +7892,7 @@
       </c>
       <c r="C529" s="1"/>
     </row>
-    <row r="530" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A530" s="1" t="s">
         <v>6</v>
       </c>
@@ -7897,7 +7901,7 @@
       </c>
       <c r="C530" s="1"/>
     </row>
-    <row r="531" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A531" s="1" t="s">
         <v>6</v>
       </c>
@@ -7906,7 +7910,7 @@
       </c>
       <c r="C531" s="1"/>
     </row>
-    <row r="532" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A532" s="1" t="s">
         <v>6</v>
       </c>
@@ -7915,7 +7919,7 @@
       </c>
       <c r="C532" s="1"/>
     </row>
-    <row r="533" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A533" s="1" t="s">
         <v>6</v>
       </c>
@@ -7924,7 +7928,7 @@
       </c>
       <c r="C533" s="1"/>
     </row>
-    <row r="534" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A534" s="1" t="s">
         <v>6</v>
       </c>
@@ -7933,7 +7937,7 @@
       </c>
       <c r="C534" s="1"/>
     </row>
-    <row r="535" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A535" s="1" t="s">
         <v>6</v>
       </c>
@@ -7942,7 +7946,7 @@
       </c>
       <c r="C535" s="1"/>
     </row>
-    <row r="536" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A536" s="1" t="s">
         <v>6</v>
       </c>
@@ -7951,7 +7955,7 @@
       </c>
       <c r="C536" s="1"/>
     </row>
-    <row r="537" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A537" s="1" t="s">
         <v>6</v>
       </c>
@@ -7960,7 +7964,7 @@
       </c>
       <c r="C537" s="1"/>
     </row>
-    <row r="538" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A538" s="1" t="s">
         <v>6</v>
       </c>
@@ -7969,7 +7973,7 @@
       </c>
       <c r="C538" s="1"/>
     </row>
-    <row r="539" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A539" s="1" t="s">
         <v>6</v>
       </c>
@@ -7978,7 +7982,7 @@
       </c>
       <c r="C539" s="1"/>
     </row>
-    <row r="540" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A540" s="1" t="s">
         <v>6</v>
       </c>
@@ -7987,7 +7991,7 @@
       </c>
       <c r="C540" s="1"/>
     </row>
-    <row r="541" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A541" s="1" t="s">
         <v>6</v>
       </c>
@@ -7996,7 +8000,7 @@
       </c>
       <c r="C541" s="1"/>
     </row>
-    <row r="542" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A542" s="1" t="s">
         <v>6</v>
       </c>
@@ -8005,7 +8009,7 @@
       </c>
       <c r="C542" s="1"/>
     </row>
-    <row r="543" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A543" s="1" t="s">
         <v>18</v>
       </c>
@@ -8014,7 +8018,7 @@
       </c>
       <c r="C543" s="1"/>
     </row>
-    <row r="544" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A544" s="1" t="s">
         <v>18</v>
       </c>
@@ -8023,7 +8027,7 @@
       </c>
       <c r="C544" s="1"/>
     </row>
-    <row r="545" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A545" s="1" t="s">
         <v>18</v>
       </c>
@@ -8032,7 +8036,7 @@
       </c>
       <c r="C545" s="1"/>
     </row>
-    <row r="546" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A546" s="1" t="s">
         <v>18</v>
       </c>
@@ -8041,7 +8045,7 @@
       </c>
       <c r="C546" s="1"/>
     </row>
-    <row r="547" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A547" s="1" t="s">
         <v>18</v>
       </c>
@@ -8050,7 +8054,7 @@
       </c>
       <c r="C547" s="1"/>
     </row>
-    <row r="548" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A548" s="1" t="s">
         <v>18</v>
       </c>
@@ -8059,7 +8063,7 @@
       </c>
       <c r="C548" s="1"/>
     </row>
-    <row r="549" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A549" s="1" t="s">
         <v>18</v>
       </c>
@@ -8068,7 +8072,7 @@
       </c>
       <c r="C549" s="1"/>
     </row>
-    <row r="550" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A550" s="1" t="s">
         <v>18</v>
       </c>
@@ -8077,7 +8081,7 @@
       </c>
       <c r="C550" s="1"/>
     </row>
-    <row r="551" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A551" s="1" t="s">
         <v>18</v>
       </c>
@@ -8086,7 +8090,7 @@
       </c>
       <c r="C551" s="1"/>
     </row>
-    <row r="552" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A552" s="1" t="s">
         <v>18</v>
       </c>
@@ -8095,7 +8099,7 @@
       </c>
       <c r="C552" s="1"/>
     </row>
-    <row r="553" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A553" s="1" t="s">
         <v>18</v>
       </c>
@@ -8104,7 +8108,7 @@
       </c>
       <c r="C553" s="1"/>
     </row>
-    <row r="554" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A554" s="1" t="s">
         <v>18</v>
       </c>
@@ -8113,7 +8117,7 @@
       </c>
       <c r="C554" s="1"/>
     </row>
-    <row r="555" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A555" s="1" t="s">
         <v>18</v>
       </c>
@@ -8122,7 +8126,7 @@
       </c>
       <c r="C555" s="1"/>
     </row>
-    <row r="556" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A556" s="1" t="s">
         <v>18</v>
       </c>
@@ -8131,7 +8135,7 @@
       </c>
       <c r="C556" s="1"/>
     </row>
-    <row r="557" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A557" s="1" t="s">
         <v>18</v>
       </c>
@@ -8140,7 +8144,7 @@
       </c>
       <c r="C557" s="1"/>
     </row>
-    <row r="558" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A558" s="1" t="s">
         <v>18</v>
       </c>
@@ -8149,7 +8153,7 @@
       </c>
       <c r="C558" s="1"/>
     </row>
-    <row r="559" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A559" s="1" t="s">
         <v>18</v>
       </c>
@@ -8158,7 +8162,7 @@
       </c>
       <c r="C559" s="1"/>
     </row>
-    <row r="560" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A560" s="1" t="s">
         <v>18</v>
       </c>
@@ -8167,7 +8171,7 @@
       </c>
       <c r="C560" s="1"/>
     </row>
-    <row r="561" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A561" s="1" t="s">
         <v>18</v>
       </c>
@@ -8176,7 +8180,7 @@
       </c>
       <c r="C561" s="1"/>
     </row>
-    <row r="562" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A562" s="1" t="s">
         <v>18</v>
       </c>
@@ -8185,7 +8189,7 @@
       </c>
       <c r="C562" s="1"/>
     </row>
-    <row r="563" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A563" s="1" t="s">
         <v>18</v>
       </c>
@@ -8194,7 +8198,7 @@
       </c>
       <c r="C563" s="1"/>
     </row>
-    <row r="564" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A564" s="1" t="s">
         <v>18</v>
       </c>
@@ -8203,7 +8207,7 @@
       </c>
       <c r="C564" s="1"/>
     </row>
-    <row r="565" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A565" s="1" t="s">
         <v>18</v>
       </c>
@@ -8212,7 +8216,7 @@
       </c>
       <c r="C565" s="1"/>
     </row>
-    <row r="566" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A566" s="1" t="s">
         <v>18</v>
       </c>
@@ -8221,7 +8225,7 @@
       </c>
       <c r="C566" s="1"/>
     </row>
-    <row r="567" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A567" s="1" t="s">
         <v>18</v>
       </c>
@@ -8230,7 +8234,7 @@
       </c>
       <c r="C567" s="1"/>
     </row>
-    <row r="568" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A568" s="1" t="s">
         <v>18</v>
       </c>
@@ -8239,7 +8243,7 @@
       </c>
       <c r="C568" s="1"/>
     </row>
-    <row r="569" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A569" s="1" t="s">
         <v>18</v>
       </c>
@@ -8248,7 +8252,7 @@
       </c>
       <c r="C569" s="1"/>
     </row>
-    <row r="570" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A570" s="1" t="s">
         <v>18</v>
       </c>
@@ -8257,7 +8261,7 @@
       </c>
       <c r="C570" s="1"/>
     </row>
-    <row r="571" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A571" s="1" t="s">
         <v>18</v>
       </c>
@@ -8266,7 +8270,7 @@
       </c>
       <c r="C571" s="1"/>
     </row>
-    <row r="572" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A572" s="1" t="s">
         <v>18</v>
       </c>
@@ -8275,7 +8279,7 @@
       </c>
       <c r="C572" s="1"/>
     </row>
-    <row r="573" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A573" s="1" t="s">
         <v>18</v>
       </c>
@@ -8284,7 +8288,7 @@
       </c>
       <c r="C573" s="1"/>
     </row>
-    <row r="574" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A574" s="1" t="s">
         <v>18</v>
       </c>
@@ -8293,7 +8297,7 @@
       </c>
       <c r="C574" s="1"/>
     </row>
-    <row r="575" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A575" s="1" t="s">
         <v>18</v>
       </c>
@@ -8302,7 +8306,7 @@
       </c>
       <c r="C575" s="1"/>
     </row>
-    <row r="576" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A576" s="1" t="s">
         <v>18</v>
       </c>
@@ -8311,7 +8315,7 @@
       </c>
       <c r="C576" s="1"/>
     </row>
-    <row r="577" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A577" s="1" t="s">
         <v>18</v>
       </c>
@@ -8320,7 +8324,7 @@
       </c>
       <c r="C577" s="1"/>
     </row>
-    <row r="578" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A578" s="1" t="s">
         <v>18</v>
       </c>
@@ -8329,7 +8333,7 @@
       </c>
       <c r="C578" s="1"/>
     </row>
-    <row r="579" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A579" s="1" t="s">
         <v>18</v>
       </c>
@@ -8338,7 +8342,7 @@
       </c>
       <c r="C579" s="1"/>
     </row>
-    <row r="580" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A580" s="1" t="s">
         <v>18</v>
       </c>
@@ -8347,7 +8351,7 @@
       </c>
       <c r="C580" s="1"/>
     </row>
-    <row r="581" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A581" s="1" t="s">
         <v>18</v>
       </c>
@@ -8356,7 +8360,7 @@
       </c>
       <c r="C581" s="1"/>
     </row>
-    <row r="582" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A582" s="1" t="s">
         <v>18</v>
       </c>
@@ -8365,7 +8369,7 @@
       </c>
       <c r="C582" s="1"/>
     </row>
-    <row r="583" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A583" s="1" t="s">
         <v>18</v>
       </c>
@@ -8374,7 +8378,7 @@
       </c>
       <c r="C583" s="1"/>
     </row>
-    <row r="584" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A584" s="1" t="s">
         <v>18</v>
       </c>
@@ -8383,7 +8387,7 @@
       </c>
       <c r="C584" s="1"/>
     </row>
-    <row r="585" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A585" s="1" t="s">
         <v>18</v>
       </c>
@@ -8392,7 +8396,7 @@
       </c>
       <c r="C585" s="1"/>
     </row>
-    <row r="586" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A586" s="1" t="s">
         <v>18</v>
       </c>
@@ -8401,7 +8405,7 @@
       </c>
       <c r="C586" s="1"/>
     </row>
-    <row r="587" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A587" s="1" t="s">
         <v>18</v>
       </c>
@@ -8410,7 +8414,7 @@
       </c>
       <c r="C587" s="1"/>
     </row>
-    <row r="588" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A588" s="1" t="s">
         <v>18</v>
       </c>
@@ -8419,7 +8423,7 @@
       </c>
       <c r="C588" s="1"/>
     </row>
-    <row r="589" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A589" s="1" t="s">
         <v>18</v>
       </c>
@@ -8428,7 +8432,7 @@
       </c>
       <c r="C589" s="1"/>
     </row>
-    <row r="590" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A590" s="1" t="s">
         <v>18</v>
       </c>
@@ -8437,7 +8441,7 @@
       </c>
       <c r="C590" s="1"/>
     </row>
-    <row r="591" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A591" s="1" t="s">
         <v>18</v>
       </c>
@@ -8446,7 +8450,7 @@
       </c>
       <c r="C591" s="1"/>
     </row>
-    <row r="592" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A592" s="1" t="s">
         <v>18</v>
       </c>
@@ -8455,7 +8459,7 @@
       </c>
       <c r="C592" s="1"/>
     </row>
-    <row r="593" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A593" s="1" t="s">
         <v>31</v>
       </c>
@@ -8464,7 +8468,7 @@
       </c>
       <c r="C593" s="1"/>
     </row>
-    <row r="594" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A594" s="1" t="s">
         <v>31</v>
       </c>
@@ -8473,7 +8477,7 @@
       </c>
       <c r="C594" s="1"/>
     </row>
-    <row r="595" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A595" s="1" t="s">
         <v>31</v>
       </c>
@@ -8482,7 +8486,7 @@
       </c>
       <c r="C595" s="1"/>
     </row>
-    <row r="596" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A596" s="1" t="s">
         <v>31</v>
       </c>
@@ -8491,7 +8495,7 @@
       </c>
       <c r="C596" s="1"/>
     </row>
-    <row r="597" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A597" s="1" t="s">
         <v>31</v>
       </c>
@@ -8500,7 +8504,7 @@
       </c>
       <c r="C597" s="1"/>
     </row>
-    <row r="598" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A598" s="1" t="s">
         <v>31</v>
       </c>
@@ -8509,7 +8513,7 @@
       </c>
       <c r="C598" s="1"/>
     </row>
-    <row r="599" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A599" s="1" t="s">
         <v>5</v>
       </c>
@@ -8518,7 +8522,7 @@
       </c>
       <c r="C599" s="1"/>
     </row>
-    <row r="600" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A600" s="1" t="s">
         <v>5</v>
       </c>
@@ -8527,7 +8531,7 @@
       </c>
       <c r="C600" s="1"/>
     </row>
-    <row r="601" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A601" s="1" t="s">
         <v>5</v>
       </c>
@@ -8536,7 +8540,7 @@
       </c>
       <c r="C601" s="1"/>
     </row>
-    <row r="602" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A602" s="1" t="s">
         <v>5</v>
       </c>
@@ -8545,7 +8549,7 @@
       </c>
       <c r="C602" s="1"/>
     </row>
-    <row r="603" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A603" s="1" t="s">
         <v>5</v>
       </c>
@@ -8554,7 +8558,7 @@
       </c>
       <c r="C603" s="1"/>
     </row>
-    <row r="604" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A604" s="1" t="s">
         <v>5</v>
       </c>
@@ -8563,7 +8567,7 @@
       </c>
       <c r="C604" s="1"/>
     </row>
-    <row r="605" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A605" s="1" t="s">
         <v>5</v>
       </c>
@@ -8572,7 +8576,7 @@
       </c>
       <c r="C605" s="1"/>
     </row>
-    <row r="606" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A606" s="1" t="s">
         <v>5</v>
       </c>
@@ -8581,7 +8585,7 @@
       </c>
       <c r="C606" s="1"/>
     </row>
-    <row r="607" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A607" s="1" t="s">
         <v>5</v>
       </c>
@@ -8590,7 +8594,7 @@
       </c>
       <c r="C607" s="1"/>
     </row>
-    <row r="608" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A608" s="1" t="s">
         <v>5</v>
       </c>
@@ -8599,7 +8603,7 @@
       </c>
       <c r="C608" s="1"/>
     </row>
-    <row r="609" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A609" s="1" t="s">
         <v>5</v>
       </c>
@@ -8608,7 +8612,7 @@
       </c>
       <c r="C609" s="1"/>
     </row>
-    <row r="610" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A610" s="1" t="s">
         <v>5</v>
       </c>
@@ -8617,7 +8621,7 @@
       </c>
       <c r="C610" s="1"/>
     </row>
-    <row r="611" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A611" s="1" t="s">
         <v>5</v>
       </c>
@@ -8626,7 +8630,7 @@
       </c>
       <c r="C611" s="1"/>
     </row>
-    <row r="612" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A612" s="1" t="s">
         <v>5</v>
       </c>
@@ -8635,7 +8639,7 @@
       </c>
       <c r="C612" s="1"/>
     </row>
-    <row r="613" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A613" s="1" t="s">
         <v>5</v>
       </c>
@@ -8644,7 +8648,7 @@
       </c>
       <c r="C613" s="1"/>
     </row>
-    <row r="614" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A614" s="1" t="s">
         <v>5</v>
       </c>
@@ -8653,7 +8657,7 @@
       </c>
       <c r="C614" s="1"/>
     </row>
-    <row r="615" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A615" s="1" t="s">
         <v>5</v>
       </c>
@@ -8662,7 +8666,7 @@
       </c>
       <c r="C615" s="1"/>
     </row>
-    <row r="616" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A616" s="1" t="s">
         <v>5</v>
       </c>
@@ -8671,7 +8675,7 @@
       </c>
       <c r="C616" s="1"/>
     </row>
-    <row r="617" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A617" s="1" t="s">
         <v>5</v>
       </c>
@@ -8680,7 +8684,7 @@
       </c>
       <c r="C617" s="1"/>
     </row>
-    <row r="618" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A618" s="1" t="s">
         <v>5</v>
       </c>
@@ -8689,7 +8693,7 @@
       </c>
       <c r="C618" s="1"/>
     </row>
-    <row r="619" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A619" s="1" t="s">
         <v>5</v>
       </c>
@@ -8698,7 +8702,7 @@
       </c>
       <c r="C619" s="1"/>
     </row>
-    <row r="620" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A620" s="1" t="s">
         <v>5</v>
       </c>
@@ -8707,7 +8711,7 @@
       </c>
       <c r="C620" s="1"/>
     </row>
-    <row r="621" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A621" s="1" t="s">
         <v>5</v>
       </c>
@@ -8716,7 +8720,7 @@
       </c>
       <c r="C621" s="1"/>
     </row>
-    <row r="622" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A622" s="1" t="s">
         <v>5</v>
       </c>
@@ -8725,7 +8729,7 @@
       </c>
       <c r="C622" s="1"/>
     </row>
-    <row r="623" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A623" s="1" t="s">
         <v>5</v>
       </c>
@@ -8734,7 +8738,7 @@
       </c>
       <c r="C623" s="1"/>
     </row>
-    <row r="624" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A624" s="1" t="s">
         <v>5</v>
       </c>
@@ -8743,7 +8747,7 @@
       </c>
       <c r="C624" s="1"/>
     </row>
-    <row r="625" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A625" s="1" t="s">
         <v>5</v>
       </c>
@@ -8752,7 +8756,7 @@
       </c>
       <c r="C625" s="1"/>
     </row>
-    <row r="626" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A626" s="1" t="s">
         <v>5</v>
       </c>
@@ -8761,7 +8765,7 @@
       </c>
       <c r="C626" s="1"/>
     </row>
-    <row r="627" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A627" s="1" t="s">
         <v>5</v>
       </c>
@@ -8770,7 +8774,7 @@
       </c>
       <c r="C627" s="1"/>
     </row>
-    <row r="628" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A628" s="1" t="s">
         <v>5</v>
       </c>
@@ -8779,7 +8783,7 @@
       </c>
       <c r="C628" s="1"/>
     </row>
-    <row r="629" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A629" s="1" t="s">
         <v>5</v>
       </c>
@@ -8788,7 +8792,7 @@
       </c>
       <c r="C629" s="1"/>
     </row>
-    <row r="630" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A630" s="1" t="s">
         <v>5</v>
       </c>
@@ -8797,7 +8801,7 @@
       </c>
       <c r="C630" s="1"/>
     </row>
-    <row r="631" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A631" s="1" t="s">
         <v>5</v>
       </c>
@@ -8806,7 +8810,7 @@
       </c>
       <c r="C631" s="1"/>
     </row>
-    <row r="632" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A632" s="1" t="s">
         <v>5</v>
       </c>
@@ -8815,7 +8819,7 @@
       </c>
       <c r="C632" s="1"/>
     </row>
-    <row r="633" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A633" s="1" t="s">
         <v>5</v>
       </c>
@@ -8824,7 +8828,7 @@
       </c>
       <c r="C633" s="1"/>
     </row>
-    <row r="634" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A634" s="1" t="s">
         <v>5</v>
       </c>
@@ -8833,7 +8837,7 @@
       </c>
       <c r="C634" s="1"/>
     </row>
-    <row r="635" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A635" s="1" t="s">
         <v>5</v>
       </c>
@@ -8842,7 +8846,7 @@
       </c>
       <c r="C635" s="1"/>
     </row>
-    <row r="636" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A636" s="1" t="s">
         <v>5</v>
       </c>
@@ -8851,7 +8855,7 @@
       </c>
       <c r="C636" s="1"/>
     </row>
-    <row r="637" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A637" s="1" t="s">
         <v>8</v>
       </c>
@@ -8860,7 +8864,7 @@
       </c>
       <c r="C637" s="1"/>
     </row>
-    <row r="638" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A638" s="1" t="s">
         <v>8</v>
       </c>
@@ -8869,7 +8873,7 @@
       </c>
       <c r="C638" s="1"/>
     </row>
-    <row r="639" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A639" s="1" t="s">
         <v>8</v>
       </c>
@@ -8878,7 +8882,7 @@
       </c>
       <c r="C639" s="1"/>
     </row>
-    <row r="640" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A640" s="1" t="s">
         <v>8</v>
       </c>
@@ -8887,7 +8891,7 @@
       </c>
       <c r="C640" s="1"/>
     </row>
-    <row r="641" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A641" s="1" t="s">
         <v>8</v>
       </c>
@@ -8896,7 +8900,7 @@
       </c>
       <c r="C641" s="1"/>
     </row>
-    <row r="642" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A642" s="1" t="s">
         <v>8</v>
       </c>
@@ -8905,7 +8909,7 @@
       </c>
       <c r="C642" s="1"/>
     </row>
-    <row r="643" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A643" s="1" t="s">
         <v>8</v>
       </c>
@@ -8914,7 +8918,7 @@
       </c>
       <c r="C643" s="1"/>
     </row>
-    <row r="644" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A644" s="1" t="s">
         <v>8</v>
       </c>
@@ -8923,7 +8927,7 @@
       </c>
       <c r="C644" s="1"/>
     </row>
-    <row r="645" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A645" s="1" t="s">
         <v>8</v>
       </c>
@@ -8932,7 +8936,7 @@
       </c>
       <c r="C645" s="1"/>
     </row>
-    <row r="646" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A646" s="1" t="s">
         <v>8</v>
       </c>
@@ -8941,7 +8945,7 @@
       </c>
       <c r="C646" s="1"/>
     </row>
-    <row r="647" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A647" s="1" t="s">
         <v>8</v>
       </c>
@@ -8950,7 +8954,7 @@
       </c>
       <c r="C647" s="1"/>
     </row>
-    <row r="648" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A648" s="1" t="s">
         <v>8</v>
       </c>
@@ -8959,7 +8963,7 @@
       </c>
       <c r="C648" s="1"/>
     </row>
-    <row r="649" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A649" s="1" t="s">
         <v>8</v>
       </c>
@@ -8968,7 +8972,7 @@
       </c>
       <c r="C649" s="1"/>
     </row>
-    <row r="650" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A650" s="1" t="s">
         <v>8</v>
       </c>
@@ -8977,7 +8981,7 @@
       </c>
       <c r="C650" s="1"/>
     </row>
-    <row r="651" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A651" s="1" t="s">
         <v>8</v>
       </c>
@@ -8986,7 +8990,7 @@
       </c>
       <c r="C651" s="1"/>
     </row>
-    <row r="652" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A652" s="1" t="s">
         <v>8</v>
       </c>
@@ -8995,7 +8999,7 @@
       </c>
       <c r="C652" s="1"/>
     </row>
-    <row r="653" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A653" s="1" t="s">
         <v>8</v>
       </c>
@@ -9004,7 +9008,7 @@
       </c>
       <c r="C653" s="1"/>
     </row>
-    <row r="654" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A654" s="1" t="s">
         <v>8</v>
       </c>
@@ -9013,7 +9017,7 @@
       </c>
       <c r="C654" s="1"/>
     </row>
-    <row r="655" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A655" s="1" t="s">
         <v>8</v>
       </c>
@@ -9022,7 +9026,7 @@
       </c>
       <c r="C655" s="1"/>
     </row>
-    <row r="656" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A656" s="1" t="s">
         <v>8</v>
       </c>
@@ -9031,7 +9035,7 @@
       </c>
       <c r="C656" s="1"/>
     </row>
-    <row r="657" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A657" s="1" t="s">
         <v>8</v>
       </c>
@@ -9040,7 +9044,7 @@
       </c>
       <c r="C657" s="1"/>
     </row>
-    <row r="658" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A658" s="1" t="s">
         <v>8</v>
       </c>
@@ -9049,7 +9053,7 @@
       </c>
       <c r="C658" s="1"/>
     </row>
-    <row r="659" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A659" s="1" t="s">
         <v>8</v>
       </c>
@@ -9058,7 +9062,7 @@
       </c>
       <c r="C659" s="1"/>
     </row>
-    <row r="660" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A660" s="1" t="s">
         <v>8</v>
       </c>
@@ -9067,7 +9071,7 @@
       </c>
       <c r="C660" s="1"/>
     </row>
-    <row r="661" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A661" s="1" t="s">
         <v>8</v>
       </c>
@@ -9076,7 +9080,7 @@
       </c>
       <c r="C661" s="1"/>
     </row>
-    <row r="662" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A662" s="1" t="s">
         <v>8</v>
       </c>
@@ -9085,7 +9089,7 @@
       </c>
       <c r="C662" s="1"/>
     </row>
-    <row r="663" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A663" s="1" t="s">
         <v>8</v>
       </c>
@@ -9094,7 +9098,7 @@
       </c>
       <c r="C663" s="1"/>
     </row>
-    <row r="664" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A664" s="1" t="s">
         <v>8</v>
       </c>
@@ -9103,7 +9107,7 @@
       </c>
       <c r="C664" s="1"/>
     </row>
-    <row r="665" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A665" s="1" t="s">
         <v>8</v>
       </c>
@@ -9112,7 +9116,7 @@
       </c>
       <c r="C665" s="1"/>
     </row>
-    <row r="666" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A666" s="1" t="s">
         <v>8</v>
       </c>
@@ -9121,7 +9125,7 @@
       </c>
       <c r="C666" s="1"/>
     </row>
-    <row r="667" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A667" s="1" t="s">
         <v>8</v>
       </c>
@@ -9130,7 +9134,7 @@
       </c>
       <c r="C667" s="1"/>
     </row>
-    <row r="668" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A668" s="1" t="s">
         <v>8</v>
       </c>
@@ -9139,7 +9143,7 @@
       </c>
       <c r="C668" s="1"/>
     </row>
-    <row r="669" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A669" s="1" t="s">
         <v>8</v>
       </c>
@@ -9148,7 +9152,7 @@
       </c>
       <c r="C669" s="1"/>
     </row>
-    <row r="670" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A670" s="1" t="s">
         <v>27</v>
       </c>
@@ -9157,7 +9161,7 @@
       </c>
       <c r="C670" s="1"/>
     </row>
-    <row r="671" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A671" s="1" t="s">
         <v>27</v>
       </c>
@@ -9166,7 +9170,7 @@
       </c>
       <c r="C671" s="1"/>
     </row>
-    <row r="672" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A672" s="1" t="s">
         <v>27</v>
       </c>
@@ -9175,7 +9179,7 @@
       </c>
       <c r="C672" s="1"/>
     </row>
-    <row r="673" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A673" s="1" t="s">
         <v>27</v>
       </c>
@@ -9184,7 +9188,7 @@
       </c>
       <c r="C673" s="1"/>
     </row>
-    <row r="674" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A674" s="1" t="s">
         <v>27</v>
       </c>
@@ -9193,7 +9197,7 @@
       </c>
       <c r="C674" s="1"/>
     </row>
-    <row r="675" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A675" s="1" t="s">
         <v>27</v>
       </c>
@@ -9202,7 +9206,7 @@
       </c>
       <c r="C675" s="1"/>
     </row>
-    <row r="676" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A676" s="1" t="s">
         <v>27</v>
       </c>
@@ -9211,7 +9215,7 @@
       </c>
       <c r="C676" s="1"/>
     </row>
-    <row r="677" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A677" s="1" t="s">
         <v>27</v>
       </c>
@@ -9895,7 +9899,7 @@
       </c>
       <c r="C752" s="1"/>
     </row>
-    <row r="753" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A753" s="1" t="s">
         <v>20</v>
       </c>
@@ -9904,7 +9908,7 @@
       </c>
       <c r="C753" s="1"/>
     </row>
-    <row r="754" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A754" s="1" t="s">
         <v>20</v>
       </c>
@@ -9913,7 +9917,7 @@
       </c>
       <c r="C754" s="1"/>
     </row>
-    <row r="755" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A755" s="1" t="s">
         <v>20</v>
       </c>
@@ -9922,7 +9926,7 @@
       </c>
       <c r="C755" s="1"/>
     </row>
-    <row r="756" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A756" s="1" t="s">
         <v>20</v>
       </c>
@@ -9931,7 +9935,7 @@
       </c>
       <c r="C756" s="1"/>
     </row>
-    <row r="757" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A757" s="1" t="s">
         <v>20</v>
       </c>
@@ -9940,7 +9944,7 @@
       </c>
       <c r="C757" s="1"/>
     </row>
-    <row r="758" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A758" s="1" t="s">
         <v>20</v>
       </c>
@@ -9949,7 +9953,7 @@
       </c>
       <c r="C758" s="1"/>
     </row>
-    <row r="759" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A759" s="1" t="s">
         <v>20</v>
       </c>
@@ -9958,7 +9962,7 @@
       </c>
       <c r="C759" s="1"/>
     </row>
-    <row r="760" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A760" s="1" t="s">
         <v>20</v>
       </c>
@@ -9967,7 +9971,7 @@
       </c>
       <c r="C760" s="1"/>
     </row>
-    <row r="761" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A761" s="1" t="s">
         <v>20</v>
       </c>
@@ -9976,7 +9980,7 @@
       </c>
       <c r="C761" s="1"/>
     </row>
-    <row r="762" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A762" s="1" t="s">
         <v>20</v>
       </c>
@@ -9985,7 +9989,7 @@
       </c>
       <c r="C762" s="1"/>
     </row>
-    <row r="763" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A763" s="1" t="s">
         <v>20</v>
       </c>
@@ -9994,7 +9998,7 @@
       </c>
       <c r="C763" s="1"/>
     </row>
-    <row r="764" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A764" s="1" t="s">
         <v>20</v>
       </c>
@@ -10003,7 +10007,7 @@
       </c>
       <c r="C764" s="1"/>
     </row>
-    <row r="765" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A765" s="1" t="s">
         <v>20</v>
       </c>
@@ -10012,7 +10016,7 @@
       </c>
       <c r="C765" s="1"/>
     </row>
-    <row r="766" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A766" s="1" t="s">
         <v>13</v>
       </c>
@@ -10021,7 +10025,7 @@
       </c>
       <c r="C766" s="1"/>
     </row>
-    <row r="767" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A767" s="1" t="s">
         <v>13</v>
       </c>
@@ -10030,7 +10034,7 @@
       </c>
       <c r="C767" s="1"/>
     </row>
-    <row r="768" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A768" s="1" t="s">
         <v>13</v>
       </c>
@@ -10039,7 +10043,7 @@
       </c>
       <c r="C768" s="1"/>
     </row>
-    <row r="769" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A769" s="1" t="s">
         <v>13</v>
       </c>
@@ -10048,7 +10052,7 @@
       </c>
       <c r="C769" s="1"/>
     </row>
-    <row r="770" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A770" s="1" t="s">
         <v>13</v>
       </c>
@@ -10057,7 +10061,7 @@
       </c>
       <c r="C770" s="1"/>
     </row>
-    <row r="771" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A771" s="1" t="s">
         <v>13</v>
       </c>
@@ -10066,7 +10070,7 @@
       </c>
       <c r="C771" s="1"/>
     </row>
-    <row r="772" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A772" s="1" t="s">
         <v>13</v>
       </c>
@@ -10075,7 +10079,7 @@
       </c>
       <c r="C772" s="1"/>
     </row>
-    <row r="773" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A773" s="1" t="s">
         <v>13</v>
       </c>
@@ -10084,7 +10088,7 @@
       </c>
       <c r="C773" s="1"/>
     </row>
-    <row r="774" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A774" s="1" t="s">
         <v>13</v>
       </c>
@@ -10093,7 +10097,7 @@
       </c>
       <c r="C774" s="1"/>
     </row>
-    <row r="775" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A775" s="1" t="s">
         <v>13</v>
       </c>
@@ -10102,7 +10106,7 @@
       </c>
       <c r="C775" s="1"/>
     </row>
-    <row r="776" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A776" s="1" t="s">
         <v>13</v>
       </c>
@@ -10111,7 +10115,7 @@
       </c>
       <c r="C776" s="1"/>
     </row>
-    <row r="777" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A777" s="1" t="s">
         <v>13</v>
       </c>
@@ -10120,7 +10124,7 @@
       </c>
       <c r="C777" s="1"/>
     </row>
-    <row r="778" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A778" s="1" t="s">
         <v>13</v>
       </c>
@@ -10129,7 +10133,7 @@
       </c>
       <c r="C778" s="1"/>
     </row>
-    <row r="779" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A779" s="1" t="s">
         <v>13</v>
       </c>
@@ -10138,7 +10142,7 @@
       </c>
       <c r="C779" s="1"/>
     </row>
-    <row r="780" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A780" s="1" t="s">
         <v>13</v>
       </c>
@@ -10147,7 +10151,7 @@
       </c>
       <c r="C780" s="1"/>
     </row>
-    <row r="781" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A781" s="1" t="s">
         <v>13</v>
       </c>
@@ -10156,7 +10160,7 @@
       </c>
       <c r="C781" s="1"/>
     </row>
-    <row r="782" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A782" s="1" t="s">
         <v>13</v>
       </c>
@@ -10165,7 +10169,7 @@
       </c>
       <c r="C782" s="1"/>
     </row>
-    <row r="783" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A783" s="1" t="s">
         <v>13</v>
       </c>
@@ -10174,7 +10178,7 @@
       </c>
       <c r="C783" s="1"/>
     </row>
-    <row r="784" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A784" s="1" t="s">
         <v>13</v>
       </c>
@@ -10183,7 +10187,7 @@
       </c>
       <c r="C784" s="1"/>
     </row>
-    <row r="785" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A785" s="1" t="s">
         <v>13</v>
       </c>
@@ -10192,7 +10196,7 @@
       </c>
       <c r="C785" s="1"/>
     </row>
-    <row r="786" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A786" s="1" t="s">
         <v>13</v>
       </c>
@@ -10201,7 +10205,7 @@
       </c>
       <c r="C786" s="1"/>
     </row>
-    <row r="787" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A787" s="1" t="s">
         <v>13</v>
       </c>
@@ -10210,7 +10214,7 @@
       </c>
       <c r="C787" s="1"/>
     </row>
-    <row r="788" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A788" s="1" t="s">
         <v>13</v>
       </c>
@@ -10219,11 +10223,21 @@
       </c>
       <c r="C788" s="1"/>
     </row>
+    <row r="789" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A789" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B789" s="1" t="s">
+        <v>830</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C788" xr:uid="{6FDBB0FF-B482-4668-8D23-A62BD1FE53B2}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A31:C57">
-      <sortCondition ref="B1:B788"/>
-    </sortState>
+  <autoFilter ref="A1:C789" xr:uid="{6FDBB0FF-B482-4668-8D23-A62BD1FE53B2}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Uttar Pradesh"/>
+      </filters>
+    </filterColumn>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
